--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D95681-3878-4ADD-9DF5-82133EEA9EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DC8699-CE80-48FE-B186-513CF271C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -401,6 +401,15 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>选择阶段结束</t>
+  </si>
+  <si>
+    <t>选择阶段结局</t>
   </si>
 </sst>
 </file>
@@ -793,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1149,6 +1158,20 @@
       </c>
       <c r="F20" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DC8699-CE80-48FE-B186-513CF271C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DF6083-D7FC-4C1E-B449-594219E559EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="126">
   <si>
     <t>ID</t>
   </si>
@@ -410,16 +410,28 @@
   </si>
   <si>
     <t>选择阶段结局</t>
+  </si>
+  <si>
+    <t>加遗物0</t>
+  </si>
+  <si>
+    <t>VRaisingAddRelicEffect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -802,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1174,7 +1186,25 @@
         <v>121</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DF6083-D7FC-4C1E-B449-594219E559EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188BEC3A-DB4C-4F34-89CA-724DFAAF2EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -416,6 +416,18 @@
   </si>
   <si>
     <t>VRaisingAddRelicEffect</t>
+  </si>
+  <si>
+    <t>加遗物1</t>
+  </si>
+  <si>
+    <t>追加事件</t>
+  </si>
+  <si>
+    <t>VRaisingAddEventAfterCurrentEffect</t>
+  </si>
+  <si>
+    <t>追加事件Test</t>
   </si>
 </sst>
 </file>
@@ -814,13 +826,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="29.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
@@ -1201,6 +1213,40 @@
       </c>
       <c r="F22">
         <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DF6083-D7FC-4C1E-B449-594219E559EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -21,9 +15,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="138">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +174,27 @@
     <t>BARevenueShareRate</t>
   </si>
   <si>
+    <t>选择阶段结局</t>
+  </si>
+  <si>
+    <t>选择阶段结束</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>加遗物0</t>
+  </si>
+  <si>
+    <t>VRaisingAddRelicEffect</t>
+  </si>
+  <si>
+    <t>从卡组删除一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteSelected</t>
+  </si>
+  <si>
     <t>Type_M</t>
   </si>
   <si>
@@ -223,6 +237,147 @@
     <t>BackGroundColor</t>
   </si>
   <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>声乐练习</t>
+  </si>
+  <si>
+    <t>歌力+40</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>AddSinging</t>
+  </si>
+  <si>
+    <t>游戏练习</t>
+  </si>
+  <si>
+    <t>游戏力+40</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>AddGaming</t>
+  </si>
+  <si>
+    <t>对话练习</t>
+  </si>
+  <si>
+    <t>杂谈力+40</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>小憩一会</t>
+  </si>
+  <si>
+    <t>体力+25</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>体力+60</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>放一天假</t>
+  </si>
+  <si>
+    <t>体力+100</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>直播成功</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>直播失败</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>昏厥</t>
+  </si>
+  <si>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>阶段开始</t>
+  </si>
+  <si>
+    <t>#00B054</t>
+  </si>
+  <si>
+    <t>PhaseStart</t>
+  </si>
+  <si>
+    <t>阶段开始2</t>
+  </si>
+  <si>
+    <t>阶段开始3</t>
+  </si>
+  <si>
+    <t>#00B055</t>
+  </si>
+  <si>
+    <t>PhaseStart2</t>
+  </si>
+  <si>
+    <t>兼职</t>
+  </si>
+  <si>
+    <t>金钱+40</t>
+  </si>
+  <si>
+    <t>Wrok</t>
+  </si>
+  <si>
+    <t>#E5FD1F</t>
+  </si>
+  <si>
+    <t>Wrok1</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -247,9 +402,6 @@
     <t>Stream</t>
   </si>
   <si>
-    <t>Stamina</t>
-  </si>
-  <si>
     <t>#AB0580</t>
   </si>
   <si>
@@ -283,114 +435,6 @@
     <t>Ending6</t>
   </si>
   <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>声乐练习</t>
-  </si>
-  <si>
-    <t>歌力+40</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>AddSinging</t>
-  </si>
-  <si>
-    <t>游戏练习</t>
-  </si>
-  <si>
-    <t>游戏力+40</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>AddGaming</t>
-  </si>
-  <si>
-    <t>对话练习</t>
-  </si>
-  <si>
-    <t>杂谈力+40</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
-  </si>
-  <si>
-    <t>AddChatting</t>
-  </si>
-  <si>
-    <t>小憩一会</t>
-  </si>
-  <si>
-    <t>体力+25</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>外出吃饭</t>
-  </si>
-  <si>
-    <t>体力+60</t>
-  </si>
-  <si>
-    <t>Break</t>
-  </si>
-  <si>
-    <t>放一天假</t>
-  </si>
-  <si>
-    <t>体力+100</t>
-  </si>
-  <si>
-    <t>DayOff</t>
-  </si>
-  <si>
-    <t>StreamSuccess</t>
-  </si>
-  <si>
-    <t>#00B051</t>
-  </si>
-  <si>
-    <t>StreamFail</t>
-  </si>
-  <si>
-    <t>#00B052</t>
-  </si>
-  <si>
-    <t>NoStamina</t>
-  </si>
-  <si>
-    <t>#00B053</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
-  </si>
-  <si>
-    <t>PhaseStart</t>
-  </si>
-  <si>
-    <t>#00B054</t>
-  </si>
-  <si>
-    <t>PhaseStart2</t>
-  </si>
-  <si>
-    <t>#00B055</t>
-  </si>
-  <si>
     <t>NameOrID</t>
   </si>
   <si>
@@ -401,43 +445,172 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
-    <t>VRaisingPickPhaseEndingEffect</t>
-  </si>
-  <si>
-    <t>选择阶段结束</t>
-  </si>
-  <si>
-    <t>选择阶段结局</t>
-  </si>
-  <si>
-    <t>加遗物0</t>
-  </si>
-  <si>
-    <t>VRaisingAddRelicEffect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,8 +647,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5FD1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -483,11 +848,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -500,18 +1107,69 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F7BB25"/>
+      <color rgb="00E5FD1F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -560,7 +1218,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -593,26 +1251,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -645,23 +1286,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -803,30 +1427,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="31.425" customWidth="1"/>
+    <col min="3" max="3" width="29.425" customWidth="1"/>
+    <col min="4" max="4" width="28.425" customWidth="1"/>
+    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -866,7 +1485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -886,7 +1505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -906,7 +1525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -923,7 +1542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -940,7 +1559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -957,7 +1576,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -971,7 +1590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -985,7 +1604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1002,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1019,7 +1638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1036,7 +1655,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1053,7 +1672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1070,7 +1689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1087,7 +1706,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1104,7 +1723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1121,7 +1740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1138,7 +1757,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1155,7 +1774,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1172,56 +1791,71 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C731E613-AE8E-4BCD-9551-0D399E493DD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1238,74 +1872,76 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2983CD5-09FC-448D-B584-53935FACCACB}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.425" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.425" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" customWidth="1"/>
+    <col min="10" max="10" width="16.8583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1319,387 +1955,436 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D15A77-1535-49E5-8565-BF3C734F79F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
+    <col min="5" max="6" width="11.425" customWidth="1"/>
+    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
+    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
+    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1713,66 +2398,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="K1" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="L1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="N1" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -1790,33 +2475,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1834,33 +2519,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -1878,33 +2563,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1925,33 +2610,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1969,36 +2654,36 @@
         <v>7</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2019,33 +2704,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2066,33 +2751,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2110,36 +2795,36 @@
         <v>7</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2162,23 +2847,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4476F971-FB5B-4F8B-812B-3D6B61D9FDFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.425" customWidth="1"/>
+    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
+    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.425" customWidth="1"/>
+    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2192,13 +2879,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2209,7 +2896,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2218,7 +2905,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2229,7 +2916,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2238,7 +2925,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2249,16 +2936,17 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188BEC3A-DB4C-4F34-89CA-724DFAAF2EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -21,9 +15,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="138">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +174,27 @@
     <t>BARevenueShareRate</t>
   </si>
   <si>
+    <t>选择阶段结局</t>
+  </si>
+  <si>
+    <t>选择阶段结束</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>加遗物0</t>
+  </si>
+  <si>
+    <t>VRaisingAddRelicEffect</t>
+  </si>
+  <si>
+    <t>从卡组删除一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteSelected</t>
+  </si>
+  <si>
     <t>Type_M</t>
   </si>
   <si>
@@ -223,6 +237,147 @@
     <t>BackGroundColor</t>
   </si>
   <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>声乐练习</t>
+  </si>
+  <si>
+    <t>歌力+40</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>AddSinging</t>
+  </si>
+  <si>
+    <t>游戏练习</t>
+  </si>
+  <si>
+    <t>游戏力+40</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>AddGaming</t>
+  </si>
+  <si>
+    <t>对话练习</t>
+  </si>
+  <si>
+    <t>杂谈力+40</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>小憩一会</t>
+  </si>
+  <si>
+    <t>体力+25</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>体力+60</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>放一天假</t>
+  </si>
+  <si>
+    <t>体力+100</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>直播成功</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>直播失败</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>昏厥</t>
+  </si>
+  <si>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>阶段开始</t>
+  </si>
+  <si>
+    <t>#00B054</t>
+  </si>
+  <si>
+    <t>PhaseStart</t>
+  </si>
+  <si>
+    <t>阶段开始2</t>
+  </si>
+  <si>
+    <t>阶段开始3</t>
+  </si>
+  <si>
+    <t>#00B055</t>
+  </si>
+  <si>
+    <t>PhaseStart2</t>
+  </si>
+  <si>
+    <t>兼职</t>
+  </si>
+  <si>
+    <t>金钱+40</t>
+  </si>
+  <si>
+    <t>Wrok</t>
+  </si>
+  <si>
+    <t>#E5FD1F</t>
+  </si>
+  <si>
+    <t>Wrok1</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -247,9 +402,6 @@
     <t>Stream</t>
   </si>
   <si>
-    <t>Stamina</t>
-  </si>
-  <si>
     <t>#AB0580</t>
   </si>
   <si>
@@ -283,114 +435,6 @@
     <t>Ending6</t>
   </si>
   <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>声乐练习</t>
-  </si>
-  <si>
-    <t>歌力+40</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>AddSinging</t>
-  </si>
-  <si>
-    <t>游戏练习</t>
-  </si>
-  <si>
-    <t>游戏力+40</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>AddGaming</t>
-  </si>
-  <si>
-    <t>对话练习</t>
-  </si>
-  <si>
-    <t>杂谈力+40</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
-  </si>
-  <si>
-    <t>AddChatting</t>
-  </si>
-  <si>
-    <t>小憩一会</t>
-  </si>
-  <si>
-    <t>体力+25</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>外出吃饭</t>
-  </si>
-  <si>
-    <t>体力+60</t>
-  </si>
-  <si>
-    <t>Break</t>
-  </si>
-  <si>
-    <t>放一天假</t>
-  </si>
-  <si>
-    <t>体力+100</t>
-  </si>
-  <si>
-    <t>DayOff</t>
-  </si>
-  <si>
-    <t>StreamSuccess</t>
-  </si>
-  <si>
-    <t>#00B051</t>
-  </si>
-  <si>
-    <t>StreamFail</t>
-  </si>
-  <si>
-    <t>#00B052</t>
-  </si>
-  <si>
-    <t>NoStamina</t>
-  </si>
-  <si>
-    <t>#00B053</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
-  </si>
-  <si>
-    <t>PhaseStart</t>
-  </si>
-  <si>
-    <t>#00B054</t>
-  </si>
-  <si>
-    <t>PhaseStart2</t>
-  </si>
-  <si>
-    <t>#00B055</t>
-  </si>
-  <si>
     <t>NameOrID</t>
   </si>
   <si>
@@ -401,55 +445,172 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
-    <t>VRaisingPickPhaseEndingEffect</t>
-  </si>
-  <si>
-    <t>选择阶段结束</t>
-  </si>
-  <si>
-    <t>选择阶段结局</t>
-  </si>
-  <si>
-    <t>加遗物0</t>
-  </si>
-  <si>
-    <t>VRaisingAddRelicEffect</t>
-  </si>
-  <si>
-    <t>加遗物1</t>
-  </si>
-  <si>
-    <t>追加事件</t>
-  </si>
-  <si>
-    <t>VRaisingAddEventAfterCurrentEffect</t>
-  </si>
-  <si>
-    <t>追加事件Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,8 +647,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5FD1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -495,11 +848,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -512,18 +1107,69 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F7BB25"/>
+      <color rgb="00E5FD1F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -572,7 +1218,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -605,26 +1251,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -657,23 +1286,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -815,30 +1427,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="31.425" customWidth="1"/>
+    <col min="3" max="3" width="29.425" customWidth="1"/>
+    <col min="4" max="4" width="28.425" customWidth="1"/>
+    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -878,7 +1485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -898,7 +1505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -918,7 +1525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -935,7 +1542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -952,7 +1559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -969,7 +1576,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -983,7 +1590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -997,7 +1604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1014,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1031,7 +1638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1048,7 +1655,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1065,7 +1672,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1082,7 +1689,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1099,7 +1706,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1116,7 +1723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1133,7 +1740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1150,7 +1757,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1167,7 +1774,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1184,90 +1791,71 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F24" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C731E613-AE8E-4BCD-9551-0D399E493DD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1284,74 +1872,76 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2983CD5-09FC-448D-B584-53935FACCACB}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.425" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.425" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" customWidth="1"/>
+    <col min="10" max="10" width="16.8583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1365,387 +1955,436 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>97</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D15A77-1535-49E5-8565-BF3C734F79F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
+    <col min="5" max="6" width="11.425" customWidth="1"/>
+    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
+    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
+    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1759,66 +2398,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="K1" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="L1" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="N1" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -1836,33 +2475,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -1880,33 +2519,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -1924,33 +2563,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1971,33 +2610,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -2015,36 +2654,36 @@
         <v>7</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2065,33 +2704,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2112,33 +2751,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2156,36 +2795,36 @@
         <v>7</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2208,23 +2847,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4476F971-FB5B-4F8B-812B-3D6B61D9FDFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.425" customWidth="1"/>
+    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
+    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.425" customWidth="1"/>
+    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2238,13 +2879,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2255,7 +2896,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2264,7 +2905,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2275,7 +2916,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2284,7 +2925,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2295,16 +2936,17 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188BEC3A-DB4C-4F34-89CA-724DFAAF2EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF2DE9A-C055-4D03-9CB8-01385092B399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188BEC3A-DB4C-4F34-89CA-724DFAAF2EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -15,6 +21,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -22,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
   <si>
     <t>ID</t>
   </si>
@@ -174,443 +181,275 @@
     <t>BARevenueShareRate</t>
   </si>
   <si>
+    <t>Type_M</t>
+  </si>
+  <si>
+    <t>sadf</t>
+  </si>
+  <si>
+    <t>VCardTypeCondition</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>VCardRarityCondition</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>VCardPoolCondition</t>
+  </si>
+  <si>
+    <t>0,1,2</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>CostType</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>BackGroundColor</t>
+  </si>
+  <si>
+    <t>TurnCount</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>InitialViewers</t>
+  </si>
+  <si>
+    <t>SuccessEvent</t>
+  </si>
+  <si>
+    <t>FailEvent</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>歌回</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>#AB0580</t>
+  </si>
+  <si>
+    <t>游戏回</t>
+  </si>
+  <si>
+    <t>杂谈回</t>
+  </si>
+  <si>
+    <t>Ending1</t>
+  </si>
+  <si>
+    <t>Stream3</t>
+  </si>
+  <si>
+    <t>Ending2</t>
+  </si>
+  <si>
+    <t>0, 2</t>
+  </si>
+  <si>
+    <t>Ending3</t>
+  </si>
+  <si>
+    <t>Ending4</t>
+  </si>
+  <si>
+    <t>Ending5</t>
+  </si>
+  <si>
+    <t>Ending6</t>
+  </si>
+  <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>声乐练习</t>
+  </si>
+  <si>
+    <t>歌力+40</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>AddSinging</t>
+  </si>
+  <si>
+    <t>游戏练习</t>
+  </si>
+  <si>
+    <t>游戏力+40</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>AddGaming</t>
+  </si>
+  <si>
+    <t>对话练习</t>
+  </si>
+  <si>
+    <t>杂谈力+40</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>小憩一会</t>
+  </si>
+  <si>
+    <t>体力+25</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>体力+60</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>放一天假</t>
+  </si>
+  <si>
+    <t>体力+100</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
+    <t>NoStamina</t>
+  </si>
+  <si>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>PhaseStart</t>
+  </si>
+  <si>
+    <t>#00B054</t>
+  </si>
+  <si>
+    <t>PhaseStart2</t>
+  </si>
+  <si>
+    <t>#00B055</t>
+  </si>
+  <si>
+    <t>NameOrID</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>VPhaseEndingAttributeCondition</t>
+  </si>
+  <si>
+    <t>VPhaseEndingEventCondition</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>选择阶段结束</t>
+  </si>
+  <si>
     <t>选择阶段结局</t>
   </si>
   <si>
-    <t>选择阶段结束</t>
-  </si>
-  <si>
-    <t>VRaisingPickPhaseEndingEffect</t>
-  </si>
-  <si>
     <t>加遗物0</t>
   </si>
   <si>
     <t>VRaisingAddRelicEffect</t>
   </si>
   <si>
-    <t>从卡组删除一张卡牌</t>
-  </si>
-  <si>
-    <t>VRaisingDeleteSelected</t>
-  </si>
-  <si>
-    <t>Type_M</t>
-  </si>
-  <si>
-    <t>sadf</t>
-  </si>
-  <si>
-    <t>VCardTypeCondition</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>VCardRarityCondition</t>
-  </si>
-  <si>
-    <t>Pool</t>
-  </si>
-  <si>
-    <t>VCardPoolCondition</t>
-  </si>
-  <si>
-    <t>0,1,2</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>CostType</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>BackGroundColor</t>
-  </si>
-  <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>声乐练习</t>
-  </si>
-  <si>
-    <t>歌力+40</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>AddSinging</t>
-  </si>
-  <si>
-    <t>游戏练习</t>
-  </si>
-  <si>
-    <t>游戏力+40</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>AddGaming</t>
-  </si>
-  <si>
-    <t>对话练习</t>
-  </si>
-  <si>
-    <t>杂谈力+40</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
-  </si>
-  <si>
-    <t>AddChatting</t>
-  </si>
-  <si>
-    <t>小憩一会</t>
-  </si>
-  <si>
-    <t>体力+25</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>外出吃饭</t>
-  </si>
-  <si>
-    <t>体力+60</t>
-  </si>
-  <si>
-    <t>Out</t>
-  </si>
-  <si>
-    <t>放一天假</t>
-  </si>
-  <si>
-    <t>体力+100</t>
-  </si>
-  <si>
-    <t>DayOff</t>
-  </si>
-  <si>
-    <t>直播成功</t>
-  </si>
-  <si>
-    <t>#00B051</t>
-  </si>
-  <si>
-    <t>StreamSuccess</t>
-  </si>
-  <si>
-    <t>直播失败</t>
-  </si>
-  <si>
-    <t>#00B052</t>
-  </si>
-  <si>
-    <t>StreamFail</t>
-  </si>
-  <si>
-    <t>昏厥</t>
-  </si>
-  <si>
-    <t>#00B053</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
-  </si>
-  <si>
-    <t>阶段开始</t>
-  </si>
-  <si>
-    <t>#00B054</t>
-  </si>
-  <si>
-    <t>PhaseStart</t>
-  </si>
-  <si>
-    <t>阶段开始2</t>
-  </si>
-  <si>
-    <t>阶段开始3</t>
-  </si>
-  <si>
-    <t>#00B055</t>
-  </si>
-  <si>
-    <t>PhaseStart2</t>
-  </si>
-  <si>
-    <t>兼职</t>
-  </si>
-  <si>
-    <t>金钱+40</t>
-  </si>
-  <si>
-    <t>Wrok</t>
-  </si>
-  <si>
-    <t>#E5FD1F</t>
-  </si>
-  <si>
-    <t>Wrok1</t>
-  </si>
-  <si>
-    <t>TurnCount</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>InitialViewers</t>
-  </si>
-  <si>
-    <t>SuccessEvent</t>
-  </si>
-  <si>
-    <t>FailEvent</t>
-  </si>
-  <si>
-    <t>Conditions</t>
-  </si>
-  <si>
-    <t>歌回</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>#AB0580</t>
-  </si>
-  <si>
-    <t>游戏回</t>
-  </si>
-  <si>
-    <t>杂谈回</t>
-  </si>
-  <si>
-    <t>Ending1</t>
-  </si>
-  <si>
-    <t>Stream3</t>
-  </si>
-  <si>
-    <t>Ending2</t>
-  </si>
-  <si>
-    <t>0, 2</t>
-  </si>
-  <si>
-    <t>Ending3</t>
-  </si>
-  <si>
-    <t>Ending4</t>
-  </si>
-  <si>
-    <t>Ending5</t>
-  </si>
-  <si>
-    <t>Ending6</t>
-  </si>
-  <si>
-    <t>NameOrID</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>VPhaseEndingAttributeCondition</t>
-  </si>
-  <si>
-    <t>VPhaseEndingEventCondition</t>
+    <t>加遗物1</t>
+  </si>
+  <si>
+    <t>追加事件</t>
+  </si>
+  <si>
+    <t>VRaisingAddEventAfterCurrentEffect</t>
+  </si>
+  <si>
+    <t>追加事件Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -647,200 +486,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5FD1F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -848,253 +495,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1107,69 +512,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="00F7BB25"/>
-      <color rgb="00E5FD1F"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1218,7 +572,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1251,9 +605,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1286,6 +657,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1427,25 +815,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="28.425" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1465,7 +858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1485,7 +878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1505,7 +898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1525,7 +918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1542,7 +935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1559,7 +952,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1576,7 +969,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1590,7 +983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1604,7 +997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1621,7 +1014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1638,7 +1031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1655,7 +1048,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1672,7 +1065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1689,7 +1082,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1706,7 +1099,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1723,7 +1116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1740,7 +1133,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1757,7 +1150,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1774,7 +1167,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1791,71 +1184,90 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>125</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C731E613-AE8E-4BCD-9551-0D399E493DD1}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1872,76 +1284,74 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2983CD5-09FC-448D-B584-53935FACCACB}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.425" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" customWidth="1"/>
-    <col min="6" max="6" width="8.425" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1955,436 +1365,387 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
         <v>97</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>97</v>
       </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>85</v>
-      </c>
       <c r="I9" s="7" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="J10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D15A77-1535-49E5-8565-BF3C734F79F3}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
-    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2398,66 +1759,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>67</v>
       </c>
-      <c r="J1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K1" t="s">
-        <v>116</v>
-      </c>
-      <c r="L1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" t="s">
-        <v>118</v>
-      </c>
-      <c r="N1" t="s">
-        <v>119</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>121</v>
-      </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -2475,33 +1836,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -2519,33 +1880,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -2563,33 +1924,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -2610,33 +1971,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -2654,36 +2015,36 @@
         <v>7</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2704,33 +2065,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2751,33 +2112,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2795,36 +2156,36 @@
         <v>7</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2847,25 +2208,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4476F971-FB5B-4F8B-812B-3D6B61D9FDFF}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2879,13 +2238,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2896,7 +2255,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2905,7 +2264,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2916,7 +2275,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2925,7 +2284,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2936,17 +2295,16 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188BEC3A-DB4C-4F34-89CA-724DFAAF2EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EEAC22-65F8-4F45-A118-8F8C7376CE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="132">
   <si>
     <t>ID</t>
   </si>
@@ -346,9 +346,6 @@
     <t>体力+60</t>
   </si>
   <si>
-    <t>Break</t>
-  </si>
-  <si>
     <t>放一天假</t>
   </si>
   <si>
@@ -428,6 +425,15 @@
   </si>
   <si>
     <t>追加事件Test</t>
+  </si>
+  <si>
+    <t>从卡组删除一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteSelected</t>
+  </si>
+  <si>
+    <t>Out</t>
   </si>
 </sst>
 </file>
@@ -826,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1189,13 +1195,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1203,13 +1209,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
         <v>124</v>
-      </c>
-      <c r="C22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1220,13 +1226,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1237,16 +1243,30 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" t="s">
         <v>127</v>
-      </c>
-      <c r="D24" t="s">
-        <v>128</v>
       </c>
       <c r="F24" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1560,7 @@
         <v>98</v>
       </c>
       <c r="J6" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1548,10 +1568,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
         <v>103</v>
-      </c>
-      <c r="C7" t="s">
-        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>97</v>
@@ -1572,7 +1592,7 @@
         <v>98</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1580,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>97</v>
@@ -1598,10 +1618,10 @@
         <v>97</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1609,7 +1629,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>97</v>
@@ -1627,10 +1647,10 @@
         <v>97</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1638,7 +1658,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
         <v>97</v>
@@ -1656,10 +1676,10 @@
         <v>97</v>
       </c>
       <c r="I10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" t="s">
         <v>111</v>
-      </c>
-      <c r="J10" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1667,7 +1687,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>97</v>
@@ -1685,10 +1705,10 @@
         <v>97</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1696,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
         <v>97</v>
@@ -1714,10 +1734,10 @@
         <v>97</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2238,10 +2258,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" t="s">
         <v>117</v>
-      </c>
-      <c r="F1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,7 +2275,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2275,7 +2295,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2295,7 +2315,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E4">
         <v>5</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EEAC22-65F8-4F45-A118-8F8C7376CE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3788F3-7A84-431A-A68D-41880868EA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -839,7 +839,7 @@
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
     <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
     <col min="6" max="6" width="29.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EEAC22-65F8-4F45-A118-8F8C7376CE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{50E5FAE0-6D8C-4C7A-945F-E71747CBD6FA}"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -21,9 +15,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="144">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +174,48 @@
     <t>BARevenueShareRate</t>
   </si>
   <si>
+    <t>选择阶段结局</t>
+  </si>
+  <si>
+    <t>选择阶段结束</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>加遗物0</t>
+  </si>
+  <si>
+    <t>VRaisingAddRelicEffect</t>
+  </si>
+  <si>
+    <t>加遗物1</t>
+  </si>
+  <si>
+    <t>追加事件Test</t>
+  </si>
+  <si>
+    <t>追加事件</t>
+  </si>
+  <si>
+    <t>VRaisingAddEventAfterCurrentEffect</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>从卡组删除一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteSelected</t>
+  </si>
+  <si>
+    <t>从三张卡牌中选择一张卡牌加入卡组</t>
+  </si>
+  <si>
+    <t>VRaisingAddSelectedFrom3Effect</t>
+  </si>
+  <si>
     <t>Type_M</t>
   </si>
   <si>
@@ -223,6 +258,144 @@
     <t>BackGroundColor</t>
   </si>
   <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
+    <t>声乐练习</t>
+  </si>
+  <si>
+    <t>歌力+40</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>AddSinging</t>
+  </si>
+  <si>
+    <t>游戏练习</t>
+  </si>
+  <si>
+    <t>游戏力+40</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>AddGaming</t>
+  </si>
+  <si>
+    <t>对话练习</t>
+  </si>
+  <si>
+    <t>杂谈力+40</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>小憩一会</t>
+  </si>
+  <si>
+    <t>体力+25</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>体力+60</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>放一天假</t>
+  </si>
+  <si>
+    <t>体力+100</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>直播成功</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>直播失败</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>昏厥</t>
+  </si>
+  <si>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>阶段开始</t>
+  </si>
+  <si>
+    <t>#00B054</t>
+  </si>
+  <si>
+    <t>PhaseStart</t>
+  </si>
+  <si>
+    <t>阶段开始2</t>
+  </si>
+  <si>
+    <t>阶段开始3</t>
+  </si>
+  <si>
+    <t>#00B055</t>
+  </si>
+  <si>
+    <t>PhaseStart2</t>
+  </si>
+  <si>
+    <t>兼职</t>
+  </si>
+  <si>
+    <t>金钱+40</t>
+  </si>
+  <si>
+    <t>Wrok</t>
+  </si>
+  <si>
+    <t>#E5FD1F</t>
+  </si>
+  <si>
+    <t>Wrok1</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -247,9 +420,6 @@
     <t>Stream</t>
   </si>
   <si>
-    <t>Stamina</t>
-  </si>
-  <si>
     <t>#AB0580</t>
   </si>
   <si>
@@ -259,15 +429,15 @@
     <t>杂谈回</t>
   </si>
   <si>
-    <t>Ending1</t>
+    <t>歌杂</t>
+  </si>
+  <si>
+    <t>Ending2</t>
   </si>
   <si>
     <t>Stream3</t>
   </si>
   <si>
-    <t>Ending2</t>
-  </si>
-  <si>
     <t>0, 2</t>
   </si>
   <si>
@@ -283,111 +453,6 @@
     <t>Ending6</t>
   </si>
   <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>声乐练习</t>
-  </si>
-  <si>
-    <t>歌力+40</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>AddSinging</t>
-  </si>
-  <si>
-    <t>游戏练习</t>
-  </si>
-  <si>
-    <t>游戏力+40</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>AddGaming</t>
-  </si>
-  <si>
-    <t>对话练习</t>
-  </si>
-  <si>
-    <t>杂谈力+40</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
-  </si>
-  <si>
-    <t>AddChatting</t>
-  </si>
-  <si>
-    <t>小憩一会</t>
-  </si>
-  <si>
-    <t>体力+25</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>外出吃饭</t>
-  </si>
-  <si>
-    <t>体力+60</t>
-  </si>
-  <si>
-    <t>放一天假</t>
-  </si>
-  <si>
-    <t>体力+100</t>
-  </si>
-  <si>
-    <t>DayOff</t>
-  </si>
-  <si>
-    <t>StreamSuccess</t>
-  </si>
-  <si>
-    <t>#00B051</t>
-  </si>
-  <si>
-    <t>StreamFail</t>
-  </si>
-  <si>
-    <t>#00B052</t>
-  </si>
-  <si>
-    <t>NoStamina</t>
-  </si>
-  <si>
-    <t>#00B053</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
-  </si>
-  <si>
-    <t>PhaseStart</t>
-  </si>
-  <si>
-    <t>#00B054</t>
-  </si>
-  <si>
-    <t>PhaseStart2</t>
-  </si>
-  <si>
-    <t>#00B055</t>
-  </si>
-  <si>
     <t>NameOrID</t>
   </si>
   <si>
@@ -398,64 +463,179 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
-    <t>VRaisingPickPhaseEndingEffect</t>
-  </si>
-  <si>
-    <t>选择阶段结束</t>
-  </si>
-  <si>
-    <t>选择阶段结局</t>
-  </si>
-  <si>
-    <t>加遗物0</t>
-  </si>
-  <si>
-    <t>VRaisingAddRelicEffect</t>
-  </si>
-  <si>
-    <t>加遗物1</t>
-  </si>
-  <si>
-    <t>追加事件</t>
-  </si>
-  <si>
-    <t>VRaisingAddEventAfterCurrentEffect</t>
-  </si>
-  <si>
-    <t>追加事件Test</t>
-  </si>
-  <si>
-    <t>从卡组删除一张卡牌</t>
-  </si>
-  <si>
-    <t>VRaisingDeleteSelected</t>
-  </si>
-  <si>
-    <t>Out</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,8 +672,200 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5FD1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -501,11 +873,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -514,22 +1128,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -578,7 +1239,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -611,26 +1272,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -663,23 +1307,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -821,30 +1448,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B7D76C-5297-47CF-900A-9659A5CEEA70}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="31.425" customWidth="1"/>
+    <col min="3" max="3" width="29.425" customWidth="1"/>
+    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +1486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -884,7 +1506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -904,7 +1526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -924,7 +1546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -941,7 +1563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -958,7 +1580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -975,7 +1597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -989,7 +1611,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1003,7 +1625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1020,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1037,7 +1659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1054,7 +1676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1071,7 +1693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1088,7 +1710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1105,7 +1727,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1122,7 +1744,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1139,7 +1761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1156,7 +1778,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1173,7 +1795,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1190,104 +1812,122 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C731E613-AE8E-4BCD-9551-0D399E493DD1}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1304,468 +1944,523 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>53</v>
+      <c r="B4" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
-      </c>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2983CD5-09FC-448D-B584-53935FACCACB}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.425" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.1416666666667" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.425" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.8583333333333" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:10">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" s="4" customFormat="1" spans="1:10">
+      <c r="A2" s="4">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="4">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" s="4" customFormat="1" spans="1:10">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="C3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="4">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" spans="1:10">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="4">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" spans="1:10">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="4">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2">
+      <c r="H5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" spans="1:10">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" spans="1:10">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" spans="1:10">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" spans="1:10">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:10">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:10">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="1:10">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:10">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2">
+      <c r="F13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="4">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="H13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" t="s">
-        <v>114</v>
+      <c r="I13" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D15A77-1535-49E5-8565-BF3C734F79F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
+    <col min="5" max="6" width="11.425" customWidth="1"/>
+    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
+    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
+    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1779,75 +2474,75 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="I1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="K1" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="L1" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="N1" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
         <v>10</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -1856,42 +2551,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L3">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -1900,42 +2595,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J4">
+        <v>8</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>10</v>
-      </c>
-      <c r="K4">
-        <v>30</v>
-      </c>
-      <c r="L4">
-        <v>10000</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1944,42 +2639,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
       <c r="K5">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="L5">
-        <v>10000</v>
+        <v>25</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1991,33 +2686,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -2035,36 +2730,36 @@
         <v>7</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2085,33 +2780,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2132,33 +2827,33 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2176,36 +2871,36 @@
         <v>7</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2228,23 +2923,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4476F971-FB5B-4F8B-812B-3D6B61D9FDFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.425" customWidth="1"/>
+    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
+    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.425" customWidth="1"/>
+    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2258,13 +2955,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2275,7 +2972,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2284,7 +2981,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2295,7 +2992,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2304,7 +3001,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2315,16 +3012,17 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5006FBCC-F1CF-444B-82E5-A5CB2196C472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -22,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -468,174 +472,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,194 +532,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -873,253 +541,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1128,69 +554,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1448,22 +829,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1597,7 +978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1611,7 +992,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1625,7 +1006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1812,7 +1193,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1877,7 +1258,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1891,7 +1272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1910,21 +1291,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1979,7 +1358,7 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="D4" t="s">
@@ -1989,35 +1368,30 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="10"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="4" customWidth="1"/>
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:10">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2049,7 +1423,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" s="4" customFormat="1" spans="1:10">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2081,7 +1455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" spans="1:10">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -2113,7 +1487,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" spans="1:10">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -2145,7 +1519,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" spans="1:10">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -2177,7 +1551,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" spans="1:10">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -2209,7 +1583,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" spans="1:10">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -2241,7 +1615,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" spans="1:10">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -2273,7 +1647,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" spans="1:10">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -2305,7 +1679,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" spans="1:10">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -2337,7 +1711,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" spans="1:10">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -2369,7 +1743,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -2401,7 +1775,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" spans="1:10">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -2435,29 +1809,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
-    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2507,7 +1879,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2551,7 +1923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2595,7 +1967,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2923,22 +2295,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3023,6 +2393,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="153">
   <si>
     <t>ID</t>
   </si>
@@ -216,10 +216,7 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
-    <t>Type_M</t>
-  </si>
-  <si>
-    <t>sadf</t>
+    <t>M卡</t>
   </si>
   <si>
     <t>VCardTypeCondition</t>
@@ -228,12 +225,24 @@
     <t>M</t>
   </si>
   <si>
+    <t>A卡</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Rare</t>
   </si>
   <si>
     <t>VCardRarityCondition</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
     <t>Pool</t>
   </si>
   <si>
@@ -318,7 +327,9 @@
     <t>外出吃饭</t>
   </si>
   <si>
-    <t>体力+60</t>
+    <t>体力+60
+体力+40，获得一张卡牌
+体力+40，获得一个消耗品</t>
   </si>
   <si>
     <t>Out</t>
@@ -327,7 +338,7 @@
     <t>放一天假</t>
   </si>
   <si>
-    <t>体力+100</t>
+    <t>体力+100,从卡组中选择一张卡牌删除</t>
   </si>
   <si>
     <t>DayOff</t>
@@ -384,16 +395,36 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>金钱+40</t>
-  </si>
-  <si>
-    <t>Wrok</t>
+    <t>金钱+60，体力-10
+金钱+30，获得一张卡，体力-10
+金钱+100，体力-15</t>
+  </si>
+  <si>
+    <t>Work</t>
   </si>
   <si>
     <t>#E5FD1F</t>
   </si>
   <si>
-    <t>Wrok1</t>
+    <t>Work1</t>
+  </si>
+  <si>
+    <t>剪辑切片</t>
+  </si>
+  <si>
+    <t>粉丝+100，金钱+15，从卡组中删除一张牌</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>网络购物</t>
+  </si>
+  <si>
+    <t>进入商店界面</t>
+  </si>
+  <si>
+    <t>#0BF30B</t>
   </si>
   <si>
     <t>TurnCount</t>
@@ -475,14 +506,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,7 +659,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,6 +699,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE5FD1F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0BF30B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -974,152 +1004,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1128,12 +1158,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1188,6 +1236,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="000BF30B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1917,8 +1970,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1951,14 +2004,12 @@
       <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2"/>
+      <c r="D2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1966,10 +2017,11 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C3"/>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
@@ -1979,18 +2031,58 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>68</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="10"/>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2001,12 +2093,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.2833333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" style="4" customWidth="1"/>
+    <col min="3" max="3" width="27.6666666666667" style="4" customWidth="1"/>
     <col min="4" max="4" width="10.1416666666667" style="4" customWidth="1"/>
     <col min="5" max="5" width="8.14166666666667" style="4" customWidth="1"/>
     <col min="6" max="6" width="8.425" style="4" customWidth="1"/>
@@ -2017,7 +2109,7 @@
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:10">
+    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2031,33 +2123,33 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" s="4" customFormat="1" spans="1:10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>56</v>
@@ -2066,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G2" s="4">
         <v>10</v>
@@ -2074,22 +2166,22 @@
       <c r="H2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>79</v>
+      <c r="I2" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="1" spans="1:10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="4">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>56</v>
@@ -2098,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G3" s="4">
         <v>10</v>
@@ -2106,22 +2198,22 @@
       <c r="H3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>83</v>
+      <c r="I3" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" s="4" customFormat="1" spans="1:10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>56</v>
@@ -2130,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G4" s="4">
         <v>10</v>
@@ -2138,299 +2230,360 @@
       <c r="H4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>87</v>
+      <c r="I4" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="1" spans="1:10">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="4">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" spans="1:10">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" ht="48" customHeight="1" spans="1:10">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A7" s="4">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E7" s="4">
         <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" spans="1:10">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" s="4" customFormat="1" spans="1:10">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A9" s="4">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>104</v>
+        <v>94</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" spans="1:10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" spans="1:10">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A11" s="4">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>110</v>
+        <v>94</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" spans="1:10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>114</v>
+        <v>94</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" spans="1:10">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E13" s="4">
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G13" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>119</v>
+        <v>94</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>122</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="4">
+        <v>20</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2474,37 +2627,37 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="M1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2512,28 +2665,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J2">
         <v>8</v>
@@ -2556,28 +2709,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -2600,28 +2753,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -2644,28 +2797,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -2691,28 +2844,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -2730,7 +2883,7 @@
         <v>7</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2738,28 +2891,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2785,28 +2938,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" t="s">
         <v>137</v>
-      </c>
-      <c r="C8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" t="s">
-        <v>128</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2832,28 +2985,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2871,7 +3024,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2879,28 +3032,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2955,10 +3108,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2972,7 +3125,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2992,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3012,13 +3165,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0017EE-7D23-4396-B8FD-0DEFE5FFBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -22,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="156">
   <si>
     <t>ID</t>
   </si>
@@ -494,172 +498,31 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
+  </si>
+  <si>
+    <t>LiveType</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VCardLiveTypeCondition</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,194 +571,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -903,253 +580,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1158,92 +593,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
+      <color rgb="FF0BF30B"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1501,22 +891,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1650,7 +1040,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1664,7 +1054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1678,7 +1068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1865,7 +1255,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1930,7 +1320,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1944,7 +1334,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1963,21 +1353,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2004,7 +1392,6 @@
       <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="C2"/>
       <c r="D2" t="s">
         <v>62</v>
       </c>
@@ -2019,7 +1406,6 @@
       <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="C3"/>
       <c r="D3" t="s">
         <v>62</v>
       </c>
@@ -2041,7 +1427,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2073,10 +1459,9 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" t="s">
         <v>70</v>
       </c>
-      <c r="C7"/>
       <c r="D7" t="s">
         <v>71</v>
       </c>
@@ -2084,32 +1469,44 @@
         <v>72</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="27.6666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="4" customWidth="1"/>
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2141,7 +1538,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="30" customHeight="1">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2173,7 +1570,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -2205,7 +1602,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -2237,7 +1634,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -2269,7 +1666,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" ht="48" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -2301,7 +1698,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="7" spans="1:10" ht="30" customHeight="1">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -2333,7 +1730,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="8" spans="1:10" ht="30" customHeight="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -2365,7 +1762,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="9" spans="1:10" ht="30" customHeight="1">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -2397,7 +1794,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="10" spans="1:10" ht="30" customHeight="1">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -2429,7 +1826,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="11" spans="1:10" ht="30" customHeight="1">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -2461,7 +1858,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="12" spans="1:10" ht="30" customHeight="1">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -2493,7 +1890,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="13" spans="1:10" ht="30" customHeight="1">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -2525,7 +1922,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:10">
+    <row r="14" spans="1:10" ht="30" customHeight="1">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -2557,7 +1954,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" spans="1:10" ht="30" customHeight="1">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -2588,29 +1985,27 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
-    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2660,7 +2055,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2704,7 +2099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2748,7 +2143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3076,22 +2471,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3176,6 +2569,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -412,7 +412,9 @@
     <t>剪辑切片</t>
   </si>
   <si>
-    <t>粉丝+100，金钱+15，从卡组中删除一张牌</t>
+    <t>粉丝+100，金钱+15，从卡组中删除一张牌
+粉丝+100，舰长+1，选择一张卡牌变化成随机卡牌
+粉丝+100，随机获得1个消耗品（稀有度高于提督）</t>
   </si>
   <si>
     <t>Edit</t>
@@ -2004,7 +2006,6 @@
       <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="C2"/>
       <c r="D2" t="s">
         <v>62</v>
       </c>
@@ -2019,7 +2020,6 @@
       <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="C3"/>
       <c r="D3" t="s">
         <v>62</v>
       </c>
@@ -2076,7 +2076,6 @@
       <c r="B7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C7"/>
       <c r="D7" t="s">
         <v>71</v>
       </c>
@@ -2532,7 +2531,7 @@
       <c r="B14" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>125</v>
       </c>
       <c r="D14" s="4" t="s">

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0017EE-7D23-4396-B8FD-0DEFE5FFBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8843F59-FF97-445C-9799-07E0F5417482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -2201,7 +2201,7 @@
         <v>137</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="s">
         <v>81</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0017EE-7D23-4396-B8FD-0DEFE5FFBD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -28,6 +22,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="161">
   <si>
     <t>ID</t>
   </si>
@@ -254,6 +250,15 @@
   </si>
   <si>
     <t>0,1,2</t>
+  </si>
+  <si>
+    <t>LiveType</t>
+  </si>
+  <si>
+    <t>VCardLiveTypeCondition</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>Duration</t>
@@ -431,6 +436,77 @@
     <t>#0BF30B</t>
   </si>
   <si>
+    <t>歌回成功事件</t>
+  </si>
+  <si>
+    <r>
+      <t>粉丝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，金钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，舰长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，获得一张卡</t>
+    </r>
+  </si>
+  <si>
+    <t>SingSuccess</t>
+  </si>
+  <si>
+    <t>游戏回成功事件</t>
+  </si>
+  <si>
+    <t>杂谈回成功事件</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -498,31 +574,184 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
-    <t>LiveType</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VCardLiveTypeCondition</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -571,8 +800,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -580,24 +995,272 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -618,22 +1281,66 @@
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF0BF30B"/>
+      <color rgb="000BF30B"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -891,22 +1598,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="31.425" customWidth="1"/>
+    <col min="3" max="3" width="29.425" customWidth="1"/>
+    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1040,7 +1747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1054,7 +1761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1068,7 +1775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1255,7 +1962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1320,7 +2027,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1334,7 +2041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1353,19 +2060,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1474,538 +2183,626 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.7083333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.425" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.8583333333333" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" customHeight="1" spans="1:10">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1">
-      <c r="A2" s="4">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:10">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="3">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1">
-      <c r="A3" s="4">
+      <c r="I2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:10">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="3">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="4">
+      <c r="I3" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:10">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1">
-      <c r="A4" s="4">
+      <c r="I4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:10">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:10">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="F6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:10">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:10">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="4">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="F13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1">
-      <c r="A6" s="4">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="F14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="3">
+        <v>20</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="I14" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1">
-      <c r="A7" s="4">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="4">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1">
-      <c r="A8" s="4">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1">
-      <c r="A9" s="4">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1">
-      <c r="A10" s="4">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1">
-      <c r="A12" s="4">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1">
-      <c r="A14" s="4">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="4">
-        <v>20</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1">
-      <c r="A15" s="4">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="4">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>129</v>
+      <c r="J16" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:9">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:9">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
+    <col min="5" max="6" width="11.425" customWidth="1"/>
+    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
+    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
+    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2022,66 +2819,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="L1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J2">
         <v>8</v>
@@ -2092,40 +2889,40 @@
       <c r="L2">
         <v>10</v>
       </c>
-      <c r="M2">
-        <v>6</v>
+      <c r="M2" s="3">
+        <v>14</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -2143,33 +2940,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -2192,28 +2989,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -2230,7 +3027,7 @@
       <c r="N5">
         <v>7</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <v>-1</v>
       </c>
     </row>
@@ -2239,28 +3036,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -2277,8 +3074,8 @@
       <c r="N6">
         <v>7</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>144</v>
+      <c r="O6" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2286,28 +3083,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" t="s">
         <v>145</v>
-      </c>
-      <c r="C7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" t="s">
-        <v>137</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -2324,7 +3121,7 @@
       <c r="N7">
         <v>7</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2333,28 +3130,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -2371,7 +3168,7 @@
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="4">
         <v>-1</v>
       </c>
     </row>
@@ -2380,28 +3177,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -2418,8 +3215,8 @@
       <c r="N9">
         <v>7</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>144</v>
+      <c r="O9" s="4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2427,28 +3224,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -2465,26 +3262,28 @@
       <c r="N10">
         <v>7</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="4">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.425" customWidth="1"/>
+    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
+    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.425" customWidth="1"/>
+    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2501,10 +3300,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2518,7 +3317,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2538,7 +3337,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2558,16 +3357,17 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8843F59-FF97-445C-9799-07E0F5417482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39604016-F10A-4F42-A60E-A3768DD47C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId2"/>
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
-    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId5"/>
+    <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
+    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="157">
   <si>
     <t>ID</t>
   </si>
@@ -507,6 +508,9 @@
   </si>
   <si>
     <t>VCardLiveTypeCondition</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
   </si>
 </sst>
 </file>
@@ -2475,6 +2479,38 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134B16D6-70B9-4946-9E03-540C89D9600D}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="4"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId5"/>
+    <sheet name="PlacingConditions" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="170">
   <si>
     <t>ID</t>
   </si>
@@ -274,6 +275,9 @@
   </si>
   <si>
     <t>BackGroundColor</t>
+  </si>
+  <si>
+    <t>PlacingCondition</t>
   </si>
   <si>
     <t>DialogueNode</t>
@@ -467,7 +471,7 @@
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
-      <t>+50</t>
+      <t>+30</t>
     </r>
     <r>
       <rPr>
@@ -504,9 +508,24 @@
     <t>游戏回成功事件</t>
   </si>
   <si>
+    <t>gameSuccess</t>
+  </si>
+  <si>
     <t>杂谈回成功事件</t>
   </si>
   <si>
+    <t>进阶唱歌练习</t>
+  </si>
+  <si>
+    <t>歌力+60</t>
+  </si>
+  <si>
+    <t>进阶游戏练习</t>
+  </si>
+  <si>
+    <t>进阶杂谈练习</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -574,6 +593,15 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TargetValue</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1269,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1255,9 +1283,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2201,7 +2226,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
@@ -2213,11 +2238,11 @@
     <col min="7" max="7" width="6.85833333333333" style="3" customWidth="1"/>
     <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="15.5666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="10" max="11" width="16.8583333333333" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:10">
+    <row r="1" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2245,19 +2270,22 @@
       <c r="I1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
       <c r="A2" s="3">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
@@ -2266,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3">
         <v>10</v>
@@ -2274,22 +2302,22 @@
       <c r="H2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="7" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:10">
+      <c r="K2" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
@@ -2298,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2306,22 +2334,22 @@
       <c r="H3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:10">
+      <c r="K3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
@@ -2330,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="3">
         <v>10</v>
@@ -2338,331 +2366,331 @@
       <c r="H4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="9" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:10">
+      <c r="K4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="I5" s="10" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:10">
+      <c r="K5" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:11">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:10">
+      <c r="I6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:10">
+      <c r="I7" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:10">
+      <c r="K8" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:10">
+      <c r="K9" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:10">
+      <c r="K10" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="J11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:10">
+      <c r="K11" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:10">
+      <c r="K12" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:10">
+      <c r="K13" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3">
         <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>129</v>
+        <v>98</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -2670,112 +2698,151 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:10">
+        <v>98</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
       <c r="A16" s="3">
         <v>14</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>134</v>
       </c>
+      <c r="C16" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="D16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I16" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
+      <c r="I16" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
       <c r="A17" s="3">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>136</v>
+      <c r="B17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
+      <c r="I17" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>137</v>
+      <c r="B18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="11" t="s">
         <v>98</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:2">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:2">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2787,7 +2854,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.425" customWidth="1"/>
@@ -2797,15 +2864,16 @@
     <col min="5" max="6" width="11.425" customWidth="1"/>
     <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
     <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
-    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
+    <col min="10" max="10" width="16.3333333333333" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.8583333333333" customWidth="1"/>
+    <col min="13" max="13" width="15.8583333333333" customWidth="1"/>
+    <col min="14" max="14" width="13.1416666666667" customWidth="1"/>
+    <col min="15" max="15" width="10.425" customWidth="1"/>
+    <col min="16" max="16" width="12.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2834,435 +2902,438 @@
         <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="K1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>147</v>
+      </c>
+      <c r="O1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J2">
+        <v>152</v>
+      </c>
+      <c r="K2">
         <v>8</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>100</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>10</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>14</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J3">
+        <v>152</v>
+      </c>
+      <c r="K3">
         <v>8</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>100</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>6</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4">
+        <v>152</v>
+      </c>
+      <c r="K4">
         <v>8</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>100</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>6</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J5">
+        <v>152</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>200</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>25</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>6</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>7</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" t="s">
         <v>151</v>
-      </c>
-      <c r="D6" t="s">
-        <v>145</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6">
+        <v>152</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>30</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>10000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>6</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>7</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" t="s">
         <v>151</v>
-      </c>
-      <c r="D7" t="s">
-        <v>145</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J7">
+        <v>152</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>30</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>10000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>6</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>7</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
         <v>151</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8">
+        <v>152</v>
+      </c>
+      <c r="K8">
         <v>10</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>30</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>10000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>6</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>7</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" t="s">
         <v>151</v>
-      </c>
-      <c r="D9" t="s">
-        <v>145</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J9">
+        <v>152</v>
+      </c>
+      <c r="K9">
         <v>10</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>30</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>10000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>6</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>7</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" t="s">
         <v>151</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10">
+        <v>152</v>
+      </c>
+      <c r="K10">
         <v>10</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>30</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>10000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>6</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>7</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3300,10 +3371,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3317,7 +3388,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3337,7 +3408,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3357,17 +3428,53 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781B89C5-0201-49AB-99EB-B647FFA1150D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -579,18 +585,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -601,157 +601,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -800,194 +656,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -995,253 +665,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1255,9 +683,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1281,66 +706,22 @@
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
+      <color rgb="FF0BF30B"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1598,22 +979,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1747,7 +1128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1761,7 +1142,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1775,7 +1156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1962,7 +1343,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2027,7 +1408,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2041,7 +1422,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2060,21 +1441,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2194,30 +1573,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2249,7 +1626,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="30" customHeight="1">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -2274,14 +1651,14 @@
       <c r="H2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>85</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2306,14 +1683,14 @@
       <c r="H3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>89</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="30" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2338,14 +1715,14 @@
       <c r="H4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>93</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2370,14 +1747,14 @@
       <c r="H5" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>98</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="48" customHeight="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2402,14 +1779,14 @@
       <c r="H6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>98</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:10">
+    <row r="7" spans="1:10" ht="30" customHeight="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2434,14 +1811,14 @@
       <c r="H7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>98</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:10">
+    <row r="8" spans="1:10" ht="30" customHeight="1">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2466,14 +1843,14 @@
       <c r="H8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>107</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:10">
+    <row r="9" spans="1:10" ht="30" customHeight="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2498,14 +1875,14 @@
       <c r="H9" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>110</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:10">
+    <row r="10" spans="1:10" ht="30" customHeight="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2530,14 +1907,14 @@
       <c r="H10" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>113</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:10">
+    <row r="11" spans="1:10" ht="30" customHeight="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2562,14 +1939,14 @@
       <c r="H11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>116</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:10">
+    <row r="12" spans="1:10" ht="30" customHeight="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2594,14 +1971,14 @@
       <c r="H12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:10">
+    <row r="13" spans="1:10" ht="30" customHeight="1">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2626,14 +2003,14 @@
       <c r="H13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="11" t="s">
         <v>125</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:10">
+    <row r="14" spans="1:10" ht="30" customHeight="1">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2658,14 +2035,14 @@
       <c r="H14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
         <v>125</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" spans="1:10" ht="30" customHeight="1">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2690,18 +2067,18 @@
       <c r="H15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:10">
+    <row r="16" spans="1:10" ht="30" customHeight="1">
       <c r="A16" s="3">
         <v>14</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2719,18 +2096,18 @@
       <c r="H16" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>98</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:9">
+    <row r="17" spans="1:9" ht="30" customHeight="1">
       <c r="A17" s="3">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -2748,15 +2125,15 @@
       <c r="H17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:9">
+    <row r="18" spans="1:9" ht="30" customHeight="1">
       <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2774,35 +2151,33 @@
       <c r="H18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
-    <col min="15" max="15" width="12.7083333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2852,7 +2227,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2896,7 +2271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2940,7 +2315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3268,22 +2643,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3368,6 +2741,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC90EF8-8192-465A-B5AC-1877F2A0AEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId2"/>
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
-    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId5"/>
-    <sheet name="PlacingConditions" sheetId="6" r:id="rId6"/>
+    <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
+    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="176">
   <si>
     <t>ID</t>
   </si>
@@ -514,18 +518,6 @@
     <t>杂谈回成功事件</t>
   </si>
   <si>
-    <t>进阶唱歌练习</t>
-  </si>
-  <si>
-    <t>歌力+60</t>
-  </si>
-  <si>
-    <t>进阶游戏练习</t>
-  </si>
-  <si>
-    <t>进阶杂谈练习</t>
-  </si>
-  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -602,23 +594,47 @@
   </si>
   <si>
     <t xml:space="preserve"> TargetValue</t>
+  </si>
+  <si>
+    <t>VAttributePlacingCondition</t>
+  </si>
+  <si>
+    <t>CASingingAbility,200</t>
+  </si>
+  <si>
+    <t>VTimeOfDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>VDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>add coop level for goomba</t>
+  </si>
+  <si>
+    <t>VRaisingAddCoopValueEffect</t>
+  </si>
+  <si>
+    <t>UPGRADE level for goomba</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeCoopLevel</t>
+  </si>
+  <si>
+    <t>Upgrade Level for goomba</t>
+  </si>
+  <si>
+    <t>GoombaUpgradelv1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -629,157 +645,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -828,194 +706,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1023,251 +715,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1306,66 +756,22 @@
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
+      <color rgb="FF0BF30B"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1623,22 +1029,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1772,7 +1178,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1786,7 +1192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1800,7 +1206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1987,7 +1393,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2052,7 +1458,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2066,7 +1472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2083,23 +1489,52 @@
         <v>3</v>
       </c>
     </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2219,30 +1654,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="3" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2277,7 +1710,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
+    <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -2309,7 +1742,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
+    <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2341,7 +1774,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2373,7 +1806,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
+    <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2405,7 +1838,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:11">
+    <row r="6" spans="1:11" ht="48" customHeight="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2437,7 +1870,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2469,7 +1902,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:11">
+    <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2501,7 +1934,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:11">
+    <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2533,7 +1966,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:11">
+    <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -2565,7 +1998,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:11">
+    <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2597,7 +2030,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
+    <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2629,7 +2062,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:11">
+    <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2661,7 +2094,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2693,7 +2126,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2722,7 +2155,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:11">
+    <row r="16" spans="1:11" ht="30" customHeight="1">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2754,7 +2187,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:11">
+    <row r="17" spans="1:11" ht="30" customHeight="1">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2786,7 +2219,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:11">
+    <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2818,59 +2251,60 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
+    <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:2">
-      <c r="A20" s="3">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:2">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>174</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
-    <col min="10" max="10" width="16.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="10.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="15.8583333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="10.425" customWidth="1"/>
-    <col min="16" max="16" width="12.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2905,36 +2339,36 @@
         <v>81</v>
       </c>
       <c r="K1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" t="s">
+        <v>141</v>
+      </c>
+      <c r="M1" t="s">
+        <v>142</v>
+      </c>
+      <c r="N1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O1" t="s">
         <v>144</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>146</v>
       </c>
-      <c r="N1" t="s">
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
         <v>147</v>
-      </c>
-      <c r="O1" t="s">
-        <v>148</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" t="s">
-        <v>151</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2946,10 +2380,13 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
+      </c>
+      <c r="J2" t="s">
+        <v>72</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2967,18 +2404,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2990,10 +2427,10 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3011,18 +2448,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3034,10 +2471,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3060,16 +2497,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="s">
         <v>85</v>
@@ -3078,10 +2515,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3107,13 +2544,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3125,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3146,7 +2583,7 @@
         <v>7</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -3154,13 +2591,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3172,10 +2609,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3201,13 +2638,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3219,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3248,13 +2685,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3266,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -3287,7 +2724,7 @@
         <v>7</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3295,13 +2732,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3313,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -3339,22 +2776,87 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3371,10 +2873,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3388,7 +2890,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3408,7 +2910,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3428,7 +2930,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3439,42 +2941,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC90EF8-8192-465A-B5AC-1877F2A0AEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ABEAC9-B725-45BB-9E39-457E99B35C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId2"/>
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
-    <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
-    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
+    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId5"/>
+    <sheet name="PlacingConditions" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="207">
   <si>
     <t>ID</t>
   </si>
@@ -219,6 +219,24 @@
   </si>
   <si>
     <t>VRaisingAddSelectedFrom3Effect</t>
+  </si>
+  <si>
+    <t>进入结局</t>
+  </si>
+  <si>
+    <t>VRaisingEndingEffect</t>
+  </si>
+  <si>
+    <t>随机获得一个消耗品</t>
+  </si>
+  <si>
+    <t>选择一个消耗品获得</t>
+  </si>
+  <si>
+    <t>选择一张卡牌获得</t>
+  </si>
+  <si>
+    <t>随机获得一张卡牌</t>
   </si>
   <si>
     <t>M卡</t>
@@ -364,7 +382,7 @@
     <t>直播成功</t>
   </si>
   <si>
-    <t>#00B051</t>
+    <t>#D0CECE</t>
   </si>
   <si>
     <t>StreamSuccess</t>
@@ -373,37 +391,22 @@
     <t>直播失败</t>
   </si>
   <si>
-    <t>#00B052</t>
-  </si>
-  <si>
     <t>StreamFail</t>
   </si>
   <si>
     <t>昏厥</t>
   </si>
   <si>
-    <t>#00B053</t>
-  </si>
-  <si>
     <t>OuttaStamina</t>
   </si>
   <si>
-    <t>阶段开始</t>
-  </si>
-  <si>
-    <t>#00B054</t>
+    <t>第一阶段开始</t>
   </si>
   <si>
     <t>PhaseStart</t>
   </si>
   <si>
-    <t>阶段开始2</t>
-  </si>
-  <si>
-    <t>阶段开始3</t>
-  </si>
-  <si>
-    <t>#00B055</t>
+    <t>第二阶段开始</t>
   </si>
   <si>
     <t>PhaseStart2</t>
@@ -448,6 +451,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>粉丝</t>
     </r>
     <r>
@@ -518,6 +527,54 @@
     <t>杂谈回成功事件</t>
   </si>
   <si>
+    <t>进阶唱歌练习</t>
+  </si>
+  <si>
+    <t>歌力+100，获得一张卡</t>
+  </si>
+  <si>
+    <t>进阶游戏练习</t>
+  </si>
+  <si>
+    <t>游戏力+100，获得一张卡</t>
+  </si>
+  <si>
+    <t>进阶杂谈练习</t>
+  </si>
+  <si>
+    <t>杂谈力+100，获得一张卡</t>
+  </si>
+  <si>
+    <t>毕业1</t>
+  </si>
+  <si>
+    <t>第一阶段失败</t>
+  </si>
+  <si>
+    <t>Graduation_1</t>
+  </si>
+  <si>
+    <t>毕业2</t>
+  </si>
+  <si>
+    <t>第二阶段失败</t>
+  </si>
+  <si>
+    <t>Graduation_2</t>
+  </si>
+  <si>
+    <t>第三阶段开始</t>
+  </si>
+  <si>
+    <t>#D1CECE</t>
+  </si>
+  <si>
+    <t>结局阶段开始</t>
+  </si>
+  <si>
+    <t>#D2CECE</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -554,25 +611,64 @@
     <t>歌杂</t>
   </si>
   <si>
-    <t>Ending2</t>
-  </si>
-  <si>
-    <t>Stream3</t>
+    <t>主题歌回</t>
+  </si>
+  <si>
+    <t>第一阶段歌力</t>
+  </si>
+  <si>
+    <t>水友联动回</t>
+  </si>
+  <si>
+    <t>第一阶段游戏力</t>
+  </si>
+  <si>
+    <t>棉花糖回</t>
+  </si>
+  <si>
+    <t>第一阶段杂谈力</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第一阶段体力</t>
+  </si>
+  <si>
+    <t>耐久歌回</t>
+  </si>
+  <si>
+    <t>第二阶段歌力</t>
   </si>
   <si>
     <t>0, 2</t>
   </si>
   <si>
-    <t>Ending3</t>
-  </si>
-  <si>
-    <t>Ending4</t>
-  </si>
-  <si>
-    <t>Ending5</t>
-  </si>
-  <si>
-    <t>Ending6</t>
+    <t>段位挑战回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>#AB0581</t>
+  </si>
+  <si>
+    <t>故事会</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>#AB0582</t>
+  </si>
+  <si>
+    <t>冲舰回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>#AB0583</t>
   </si>
   <si>
     <t>NameOrID</t>
@@ -596,6 +692,27 @@
     <t xml:space="preserve"> TargetValue</t>
   </si>
   <si>
+    <t>VRaisingUpgradeCoopLevel</t>
+  </si>
+  <si>
+    <t>UPGRADE level for goomba</t>
+  </si>
+  <si>
+    <t>VRaisingAddCoopValueEffect</t>
+  </si>
+  <si>
+    <t>add coop level for goomba</t>
+  </si>
+  <si>
+    <t>Upgrade Level for goomba</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>GoombaUpgradelv1</t>
+  </si>
+  <si>
     <t>VAttributePlacingCondition</t>
   </si>
   <si>
@@ -606,31 +723,13 @@
   </si>
   <si>
     <t>VDayPlacingCondition</t>
-  </si>
-  <si>
-    <t>add coop level for goomba</t>
-  </si>
-  <si>
-    <t>VRaisingAddCoopValueEffect</t>
-  </si>
-  <si>
-    <t>UPGRADE level for goomba</t>
-  </si>
-  <si>
-    <t>VRaisingUpgradeCoopLevel</t>
-  </si>
-  <si>
-    <t>Upgrade Level for goomba</t>
-  </si>
-  <si>
-    <t>GoombaUpgradelv1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,14 +749,8 @@
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -696,6 +789,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE5FD1F"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -719,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -753,6 +852,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1035,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1494,16 +1596,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1511,12 +1610,61 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F28">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33">
         <v>0</v>
       </c>
     </row>
@@ -1559,13 +1707,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1573,13 +1721,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1587,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1601,13 +1749,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1615,13 +1763,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1629,13 +1777,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1643,13 +1791,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" customWidth="1"/>
@@ -1689,25 +1837,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
@@ -1715,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
@@ -1727,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G2" s="3">
         <v>10</v>
@@ -1736,10 +1884,10 @@
         <v>56</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -1747,10 +1895,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
@@ -1759,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -1768,10 +1916,10 @@
         <v>56</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -1779,10 +1927,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
@@ -1791,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3">
         <v>10</v>
@@ -1800,10 +1948,10 @@
         <v>56</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
@@ -1811,31 +1959,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="48" customHeight="1">
@@ -1843,31 +1991,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -1875,31 +2023,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -1907,31 +2055,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
@@ -1939,31 +2087,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>111</v>
+        <v>104</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
@@ -1971,31 +2119,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>114</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2003,31 +2151,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>117</v>
+        <v>104</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -2035,31 +2183,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>121</v>
+        <v>104</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -2067,31 +2215,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>126</v>
+        <v>104</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -2099,31 +2247,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3">
         <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>126</v>
+        <v>104</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -2131,28 +2279,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>133</v>
+        <v>104</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
@@ -2160,31 +2308,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -2192,31 +2340,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -2224,31 +2372,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -2256,39 +2404,247 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>174</v>
+        <v>141</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="3">
+        <v>20</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="3">
+        <v>20</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="3">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="30" customHeight="1">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="3">
         <v>1</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>175</v>
+      <c r="F26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2298,7 +2654,7 @@
     <col min="5" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="10.85546875" customWidth="1"/>
     <col min="13" max="13" width="15.85546875" customWidth="1"/>
@@ -2321,40 +2677,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="L1" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="M1" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="N1" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="O1" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2362,31 +2718,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J2" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2409,28 +2762,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2453,28 +2806,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2497,28 +2850,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2532,199 +2885,188 @@
       <c r="N5">
         <v>6</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <v>7</v>
       </c>
-      <c r="P5" s="4">
-        <v>-1</v>
-      </c>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M6">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
-      <c r="O6">
-        <v>7</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>154</v>
-      </c>
+      <c r="O6" s="3">
+        <v>20</v>
+      </c>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K7">
         <v>10</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M7">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N7">
         <v>6</v>
       </c>
-      <c r="O7">
-        <v>7</v>
-      </c>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
+      <c r="O7" s="3">
+        <v>20</v>
+      </c>
+      <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N8">
         <v>6</v>
       </c>
-      <c r="O8">
-        <v>7</v>
-      </c>
-      <c r="P8" s="4">
-        <v>-1</v>
-      </c>
+      <c r="O8" s="3">
+        <v>20</v>
+      </c>
+      <c r="P8" s="4"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N9">
         <v>6</v>
       </c>
       <c r="O9">
-        <v>7</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2732,37 +3074,37 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10">
-        <v>30</v>
+        <v>9000</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -2770,8 +3112,136 @@
       <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11">
+        <v>9000</v>
+      </c>
+      <c r="M11">
+        <v>80</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K12">
+        <v>12</v>
+      </c>
+      <c r="L12">
+        <v>9000</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>164</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K13">
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>9000</v>
+      </c>
+      <c r="M13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2780,73 +3250,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -2873,10 +3276,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="F1" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2890,7 +3293,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2910,7 +3313,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2930,16 +3333,83 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ABEAC9-B725-45BB-9E39-457E99B35C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A61D548-D8F1-4F0A-B678-F410AEB27FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="207">
   <si>
     <t>ID</t>
   </si>
@@ -1612,6 +1612,12 @@
       <c r="B28" t="s">
         <v>63</v>
       </c>
+      <c r="C28" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
@@ -1620,6 +1626,12 @@
       <c r="B29" t="s">
         <v>64</v>
       </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
@@ -1628,6 +1640,12 @@
       <c r="B30" t="s">
         <v>65</v>
       </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
@@ -1635,6 +1653,12 @@
       </c>
       <c r="B31" t="s">
         <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2644,7 +2668,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -3200,6 +3224,12 @@
       <c r="M12">
         <v>80</v>
       </c>
+      <c r="N12">
+        <v>6</v>
+      </c>
+      <c r="O12">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -3238,10 +3268,11 @@
       <c r="M13">
         <v>80</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14">
-        <v>12</v>
+      <c r="N13">
+        <v>6</v>
+      </c>
+      <c r="O13">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A61D548-D8F1-4F0A-B678-F410AEB27FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737F683C-19EA-4ABE-BE9F-0D895B5AD088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="195">
   <si>
     <t>ID</t>
   </si>
@@ -217,6 +217,18 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
+    <t>进入结局</t>
+  </si>
+  <si>
+    <t>VRaisingEndingEffect</t>
+  </si>
+  <si>
+    <t>选择一张卡牌获得</t>
+  </si>
+  <si>
+    <t>随机获得一张卡牌</t>
+  </si>
+  <si>
     <t>M卡</t>
   </si>
   <si>
@@ -260,6 +272,9 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>Duration</t>
@@ -360,7 +375,7 @@
     <t>直播成功</t>
   </si>
   <si>
-    <t>#00B051</t>
+    <t>#D0CECE</t>
   </si>
   <si>
     <t>StreamSuccess</t>
@@ -369,37 +384,22 @@
     <t>直播失败</t>
   </si>
   <si>
-    <t>#00B052</t>
-  </si>
-  <si>
     <t>StreamFail</t>
   </si>
   <si>
     <t>昏厥</t>
   </si>
   <si>
-    <t>#00B053</t>
-  </si>
-  <si>
     <t>OuttaStamina</t>
   </si>
   <si>
-    <t>阶段开始</t>
-  </si>
-  <si>
-    <t>#00B054</t>
+    <t>第一阶段开始</t>
   </si>
   <si>
     <t>PhaseStart</t>
   </si>
   <si>
-    <t>阶段开始2</t>
-  </si>
-  <si>
-    <t>阶段开始3</t>
-  </si>
-  <si>
-    <t>#00B055</t>
+    <t>第二阶段开始</t>
   </si>
   <si>
     <t>PhaseStart2</t>
@@ -408,9 +408,9 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>金钱+60，体力-10
-金钱+30，获得一张卡，体力-10
-金钱+100，体力-15</t>
+    <t>金钱+60，获得一张满足条件的卡体力-10
+金钱+60，获得一张满足条件卡，体力-10
+金钱+60，获得一张满足条件的卡</t>
   </si>
   <si>
     <t>Work</t>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>粉丝</t>
     </r>
     <r>
@@ -517,15 +523,51 @@
     <t>进阶唱歌练习</t>
   </si>
   <si>
-    <t>歌力+60</t>
+    <t>歌力+100，获得一张卡</t>
   </si>
   <si>
     <t>进阶游戏练习</t>
   </si>
   <si>
+    <t>游戏力+100，获得一张卡</t>
+  </si>
+  <si>
     <t>进阶杂谈练习</t>
   </si>
   <si>
+    <t>杂谈力+100，获得一张卡</t>
+  </si>
+  <si>
+    <t>毕业1</t>
+  </si>
+  <si>
+    <t>第一阶段失败</t>
+  </si>
+  <si>
+    <t>Graduation_1</t>
+  </si>
+  <si>
+    <t>毕业2</t>
+  </si>
+  <si>
+    <t>第二阶段失败</t>
+  </si>
+  <si>
+    <t>Graduation_2</t>
+  </si>
+  <si>
+    <t>第三阶段开始</t>
+  </si>
+  <si>
+    <t>#D1CECE</t>
+  </si>
+  <si>
+    <t>结局阶段开始</t>
+  </si>
+  <si>
+    <t>#D2CECE</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -562,25 +604,64 @@
     <t>歌杂</t>
   </si>
   <si>
-    <t>Ending2</t>
-  </si>
-  <si>
-    <t>Stream3</t>
+    <t>主题歌回</t>
+  </si>
+  <si>
+    <t>第一阶段歌力</t>
+  </si>
+  <si>
+    <t>水友联动回</t>
+  </si>
+  <si>
+    <t>第一阶段游戏力</t>
+  </si>
+  <si>
+    <t>棉花糖回</t>
+  </si>
+  <si>
+    <t>第一阶段杂谈力</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第一阶段体力</t>
+  </si>
+  <si>
+    <t>耐久歌回</t>
+  </si>
+  <si>
+    <t>第二阶段歌力</t>
   </si>
   <si>
     <t>0, 2</t>
   </si>
   <si>
-    <t>Ending3</t>
-  </si>
-  <si>
-    <t>Ending4</t>
-  </si>
-  <si>
-    <t>Ending5</t>
-  </si>
-  <si>
-    <t>Ending6</t>
+    <t>段位挑战回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>#AB0581</t>
+  </si>
+  <si>
+    <t>故事会</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>#AB0582</t>
+  </si>
+  <si>
+    <t>冲舰回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>#AB0583</t>
   </si>
   <si>
     <t>NameOrID</t>
@@ -779,7 +860,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,6 +894,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1145,7 +1232,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1169,16 +1256,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1187,89 +1274,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1303,6 +1390,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1629,7 +1719,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2083,6 +2173,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2092,8 +2218,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2124,13 +2250,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2138,13 +2264,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2152,13 +2278,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2166,13 +2292,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2180,13 +2306,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2194,13 +2320,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2208,13 +2334,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2226,7 +2366,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
@@ -2256,25 +2396,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -2282,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
@@ -2294,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G2" s="3">
         <v>10</v>
@@ -2303,10 +2443,10 @@
         <v>56</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -2314,10 +2454,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
@@ -2326,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2335,10 +2475,10 @@
         <v>56</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -2346,10 +2486,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
@@ -2358,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3">
         <v>10</v>
@@ -2367,10 +2507,10 @@
         <v>56</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -2378,31 +2518,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:11">
@@ -2410,31 +2550,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -2442,31 +2582,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -2474,31 +2614,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -2506,31 +2646,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -2538,31 +2678,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>114</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -2570,31 +2710,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>117</v>
+        <v>103</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -2602,28 +2742,28 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>121</v>
+        <v>103</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>122</v>
@@ -2646,15 +2786,15 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>126</v>
       </c>
       <c r="K13" s="3" t="s">
@@ -2678,15 +2818,15 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3">
         <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>126</v>
       </c>
       <c r="K14" s="3" t="s">
@@ -2704,21 +2844,21 @@
         <v>132</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2733,22 +2873,22 @@
         <v>135</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>136</v>
@@ -2765,22 +2905,22 @@
         <v>135</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>138</v>
@@ -2797,28 +2937,28 @@
         <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:3">
+    <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2828,21 +2968,203 @@
       <c r="C19" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:2">
+      <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="3">
+        <v>20</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:2">
+      <c r="C20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="3">
+        <v>20</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="3">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2854,7 +3176,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.425" customWidth="1"/>
@@ -2887,40 +3209,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="L1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="M1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="N1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="O1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2928,28 +3250,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2972,28 +3294,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3016,28 +3338,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3060,28 +3382,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3095,199 +3417,188 @@
       <c r="N5">
         <v>6</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <v>7</v>
       </c>
-      <c r="P5" s="4">
-        <v>-1</v>
-      </c>
+      <c r="P5" s="4"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M6">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
-      <c r="O6">
-        <v>7</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>158</v>
-      </c>
+      <c r="O6" s="3">
+        <v>20</v>
+      </c>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K7">
         <v>10</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M7">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N7">
         <v>6</v>
       </c>
-      <c r="O7">
-        <v>7</v>
-      </c>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
+      <c r="O7" s="3">
+        <v>20</v>
+      </c>
+      <c r="P7" s="4"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N8">
         <v>6</v>
       </c>
-      <c r="O8">
-        <v>7</v>
-      </c>
-      <c r="P8" s="4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="O8" s="3">
+        <v>20</v>
+      </c>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>30</v>
+        <v>5000</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="N9">
         <v>6</v>
       </c>
       <c r="O9">
-        <v>7</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>158</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3295,37 +3606,37 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10">
-        <v>30</v>
+        <v>9000</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>6</v>
@@ -3333,8 +3644,136 @@
       <c r="O10">
         <v>7</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K11">
+        <v>12</v>
+      </c>
+      <c r="L11">
+        <v>9000</v>
+      </c>
+      <c r="M11">
+        <v>80</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K12">
+        <v>12</v>
+      </c>
+      <c r="L12">
+        <v>9000</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K13">
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <v>9000</v>
+      </c>
+      <c r="M13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3371,10 +3810,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="F1" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3388,7 +3827,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3408,7 +3847,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3428,13 +3867,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3461,16 +3900,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" firstSheet="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId2"/>
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
-    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId5"/>
-    <sheet name="PlacingConditions" sheetId="6" r:id="rId6"/>
+    <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
+    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="244">
   <si>
     <t>ID</t>
   </si>
@@ -217,16 +217,19 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
+    <t>0.5,0.3,0.1,0.1,0.05,0.01</t>
+  </si>
+  <si>
     <t>进入结局</t>
   </si>
   <si>
     <t>VRaisingEndingEffect</t>
   </si>
   <si>
-    <t>选择一张卡牌获得</t>
-  </si>
-  <si>
-    <t>随机获得一张卡牌</t>
+    <t>选择一张A卡牌获得</t>
+  </si>
+  <si>
+    <t>选择一张M卡牌获得</t>
   </si>
   <si>
     <t>M卡</t>
@@ -254,15 +257,6 @@
   </si>
   <si>
     <t>Common</t>
-  </si>
-  <si>
-    <t>Pool</t>
-  </si>
-  <si>
-    <t>VCardPoolCondition</t>
-  </si>
-  <si>
-    <t>0,1,2</t>
   </si>
   <si>
     <t>LiveType</t>
@@ -562,12 +556,18 @@
     <t>#D1CECE</t>
   </si>
   <si>
+    <t>PhaseStart3</t>
+  </si>
+  <si>
     <t>结局阶段开始</t>
   </si>
   <si>
     <t>#D2CECE</t>
   </si>
   <si>
+    <t>PhaseStart4</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -577,6 +577,12 @@
     <t>InitialViewers</t>
   </si>
   <si>
+    <t>MainAbility</t>
+  </si>
+  <si>
+    <t>AbilityTurns</t>
+  </si>
+  <si>
     <t>SuccessEvent</t>
   </si>
   <si>
@@ -595,73 +601,223 @@
     <t>#AB0580</t>
   </si>
   <si>
+    <t>4,2,2</t>
+  </si>
+  <si>
     <t>游戏回</t>
   </si>
   <si>
+    <t>2,4,2</t>
+  </si>
+  <si>
     <t>杂谈回</t>
   </si>
   <si>
+    <t>2,2,4</t>
+  </si>
+  <si>
     <t>歌杂</t>
   </si>
   <si>
+    <t>4,2,4</t>
+  </si>
+  <si>
     <t>主题歌回</t>
   </si>
   <si>
     <t>第一阶段歌力</t>
   </si>
   <si>
-    <t>水友联动回</t>
+    <t>5,2,3</t>
+  </si>
+  <si>
+    <t>水友联动游戏回</t>
   </si>
   <si>
     <t>第一阶段游戏力</t>
   </si>
   <si>
+    <t>2,5,3</t>
+  </si>
+  <si>
     <t>棉花糖回</t>
   </si>
   <si>
     <t>第一阶段杂谈力</t>
   </si>
   <si>
+    <t>2,2,6</t>
+  </si>
+  <si>
+    <t>水友歌回</t>
+  </si>
+  <si>
+    <t>第二阶段歌力</t>
+  </si>
+  <si>
+    <t>6,3,3</t>
+  </si>
+  <si>
+    <t>段位挑战回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>#AB0581</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>#AB0582</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>#AB0583</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>4,3,5</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
     <t>健身环挑战回</t>
   </si>
   <si>
-    <t>第一阶段体力</t>
-  </si>
-  <si>
-    <t>耐久歌回</t>
-  </si>
-  <si>
-    <t>第二阶段歌力</t>
-  </si>
-  <si>
-    <t>0, 2</t>
-  </si>
-  <si>
-    <t>段位挑战回</t>
-  </si>
-  <si>
-    <t>第二阶段游戏</t>
-  </si>
-  <si>
-    <t>#AB0581</t>
-  </si>
-  <si>
-    <t>故事会</t>
-  </si>
-  <si>
-    <t>第二阶段杂谈</t>
-  </si>
-  <si>
-    <t>#AB0582</t>
-  </si>
-  <si>
-    <t>冲舰回</t>
-  </si>
-  <si>
-    <t>第二阶段营收</t>
-  </si>
-  <si>
-    <t>#AB0583</t>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>光暗歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>4,4,7</t>
+  </si>
+  <si>
+    <t>速通挑战赛</t>
+  </si>
+  <si>
+    <t>游戏力加成结局</t>
+  </si>
+  <si>
+    <t>4,7,4</t>
+  </si>
+  <si>
+    <t>清楚聊天室</t>
+  </si>
+  <si>
+    <t>杂谈力加成结局</t>
+  </si>
+  <si>
+    <t>人头麦回</t>
+  </si>
+  <si>
+    <t>营收加成结局</t>
+  </si>
+  <si>
+    <t>5,4,6</t>
+  </si>
+  <si>
+    <t>健身环耐久回</t>
+  </si>
+  <si>
+    <t>体力加成结局</t>
+  </si>
+  <si>
+    <t>4,6,5</t>
+  </si>
+  <si>
+    <t>百舰回</t>
+  </si>
+  <si>
+    <t>舰长加成结局</t>
+  </si>
+  <si>
+    <t>6,4,5</t>
+  </si>
+  <si>
+    <t>新衣回嘉宾</t>
+  </si>
+  <si>
+    <t>好感度加成结局</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>一阶歌力向直播</t>
+  </si>
+  <si>
+    <t>一阶游戏力直播</t>
+  </si>
+  <si>
+    <t>一阶杂谈直播</t>
+  </si>
+  <si>
+    <t>二阶歌力向直播</t>
+  </si>
+  <si>
+    <t>二阶游戏力直播</t>
+  </si>
+  <si>
+    <t>二阶杂谈直播</t>
+  </si>
+  <si>
+    <t>才艺回</t>
+  </si>
+  <si>
+    <t>二阶营收直播</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TargetValue</t>
   </si>
   <si>
     <t>NameOrID</t>
@@ -674,15 +830,6 @@
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TargetValue</t>
   </si>
 </sst>
 </file>
@@ -1358,12 +1505,12 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2156,7 +2303,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2170,7 +2317,10 @@
         <v>60</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2178,35 +2328,47 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>60</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2218,8 +2380,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2250,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2264,13 +2426,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2278,13 +2440,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
         <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2292,13 +2454,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2306,13 +2468,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2320,13 +2482,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2334,27 +2496,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
         <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2369,801 +2517,807 @@
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="3" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="10.425" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.7083333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.425" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" style="2" customWidth="1"/>
+    <col min="10" max="11" width="16.8583333333333" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="2">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="K2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="F3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="2">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="3">
+      <c r="I3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:11">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="2">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="2">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="2">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="I21" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="3">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:11">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="3">
-        <v>20</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="3">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="3">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="3">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="3">
-        <v>20</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="3">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="3">
-        <v>20</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="3">
-        <v>20</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="3">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="K22" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="3" t="s">
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="3">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="3" t="s">
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="C24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="3">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="K24" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="11" t="s">
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:9">
-      <c r="A25" s="3">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="11" t="s">
+      <c r="K25" s="2" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3176,26 +3330,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
+    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
     <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
     <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
     <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
     <col min="5" max="6" width="11.425" customWidth="1"/>
     <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
-    <col min="10" max="10" width="16.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="10.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="15.8583333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="10.425" customWidth="1"/>
-    <col min="16" max="16" width="12.7083333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.15" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="3.26666666666667" customWidth="1"/>
+    <col min="12" max="12" width="6.41666666666667" customWidth="1"/>
+    <col min="13" max="13" width="11.75" customWidth="1"/>
+    <col min="14" max="14" width="10.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="10.6666666666667" customWidth="1"/>
+    <col min="16" max="16" width="11.9166666666667" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
+    <col min="18" max="18" width="10.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3209,22 +3365,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>84</v>
-      </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>86</v>
       </c>
       <c r="K1" t="s">
         <v>156</v>
@@ -3241,37 +3397,43 @@
       <c r="O1" t="s">
         <v>160</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="Q1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -3282,40 +3444,46 @@
       <c r="M2">
         <v>10</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>167</v>
+      </c>
+      <c r="P2" s="2">
         <v>14</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3327,39 +3495,45 @@
         <v>10</v>
       </c>
       <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>169</v>
+      </c>
+      <c r="P3">
         <v>6</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>163</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3371,39 +3545,45 @@
         <v>10</v>
       </c>
       <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>171</v>
+      </c>
+      <c r="P4">
         <v>6</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3415,40 +3595,46 @@
         <v>25</v>
       </c>
       <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>173</v>
+      </c>
+      <c r="P5">
         <v>6</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="2">
         <v>7</v>
       </c>
-      <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3460,40 +3646,46 @@
         <v>50</v>
       </c>
       <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>176</v>
+      </c>
+      <c r="P6">
         <v>6</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="2">
         <v>20</v>
       </c>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="R6" s="4"/>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3505,40 +3697,46 @@
         <v>50</v>
       </c>
       <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>179</v>
+      </c>
+      <c r="P7">
         <v>6</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="2">
         <v>20</v>
       </c>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>163</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3550,230 +3748,1119 @@
         <v>50</v>
       </c>
       <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>182</v>
+      </c>
+      <c r="P8">
         <v>6</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="2">
         <v>20</v>
       </c>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>185</v>
+      </c>
+      <c r="P9">
         <v>6</v>
       </c>
-      <c r="O9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>7</v>
+      </c>
+      <c r="R9" s="4"/>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>163</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="K10">
         <v>12</v>
       </c>
       <c r="L10">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10">
         <v>6</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>7</v>
       </c>
-      <c r="P10" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="R10" s="4"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="M11">
         <v>80</v>
       </c>
       <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>193</v>
+      </c>
+      <c r="P11">
         <v>6</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>7</v>
       </c>
-      <c r="P11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>184</v>
+        <v>165</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="K12">
         <v>12</v>
       </c>
       <c r="L12">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="M12">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>197</v>
+      </c>
+      <c r="P12">
+        <v>6</v>
+      </c>
+      <c r="Q12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>187</v>
+        <v>165</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="K13">
         <v>12</v>
       </c>
       <c r="L13">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="M13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>193</v>
+      </c>
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
+      <c r="L14">
+        <v>20000</v>
+      </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>202</v>
+      </c>
+      <c r="P14">
+        <v>6</v>
+      </c>
+      <c r="Q14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
+      <c r="L15">
+        <v>20000</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>205</v>
+      </c>
+      <c r="P15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16">
+        <v>12</v>
+      </c>
+      <c r="L16">
+        <v>20000</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16">
+        <v>6</v>
+      </c>
+      <c r="Q16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K17">
+        <v>15</v>
+      </c>
+      <c r="L17">
+        <v>40000</v>
+      </c>
+      <c r="M17">
+        <v>130</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>211</v>
+      </c>
+      <c r="P17">
+        <v>6</v>
+      </c>
+      <c r="Q17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>165</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K18">
+        <v>15</v>
+      </c>
+      <c r="L18">
+        <v>40000</v>
+      </c>
+      <c r="M18">
+        <v>130</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>214</v>
+      </c>
+      <c r="P18">
+        <v>6</v>
+      </c>
+      <c r="Q18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>165</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19">
+        <v>15</v>
+      </c>
+      <c r="L19">
+        <v>40000</v>
+      </c>
+      <c r="M19">
+        <v>130</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>211</v>
+      </c>
+      <c r="P19">
+        <v>6</v>
+      </c>
+      <c r="Q19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K20">
+        <v>15</v>
+      </c>
+      <c r="L20">
+        <v>40000</v>
+      </c>
+      <c r="M20">
+        <v>130</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20" t="s">
+        <v>219</v>
+      </c>
+      <c r="P20">
+        <v>6</v>
+      </c>
+      <c r="Q20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21">
+        <v>15</v>
+      </c>
+      <c r="L21">
+        <v>40000</v>
+      </c>
+      <c r="M21">
+        <v>130</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>222</v>
+      </c>
+      <c r="P21">
+        <v>6</v>
+      </c>
+      <c r="Q21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K22">
+        <v>15</v>
+      </c>
+      <c r="L22">
+        <v>40000</v>
+      </c>
+      <c r="M22">
+        <v>130</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>225</v>
+      </c>
+      <c r="P22">
+        <v>6</v>
+      </c>
+      <c r="Q22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23">
+        <v>15</v>
+      </c>
+      <c r="L23">
+        <v>40000</v>
+      </c>
+      <c r="M23">
+        <v>130</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>228</v>
+      </c>
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>165</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+      <c r="L24">
+        <v>7000</v>
+      </c>
+      <c r="M24">
+        <v>30</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>176</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>7000</v>
+      </c>
+      <c r="M25">
+        <v>30</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25" t="s">
+        <v>179</v>
+      </c>
+      <c r="P25">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K26">
+        <v>10</v>
+      </c>
+      <c r="L26">
+        <v>7000</v>
+      </c>
+      <c r="M26">
+        <v>30</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>182</v>
+      </c>
+      <c r="P26">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K27">
+        <v>12</v>
+      </c>
+      <c r="L27">
+        <v>14000</v>
+      </c>
+      <c r="M27">
+        <v>50</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>185</v>
+      </c>
+      <c r="P27">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>165</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28">
+        <v>12</v>
+      </c>
+      <c r="L28">
+        <v>14000</v>
+      </c>
+      <c r="M28">
+        <v>50</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>189</v>
+      </c>
+      <c r="P28">
+        <v>6</v>
+      </c>
+      <c r="Q28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" t="s">
+        <v>165</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>165</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K29">
+        <v>12</v>
+      </c>
+      <c r="L29">
+        <v>14000</v>
+      </c>
+      <c r="M29">
+        <v>50</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>193</v>
+      </c>
+      <c r="P29">
+        <v>6</v>
+      </c>
+      <c r="Q29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30">
+        <v>20</v>
+      </c>
+      <c r="H30" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K30">
+        <v>12</v>
+      </c>
+      <c r="L30">
+        <v>14000</v>
+      </c>
+      <c r="M30">
+        <v>50</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
+        <v>197</v>
+      </c>
+      <c r="P30">
+        <v>6</v>
+      </c>
+      <c r="Q30">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3783,6 +4870,42 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
+    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F4"/>
@@ -3810,10 +4933,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>188</v>
+        <v>240</v>
       </c>
       <c r="F1" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3827,7 +4950,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3847,7 +4970,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3867,53 +4990,17 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="237">
   <si>
     <t>ID</t>
   </si>
@@ -109,12 +109,6 @@
     <t>VRaisingModifyScheduleEffect</t>
   </si>
   <si>
-    <t>AddRandomM</t>
-  </si>
-  <si>
-    <t>VRaisingAddRandomCardEffect</t>
-  </si>
-  <si>
     <t>歌力提升率+X%</t>
   </si>
   <si>
@@ -217,7 +211,7 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
-    <t>0.5,0.3,0.1,0.1,0.05,0.01</t>
+    <t>0.5,0.3,0.1,0.1,0.5,0.1</t>
   </si>
   <si>
     <t>进入结局</t>
@@ -302,9 +296,6 @@
   </si>
   <si>
     <t>#FF2160</t>
-  </si>
-  <si>
-    <t>AddSinging</t>
   </si>
   <si>
     <t>游戏练习</t>
@@ -390,13 +381,7 @@
     <t>第一阶段开始</t>
   </si>
   <si>
-    <t>PhaseStart</t>
-  </si>
-  <si>
     <t>第二阶段开始</t>
-  </si>
-  <si>
-    <t>PhaseStart2</t>
   </si>
   <si>
     <t>兼职</t>
@@ -556,16 +541,10 @@
     <t>#D1CECE</t>
   </si>
   <si>
-    <t>PhaseStart3</t>
-  </si>
-  <si>
     <t>结局阶段开始</t>
   </si>
   <si>
     <t>#D2CECE</t>
-  </si>
-  <si>
-    <t>PhaseStart4</t>
   </si>
   <si>
     <t>TurnCount</t>
@@ -2037,21 +2016,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" customFormat="1" spans="1:4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2059,16 +2035,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2076,16 +2052,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2093,16 +2069,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2110,16 +2086,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2127,16 +2103,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2144,16 +2120,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2161,16 +2137,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2178,16 +2154,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2195,16 +2171,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2212,16 +2188,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2229,13 +2205,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2243,13 +2219,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2260,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2277,16 +2253,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
         <v>53</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" t="s">
         <v>54</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2294,13 +2270,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2308,19 +2284,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2328,13 +2304,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2342,16 +2318,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2359,16 +2335,16 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2412,13 +2388,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2426,13 +2402,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2440,13 +2416,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2454,13 +2430,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2468,13 +2444,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
         <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2482,13 +2458,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2496,13 +2472,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2544,25 +2520,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="J1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -2570,31 +2546,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G2" s="2">
         <v>10</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -2602,31 +2578,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G3" s="2">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -2634,31 +2610,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4" s="2">
         <v>10</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -2666,31 +2642,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:11">
@@ -2698,31 +2674,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -2730,31 +2706,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -2762,31 +2738,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -2794,31 +2770,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -2826,31 +2802,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -2858,31 +2834,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -2890,31 +2866,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -2922,31 +2898,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -2954,31 +2930,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -2986,28 +2962,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:11">
@@ -3015,31 +2991,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -3047,31 +3023,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -3079,31 +3055,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -3111,28 +3087,28 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -3140,28 +3116,28 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2">
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -3169,28 +3145,28 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2">
         <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -3198,31 +3174,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -3230,31 +3206,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -3262,31 +3238,31 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:11">
@@ -3294,31 +3270,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3365,46 +3341,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" t="s">
-        <v>84</v>
-      </c>
       <c r="K1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="L1" t="s">
-        <v>157</v>
-      </c>
-      <c r="M1" t="s">
-        <v>158</v>
-      </c>
-      <c r="N1" t="s">
-        <v>159</v>
-      </c>
-      <c r="O1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>162</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -3412,28 +3388,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G2">
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -3448,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="P2" s="2">
         <v>14</v>
@@ -3462,28 +3438,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G3">
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3498,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -3512,28 +3488,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3548,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -3562,28 +3538,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3598,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -3613,28 +3589,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3649,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3664,28 +3640,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3700,7 +3676,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3715,28 +3691,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3751,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3766,28 +3742,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3802,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3817,28 +3793,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3853,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3868,28 +3844,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3904,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3918,28 +3894,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3954,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3968,28 +3944,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -4004,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -4018,28 +3994,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4054,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -4068,28 +4044,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -4104,7 +4080,7 @@
         <v>2</v>
       </c>
       <c r="O15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -4118,28 +4094,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -4154,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -4168,28 +4144,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -4204,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -4218,28 +4194,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -4254,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -4268,28 +4244,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -4304,7 +4280,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -4318,28 +4294,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -4354,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="O20" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -4368,28 +4344,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -4404,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -4418,28 +4394,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -4454,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -4468,28 +4444,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4504,7 +4480,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -4518,28 +4494,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -4554,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -4568,28 +4544,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G25">
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -4604,7 +4580,7 @@
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -4618,28 +4594,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -4654,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -4668,28 +4644,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K27">
         <v>12</v>
@@ -4704,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="P27">
         <v>6</v>
@@ -4718,28 +4694,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G28">
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K28">
         <v>12</v>
@@ -4754,7 +4730,7 @@
         <v>2</v>
       </c>
       <c r="O28" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -4768,28 +4744,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G29">
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K29">
         <v>12</v>
@@ -4804,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -4818,28 +4794,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C30" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D30" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G30">
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K30">
         <v>12</v>
@@ -4854,7 +4830,7 @@
         <v>2</v>
       </c>
       <c r="O30" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="P30">
         <v>6</v>
@@ -4887,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4933,10 +4909,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4950,7 +4926,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4970,7 +4946,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4990,13 +4966,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="238">
   <si>
     <t>ID</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>第一阶段开始</t>
+  </si>
+  <si>
+    <t>test1</t>
   </si>
   <si>
     <t>第二阶段开始</t>
@@ -2857,8 +2860,8 @@
       <c r="I11" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="2">
-        <v>0</v>
+      <c r="K11" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -2866,10 +2869,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>98</v>
@@ -2898,13 +2901,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -2919,10 +2922,10 @@
         <v>98</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -2930,13 +2933,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -2951,10 +2954,10 @@
         <v>98</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -2962,10 +2965,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>98</v>
@@ -2983,7 +2986,7 @@
         <v>98</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:11">
@@ -2991,10 +2994,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>98</v>
@@ -3015,7 +3018,7 @@
         <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -3023,10 +3026,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>98</v>
@@ -3047,7 +3050,7 @@
         <v>108</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -3055,10 +3058,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>98</v>
@@ -3079,7 +3082,7 @@
         <v>108</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -3087,10 +3090,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>54</v>
@@ -3116,10 +3119,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>54</v>
@@ -3145,10 +3148,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>54</v>
@@ -3174,10 +3177,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>98</v>
@@ -3198,7 +3201,7 @@
         <v>108</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -3206,10 +3209,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>98</v>
@@ -3230,7 +3233,7 @@
         <v>108</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -3238,10 +3241,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>98</v>
@@ -3259,7 +3262,7 @@
         <v>98</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
@@ -3270,10 +3273,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>98</v>
@@ -3291,7 +3294,7 @@
         <v>98</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
@@ -3359,28 +3362,28 @@
         <v>82</v>
       </c>
       <c r="K1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -3388,13 +3391,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3406,10 +3409,10 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -3424,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P2" s="2">
         <v>14</v>
@@ -3438,13 +3441,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3456,10 +3459,10 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3474,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -3488,13 +3491,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3506,10 +3509,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3524,7 +3527,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -3538,13 +3541,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3556,10 +3559,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3574,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -3589,13 +3592,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3607,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3625,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3640,13 +3643,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3658,10 +3661,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3676,7 +3679,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3691,13 +3694,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3709,10 +3712,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3727,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3742,13 +3745,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3760,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3778,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3793,13 +3796,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3811,10 +3814,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3829,7 +3832,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3844,13 +3847,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3862,10 +3865,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3880,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3894,13 +3897,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3912,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3930,7 +3933,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3944,13 +3947,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3962,10 +3965,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3980,7 +3983,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3994,13 +3997,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4012,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4030,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -4044,13 +4047,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4062,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -4080,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="O15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -4094,13 +4097,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -4112,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -4130,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -4144,13 +4147,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4162,10 +4165,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -4180,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -4194,13 +4197,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -4212,10 +4215,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -4230,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -4244,13 +4247,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -4262,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -4280,7 +4283,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -4294,13 +4297,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -4312,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -4330,7 +4333,7 @@
         <v>2</v>
       </c>
       <c r="O20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -4344,13 +4347,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -4362,10 +4365,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -4380,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -4394,13 +4397,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -4412,10 +4415,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -4430,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -4444,13 +4447,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -4462,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4480,7 +4483,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -4494,13 +4497,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -4512,10 +4515,10 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -4530,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -4544,13 +4547,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -4562,10 +4565,10 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -4580,7 +4583,7 @@
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -4594,13 +4597,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -4612,10 +4615,10 @@
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -4630,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -4644,13 +4647,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -4662,10 +4665,10 @@
         <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K27">
         <v>12</v>
@@ -4680,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P27">
         <v>6</v>
@@ -4694,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -4712,10 +4715,10 @@
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K28">
         <v>12</v>
@@ -4730,7 +4733,7 @@
         <v>2</v>
       </c>
       <c r="O28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -4744,13 +4747,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -4762,10 +4765,10 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K29">
         <v>12</v>
@@ -4780,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -4794,13 +4797,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -4812,10 +4815,10 @@
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K30">
         <v>12</v>
@@ -4830,7 +4833,7 @@
         <v>2</v>
       </c>
       <c r="O30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P30">
         <v>6</v>
@@ -4863,16 +4866,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -4909,10 +4912,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4926,7 +4929,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4946,7 +4949,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4966,7 +4969,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E4">
         <v>5</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="11950" windowHeight="10480" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -2989,7 +2989,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:11">
+    <row r="16" ht="42" customHeight="1" spans="1:11">
       <c r="A16" s="2">
         <v>14</v>
       </c>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="10480" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="12110" windowHeight="19120" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="239">
   <si>
     <t>ID</t>
   </si>
@@ -381,10 +381,13 @@
     <t>第一阶段开始</t>
   </si>
   <si>
-    <t>test1</t>
+    <t>phase1</t>
   </si>
   <si>
     <t>第二阶段开始</t>
+  </si>
+  <si>
+    <t>phase2</t>
   </si>
   <si>
     <t>兼职</t>
@@ -640,85 +643,85 @@
     <t>6,3,3</t>
   </si>
   <si>
+    <t>水友游戏回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>#AB0581</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>#AB0582</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>#AB0583</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>4,3,5</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>光暗歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>4,4,7</t>
+  </si>
+  <si>
     <t>段位挑战回</t>
-  </si>
-  <si>
-    <t>第二阶段游戏</t>
-  </si>
-  <si>
-    <t>#AB0581</t>
-  </si>
-  <si>
-    <t>3,6,3</t>
-  </si>
-  <si>
-    <t>视频鉴赏回</t>
-  </si>
-  <si>
-    <t>第二阶段杂谈</t>
-  </si>
-  <si>
-    <t>#AB0582</t>
-  </si>
-  <si>
-    <t>3,3,6</t>
-  </si>
-  <si>
-    <t>代抽回</t>
-  </si>
-  <si>
-    <t>第二阶段营收</t>
-  </si>
-  <si>
-    <t>#AB0583</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>水友投稿回</t>
-  </si>
-  <si>
-    <t>第三阶段粉丝</t>
-  </si>
-  <si>
-    <t>生日回</t>
-  </si>
-  <si>
-    <t>第三阶段舰长</t>
-  </si>
-  <si>
-    <t>4,3,5</t>
-  </si>
-  <si>
-    <t>粉丝礼物回</t>
-  </si>
-  <si>
-    <t>第三阶段营收</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>健身环挑战回</t>
-  </si>
-  <si>
-    <t>第三阶段体力</t>
-  </si>
-  <si>
-    <t>3,5,4</t>
-  </si>
-  <si>
-    <t>光暗歌会</t>
-  </si>
-  <si>
-    <t>歌力加成结局</t>
-  </si>
-  <si>
-    <t>4,4,7</t>
-  </si>
-  <si>
-    <t>速通挑战赛</t>
   </si>
   <si>
     <t>游戏力加成结局</t>
@@ -2892,8 +2895,8 @@
       <c r="I12" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="K12" s="2">
-        <v>0</v>
+      <c r="K12" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -2901,13 +2904,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -2922,10 +2925,10 @@
         <v>98</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -2933,13 +2936,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -2954,10 +2957,10 @@
         <v>98</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -2965,10 +2968,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>98</v>
@@ -2986,7 +2989,7 @@
         <v>98</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -2994,10 +2997,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>98</v>
@@ -3018,7 +3021,7 @@
         <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -3026,10 +3029,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>98</v>
@@ -3050,7 +3053,7 @@
         <v>108</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -3058,10 +3061,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>98</v>
@@ -3082,7 +3085,7 @@
         <v>108</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -3090,10 +3093,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>54</v>
@@ -3119,10 +3122,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>54</v>
@@ -3148,10 +3151,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>54</v>
@@ -3177,10 +3180,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>98</v>
@@ -3201,7 +3204,7 @@
         <v>108</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -3209,10 +3212,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>98</v>
@@ -3233,7 +3236,7 @@
         <v>108</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -3241,10 +3244,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>98</v>
@@ -3262,7 +3265,7 @@
         <v>98</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
@@ -3273,10 +3276,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>98</v>
@@ -3294,7 +3297,7 @@
         <v>98</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
@@ -3362,28 +3365,28 @@
         <v>82</v>
       </c>
       <c r="K1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -3391,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3409,10 +3412,10 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -3427,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P2" s="2">
         <v>14</v>
@@ -3441,13 +3444,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3459,10 +3462,10 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3477,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -3491,13 +3494,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3509,10 +3512,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3527,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -3541,13 +3544,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3559,10 +3562,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3577,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -3592,13 +3595,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3610,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3628,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3643,13 +3646,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3661,10 +3664,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3679,7 +3682,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3694,13 +3697,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3712,10 +3715,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3730,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3745,13 +3748,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3763,10 +3766,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3781,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3796,13 +3799,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3814,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3832,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3847,13 +3850,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3865,10 +3868,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3883,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3897,13 +3900,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3915,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3933,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3947,13 +3950,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3965,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3983,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3997,13 +4000,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4015,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4033,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -4047,13 +4050,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4065,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -4083,7 +4086,7 @@
         <v>2</v>
       </c>
       <c r="O15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -4097,13 +4100,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -4115,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -4133,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -4147,13 +4150,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4165,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -4183,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -4197,13 +4200,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -4215,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -4233,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -4247,13 +4250,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -4265,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -4283,7 +4286,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -4297,13 +4300,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -4315,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -4333,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="O20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -4347,13 +4350,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -4365,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -4383,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -4397,13 +4400,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -4415,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -4433,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -4447,13 +4450,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -4465,10 +4468,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4483,7 +4486,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -4497,13 +4500,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -4515,10 +4518,10 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K24">
         <v>10</v>
@@ -4533,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -4547,13 +4550,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -4565,10 +4568,10 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -4583,7 +4586,7 @@
         <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -4597,13 +4600,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -4615,10 +4618,10 @@
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -4633,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -4647,13 +4650,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -4665,10 +4668,10 @@
         <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K27">
         <v>12</v>
@@ -4683,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P27">
         <v>6</v>
@@ -4697,13 +4700,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -4715,10 +4718,10 @@
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K28">
         <v>12</v>
@@ -4733,7 +4736,7 @@
         <v>2</v>
       </c>
       <c r="O28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -4747,13 +4750,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -4765,10 +4768,10 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K29">
         <v>12</v>
@@ -4783,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -4797,13 +4800,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -4815,10 +4818,10 @@
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K30">
         <v>12</v>
@@ -4833,7 +4836,7 @@
         <v>2</v>
       </c>
       <c r="O30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P30">
         <v>6</v>
@@ -4866,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4912,10 +4915,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4929,7 +4932,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4949,7 +4952,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4969,7 +4972,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E4">
         <v>5</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12110" windowHeight="19120" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="22190" windowHeight="9040" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,9 @@
     <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">StreamEvents!$A$1:$R$30</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="241">
   <si>
     <t>ID</t>
   </si>
@@ -226,6 +229,9 @@
     <t>选择一张M卡牌获得</t>
   </si>
   <si>
+    <t>固定值</t>
+  </si>
+  <si>
     <t>M卡</t>
   </si>
   <si>
@@ -289,7 +295,7 @@
     <t>声乐练习</t>
   </si>
   <si>
-    <t>歌力+40</t>
+    <t>歌力+20</t>
   </si>
   <si>
     <t>Stamina</t>
@@ -298,34 +304,40 @@
     <t>#FF2160</t>
   </si>
   <si>
+    <t>SingPractice</t>
+  </si>
+  <si>
     <t>游戏练习</t>
   </si>
   <si>
-    <t>游戏力+40</t>
+    <t>游戏力+20</t>
   </si>
   <si>
     <t>#4B58FF</t>
   </si>
   <si>
-    <t>AddGaming</t>
+    <t>GamePractice</t>
   </si>
   <si>
     <t>对话练习</t>
   </si>
   <si>
-    <t>杂谈力+40</t>
+    <t>杂谈力+20</t>
   </si>
   <si>
     <t>#FFB200</t>
   </si>
   <si>
-    <t>AddChatting</t>
+    <t>ChatPractice</t>
   </si>
   <si>
     <t>小憩一会</t>
   </si>
   <si>
-    <t>体力+25</t>
+    <t>体力+15</t>
+  </si>
+  <si>
+    <t>Rest</t>
   </si>
   <si>
     <t>Recovery</t>
@@ -337,27 +349,28 @@
     <t>Nap</t>
   </si>
   <si>
-    <t>外出吃饭</t>
-  </si>
-  <si>
-    <t>体力+60
-体力+40，获得一张卡牌
-体力+40，获得一个消耗品</t>
-  </si>
-  <si>
-    <t>Out</t>
+    <t>睡个大的</t>
+  </si>
+  <si>
+    <t>体力+35</t>
+  </si>
+  <si>
+    <t>Sleep</t>
   </si>
   <si>
     <t>放一天假</t>
   </si>
   <si>
-    <t>体力+100,从卡组中选择一张卡牌删除</t>
+    <t>体力+70,从卡组中选择一张卡牌删除</t>
   </si>
   <si>
     <t>DayOff</t>
   </si>
   <si>
     <t>直播成功</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
   <si>
     <t>#D0CECE</t>
@@ -416,10 +429,13 @@
     <t>Edit</t>
   </si>
   <si>
-    <t>网络购物</t>
+    <t>购物</t>
   </si>
   <si>
     <t>进入商店界面</t>
+  </si>
+  <si>
+    <t>Outside</t>
   </si>
   <si>
     <t>#0BF30B</t>
@@ -508,19 +524,19 @@
     <t>进阶唱歌练习</t>
   </si>
   <si>
-    <t>歌力+100，获得一张卡</t>
+    <t>歌力+30，获得一张卡</t>
   </si>
   <si>
     <t>进阶游戏练习</t>
   </si>
   <si>
-    <t>游戏力+100，获得一张卡</t>
+    <t>游戏力+30，获得一张卡</t>
   </si>
   <si>
     <t>进阶杂谈练习</t>
   </si>
   <si>
-    <t>杂谈力+100，获得一张卡</t>
+    <t>杂谈力+30，获得一张卡</t>
   </si>
   <si>
     <t>毕业1</t>
@@ -553,6 +569,36 @@
     <t>#D2CECE</t>
   </si>
   <si>
+    <t>雪王好感度增加事件</t>
+  </si>
+  <si>
+    <t>Coop</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>#F567ED</t>
+  </si>
+  <si>
+    <t>小室好感度增加事件</t>
+  </si>
+  <si>
+    <t>井井好感度增加事件</t>
+  </si>
+  <si>
+    <t>奶茶好感度增加事件</t>
+  </si>
+  <si>
+    <t>画师好感度增加事件</t>
+  </si>
+  <si>
+    <t>大白猫好感度增加事件</t>
+  </si>
+  <si>
+    <t>外出吃饭</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -583,9 +629,6 @@
     <t>Stream</t>
   </si>
   <si>
-    <t>#AB0580</t>
-  </si>
-  <si>
     <t>4,2,2</t>
   </si>
   <si>
@@ -649,9 +692,6 @@
     <t>第二阶段游戏</t>
   </si>
   <si>
-    <t>#AB0581</t>
-  </si>
-  <si>
     <t>3,6,3</t>
   </si>
   <si>
@@ -661,9 +701,6 @@
     <t>第二阶段杂谈</t>
   </si>
   <si>
-    <t>#AB0582</t>
-  </si>
-  <si>
     <t>3,3,6</t>
   </si>
   <si>
@@ -673,9 +710,6 @@
     <t>第二阶段营收</t>
   </si>
   <si>
-    <t>#AB0583</t>
-  </si>
-  <si>
     <t>3,4,5</t>
   </si>
   <si>
@@ -691,7 +725,7 @@
     <t>第三阶段舰长</t>
   </si>
   <si>
-    <t>4,3,5</t>
+    <t>5,3,4</t>
   </si>
   <si>
     <t>粉丝礼物回</t>
@@ -742,7 +776,7 @@
     <t>营收加成结局</t>
   </si>
   <si>
-    <t>5,4,6</t>
+    <t>6,4,5</t>
   </si>
   <si>
     <t>健身环耐久回</t>
@@ -760,9 +794,6 @@
     <t>舰长加成结局</t>
   </si>
   <si>
-    <t>6,4,5</t>
-  </si>
-  <si>
     <t>新衣回嘉宾</t>
   </si>
   <si>
@@ -770,30 +801,6 @@
   </si>
   <si>
     <t>4,5,6</t>
-  </si>
-  <si>
-    <t>一阶歌力向直播</t>
-  </si>
-  <si>
-    <t>一阶游戏力直播</t>
-  </si>
-  <si>
-    <t>一阶杂谈直播</t>
-  </si>
-  <si>
-    <t>二阶歌力向直播</t>
-  </si>
-  <si>
-    <t>二阶游戏力直播</t>
-  </si>
-  <si>
-    <t>二阶杂谈直播</t>
-  </si>
-  <si>
-    <t>才艺回</t>
-  </si>
-  <si>
-    <t>二阶营收直播</t>
   </si>
   <si>
     <t xml:space="preserve">Name </t>
@@ -1001,12 +1008,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB0580"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF2160"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1044,6 +1045,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0BF30B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF567ED"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1488,12 +1495,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1505,12 +1521,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1583,6 +1593,10 @@
   <colors>
     <mruColors>
       <color rgb="000BF30B"/>
+      <color rgb="00E3A7F7"/>
+      <color rgb="00F567ED"/>
+      <color rgb="00DEBA2C"/>
+      <color rgb="00FD460D"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1851,7 +1865,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2351,6 +2365,66 @@
       </c>
       <c r="F29" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2394,13 +2468,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2408,13 +2482,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2422,13 +2496,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
         <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2436,13 +2510,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2450,13 +2524,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2464,13 +2538,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2478,13 +2552,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2496,7 +2570,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="2" customWidth="1"/>
@@ -2526,25 +2600,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -2552,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="5" t="s">
         <v>85</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>54</v>
@@ -2564,19 +2638,19 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
+      <c r="I2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -2584,10 +2658,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>54</v>
@@ -2596,19 +2670,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>90</v>
+      <c r="I3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -2616,10 +2690,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>54</v>
@@ -2628,19 +2702,19 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G4" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>94</v>
+      <c r="I4" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -2648,63 +2722,63 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:11">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -2712,31 +2786,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -2744,31 +2818,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -2776,31 +2850,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -2808,31 +2882,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>108</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -2840,31 +2914,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -2872,31 +2946,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -2904,31 +2978,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -2936,31 +3010,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -2968,28 +3042,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -2997,31 +3071,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" s="2">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -3029,31 +3103,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -3061,31 +3135,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -3093,10 +3167,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>54</v>
@@ -3105,16 +3179,16 @@
         <v>2</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>87</v>
+      <c r="I19" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -3122,10 +3196,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>54</v>
@@ -3134,16 +3208,16 @@
         <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>90</v>
+      <c r="I20" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -3151,10 +3225,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>54</v>
@@ -3163,16 +3237,16 @@
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>94</v>
+      <c r="I21" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -3180,31 +3254,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -3212,31 +3286,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -3244,28 +3318,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K24" s="2">
         <v>0</v>
@@ -3276,31 +3350,231 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:9">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:9">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3347,46 +3621,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="L1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="M1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="N1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="O1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="P1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="Q1" t="s">
-        <v>157</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -3394,28 +3668,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -3430,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="P2" s="2">
         <v>14</v>
@@ -3444,28 +3718,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3480,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -3494,28 +3768,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3530,7 +3804,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -3544,28 +3818,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -3580,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -3588,35 +3862,35 @@
       <c r="Q5" s="2">
         <v>7</v>
       </c>
-      <c r="R5" s="4"/>
+      <c r="R5" s="7"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3628,10 +3902,10 @@
         <v>50</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3639,35 +3913,35 @@
       <c r="Q6" s="2">
         <v>20</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>160</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3679,10 +3953,10 @@
         <v>50</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3690,35 +3964,35 @@
       <c r="Q7" s="2">
         <v>20</v>
       </c>
-      <c r="R7" s="4"/>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" t="s">
         <v>175</v>
-      </c>
-      <c r="C8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" t="s">
-        <v>160</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3730,10 +4004,10 @@
         <v>50</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3741,35 +4015,35 @@
       <c r="Q8" s="2">
         <v>20</v>
       </c>
-      <c r="R8" s="4"/>
+      <c r="R8" s="7"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3781,10 +4055,10 @@
         <v>80</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3792,35 +4066,35 @@
       <c r="Q9">
         <v>7</v>
       </c>
-      <c r="R9" s="4"/>
+      <c r="R9" s="7"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>160</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3832,10 +4106,10 @@
         <v>80</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3843,35 +4117,35 @@
       <c r="Q10">
         <v>7</v>
       </c>
-      <c r="R10" s="4"/>
+      <c r="R10" s="7"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3883,10 +4157,10 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3900,28 +4174,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>191</v>
+        <v>175</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3936,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3950,28 +4224,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>160</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3986,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -4000,28 +4274,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4036,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -4050,28 +4324,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>160</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -4083,10 +4357,10 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -4100,28 +4374,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -4136,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -4150,28 +4424,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>160</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -4183,10 +4457,10 @@
         <v>130</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -4200,28 +4474,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -4236,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -4250,28 +4524,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>160</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>191</v>
+        <v>175</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -4286,7 +4560,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -4300,28 +4574,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -4333,10 +4607,10 @@
         <v>130</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -4350,28 +4624,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -4386,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -4400,28 +4674,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -4436,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -4450,28 +4724,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C23" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>160</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4486,7 +4760,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -4495,355 +4769,30 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" t="s">
-        <v>224</v>
-      </c>
-      <c r="D24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24">
-        <v>20</v>
-      </c>
-      <c r="H24" t="s">
-        <v>160</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K24">
-        <v>10</v>
-      </c>
-      <c r="L24">
-        <v>7000</v>
-      </c>
-      <c r="M24">
-        <v>30</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24" t="s">
-        <v>171</v>
-      </c>
-      <c r="P24">
-        <v>6</v>
-      </c>
-      <c r="Q24" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" t="s">
-        <v>160</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25">
-        <v>20</v>
-      </c>
-      <c r="H25" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K25">
-        <v>10</v>
-      </c>
-      <c r="L25">
-        <v>7000</v>
-      </c>
-      <c r="M25">
-        <v>30</v>
-      </c>
-      <c r="N25">
-        <v>2</v>
-      </c>
-      <c r="O25" t="s">
-        <v>174</v>
-      </c>
-      <c r="P25">
-        <v>6</v>
-      </c>
-      <c r="Q25" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" t="s">
-        <v>226</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26">
-        <v>20</v>
-      </c>
-      <c r="H26" t="s">
-        <v>160</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K26">
-        <v>10</v>
-      </c>
-      <c r="L26">
-        <v>7000</v>
-      </c>
-      <c r="M26">
-        <v>30</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>177</v>
-      </c>
-      <c r="P26">
-        <v>6</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" t="s">
-        <v>227</v>
-      </c>
-      <c r="D27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27">
-        <v>20</v>
-      </c>
-      <c r="H27" t="s">
-        <v>160</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K27">
-        <v>12</v>
-      </c>
-      <c r="L27">
-        <v>14000</v>
-      </c>
-      <c r="M27">
-        <v>50</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27" t="s">
-        <v>180</v>
-      </c>
-      <c r="P27">
-        <v>6</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>207</v>
-      </c>
-      <c r="C28" t="s">
-        <v>228</v>
-      </c>
-      <c r="D28" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28">
-        <v>20</v>
-      </c>
-      <c r="H28" t="s">
-        <v>160</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K28">
-        <v>12</v>
-      </c>
-      <c r="L28">
-        <v>14000</v>
-      </c>
-      <c r="M28">
-        <v>50</v>
-      </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-      <c r="O28" t="s">
-        <v>184</v>
-      </c>
-      <c r="P28">
-        <v>6</v>
-      </c>
-      <c r="Q28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" t="s">
-        <v>229</v>
-      </c>
-      <c r="D29" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29">
-        <v>20</v>
-      </c>
-      <c r="H29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K29">
-        <v>12</v>
-      </c>
-      <c r="L29">
-        <v>14000</v>
-      </c>
-      <c r="M29">
-        <v>50</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>188</v>
-      </c>
-      <c r="P29">
-        <v>6</v>
-      </c>
-      <c r="Q29">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>230</v>
-      </c>
-      <c r="C30" t="s">
-        <v>231</v>
-      </c>
-      <c r="D30" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>86</v>
-      </c>
-      <c r="G30">
-        <v>20</v>
-      </c>
-      <c r="H30" t="s">
-        <v>160</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K30">
-        <v>12</v>
-      </c>
-      <c r="L30">
-        <v>14000</v>
-      </c>
-      <c r="M30">
-        <v>50</v>
-      </c>
-      <c r="N30">
-        <v>2</v>
-      </c>
-      <c r="O30" t="s">
-        <v>192</v>
-      </c>
-      <c r="P30">
-        <v>6</v>
-      </c>
-      <c r="Q30">
-        <v>7</v>
-      </c>
+    <row r="24" spans="9:17">
+      <c r="I24" s="5"/>
+      <c r="Q24" s="2"/>
+    </row>
+    <row r="25" spans="9:17">
+      <c r="I25" s="5"/>
+      <c r="Q25" s="2"/>
+    </row>
+    <row r="26" spans="9:17">
+      <c r="I26" s="5"/>
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" spans="9:17">
+      <c r="I27" s="5"/>
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="28" spans="9:9">
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="9:9">
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="9:9">
+      <c r="I30" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4869,16 +4818,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -4915,10 +4864,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4932,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4952,7 +4901,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4972,13 +4921,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
-    <sheet name="CardConditions" sheetId="2" r:id="rId2"/>
+    <sheet name="StreamEvents" sheetId="3" r:id="rId2"/>
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
-    <sheet name="StreamEvents" sheetId="3" r:id="rId4"/>
+    <sheet name="CardConditions" sheetId="2" r:id="rId4"/>
     <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">StreamEvents!$A$1:$R$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$R$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="252">
   <si>
     <t>ID</t>
   </si>
@@ -232,43 +232,22 @@
     <t>固定值</t>
   </si>
   <si>
-    <t>M卡</t>
-  </si>
-  <si>
-    <t>VCardTypeCondition</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>A卡</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>VCardRarityCondition</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>LiveType</t>
-  </si>
-  <si>
-    <t>VCardLiveTypeCondition</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>F</t>
+    <t>小室好感+X</t>
+  </si>
+  <si>
+    <t>VRaisingAddCoopValueEffect</t>
+  </si>
+  <si>
+    <t>雪王好感+X</t>
+  </si>
+  <si>
+    <t>井井好感+X</t>
+  </si>
+  <si>
+    <t>柚子茶好感+X</t>
+  </si>
+  <si>
+    <t>麻麻好感+X</t>
   </si>
   <si>
     <t>Duration</t>
@@ -289,6 +268,222 @@
     <t>PlacingCondition</t>
   </si>
   <si>
+    <t>TurnCount</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>InitialViewers</t>
+  </si>
+  <si>
+    <t>MainAbility</t>
+  </si>
+  <si>
+    <t>AbilityTurns</t>
+  </si>
+  <si>
+    <t>SuccessEvent</t>
+  </si>
+  <si>
+    <t>FailEvent</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>歌回</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>4,2,2</t>
+  </si>
+  <si>
+    <t>游戏回</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>2,4,2</t>
+  </si>
+  <si>
+    <t>杂谈回</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>2,2,4</t>
+  </si>
+  <si>
+    <t>歌杂</t>
+  </si>
+  <si>
+    <t>4,2,4</t>
+  </si>
+  <si>
+    <t>主题歌回</t>
+  </si>
+  <si>
+    <t>第一阶段歌力</t>
+  </si>
+  <si>
+    <t>5,2,3</t>
+  </si>
+  <si>
+    <t>水友联动游戏回</t>
+  </si>
+  <si>
+    <t>第一阶段游戏力</t>
+  </si>
+  <si>
+    <t>2,5,3</t>
+  </si>
+  <si>
+    <t>棉花糖回</t>
+  </si>
+  <si>
+    <t>第一阶段杂谈力</t>
+  </si>
+  <si>
+    <t>2,2,6</t>
+  </si>
+  <si>
+    <t>水友歌回</t>
+  </si>
+  <si>
+    <t>第二阶段歌力</t>
+  </si>
+  <si>
+    <t>6,3,3</t>
+  </si>
+  <si>
+    <t>水友游戏回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>5,3,4</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>光暗歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>4,4,7</t>
+  </si>
+  <si>
+    <t>段位挑战回</t>
+  </si>
+  <si>
+    <t>游戏力加成结局</t>
+  </si>
+  <si>
+    <t>4,7,4</t>
+  </si>
+  <si>
+    <t>清楚聊天室</t>
+  </si>
+  <si>
+    <t>杂谈力加成结局</t>
+  </si>
+  <si>
+    <t>人头麦回</t>
+  </si>
+  <si>
+    <t>营收加成结局</t>
+  </si>
+  <si>
+    <t>6,4,5</t>
+  </si>
+  <si>
+    <t>健身环耐久回</t>
+  </si>
+  <si>
+    <t>体力加成结局</t>
+  </si>
+  <si>
+    <t>4,6,5</t>
+  </si>
+  <si>
+    <t>百舰回</t>
+  </si>
+  <si>
+    <t>舰长加成结局</t>
+  </si>
+  <si>
+    <t>新衣回嘉宾</t>
+  </si>
+  <si>
+    <t>好感度加成结局</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
     <t>DialogueNode</t>
   </si>
   <si>
@@ -298,12 +493,6 @@
     <t>歌力+20</t>
   </si>
   <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
     <t>SingPractice</t>
   </si>
   <si>
@@ -313,9 +502,6 @@
     <t>游戏力+20</t>
   </si>
   <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
     <t>GamePractice</t>
   </si>
   <si>
@@ -323,9 +509,6 @@
   </si>
   <si>
     <t>杂谈力+20</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
   </si>
   <si>
     <t>ChatPractice</t>
@@ -581,226 +764,76 @@
     <t>#F567ED</t>
   </si>
   <si>
+    <t>XuewangMeet1</t>
+  </si>
+  <si>
     <t>小室好感度增加事件</t>
   </si>
   <si>
+    <t>XiaoShiMeet1</t>
+  </si>
+  <si>
     <t>井井好感度增加事件</t>
   </si>
   <si>
+    <t>##Meet1</t>
+  </si>
+  <si>
     <t>奶茶好感度增加事件</t>
   </si>
   <si>
+    <t>YuzuMeet1</t>
+  </si>
+  <si>
     <t>画师好感度增加事件</t>
   </si>
   <si>
+    <t>MamaMeet1</t>
+  </si>
+  <si>
     <t>大白猫好感度增加事件</t>
   </si>
   <si>
     <t>外出吃饭</t>
   </si>
   <si>
-    <t>TurnCount</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>InitialViewers</t>
-  </si>
-  <si>
-    <t>MainAbility</t>
-  </si>
-  <si>
-    <t>AbilityTurns</t>
-  </si>
-  <si>
-    <t>SuccessEvent</t>
-  </si>
-  <si>
-    <t>FailEvent</t>
-  </si>
-  <si>
-    <t>Conditions</t>
-  </si>
-  <si>
-    <t>歌回</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>4,2,2</t>
-  </si>
-  <si>
-    <t>游戏回</t>
-  </si>
-  <si>
-    <t>2,4,2</t>
-  </si>
-  <si>
-    <t>杂谈回</t>
-  </si>
-  <si>
-    <t>2,2,4</t>
-  </si>
-  <si>
-    <t>歌杂</t>
-  </si>
-  <si>
-    <t>4,2,4</t>
-  </si>
-  <si>
-    <t>主题歌回</t>
-  </si>
-  <si>
-    <t>第一阶段歌力</t>
-  </si>
-  <si>
-    <t>5,2,3</t>
-  </si>
-  <si>
-    <t>水友联动游戏回</t>
-  </si>
-  <si>
-    <t>第一阶段游戏力</t>
-  </si>
-  <si>
-    <t>2,5,3</t>
-  </si>
-  <si>
-    <t>棉花糖回</t>
-  </si>
-  <si>
-    <t>第一阶段杂谈力</t>
-  </si>
-  <si>
-    <t>2,2,6</t>
-  </si>
-  <si>
-    <t>水友歌回</t>
-  </si>
-  <si>
-    <t>第二阶段歌力</t>
-  </si>
-  <si>
-    <t>6,3,3</t>
-  </si>
-  <si>
-    <t>水友游戏回</t>
-  </si>
-  <si>
-    <t>第二阶段游戏</t>
-  </si>
-  <si>
-    <t>3,6,3</t>
-  </si>
-  <si>
-    <t>视频鉴赏回</t>
-  </si>
-  <si>
-    <t>第二阶段杂谈</t>
-  </si>
-  <si>
-    <t>3,3,6</t>
-  </si>
-  <si>
-    <t>代抽回</t>
-  </si>
-  <si>
-    <t>第二阶段营收</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>水友投稿回</t>
-  </si>
-  <si>
-    <t>第三阶段粉丝</t>
-  </si>
-  <si>
-    <t>生日回</t>
-  </si>
-  <si>
-    <t>第三阶段舰长</t>
-  </si>
-  <si>
-    <t>5,3,4</t>
-  </si>
-  <si>
-    <t>粉丝礼物回</t>
-  </si>
-  <si>
-    <t>第三阶段营收</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>健身环挑战回</t>
-  </si>
-  <si>
-    <t>第三阶段体力</t>
-  </si>
-  <si>
-    <t>3,5,4</t>
-  </si>
-  <si>
-    <t>光暗歌会</t>
-  </si>
-  <si>
-    <t>歌力加成结局</t>
-  </si>
-  <si>
-    <t>4,4,7</t>
-  </si>
-  <si>
-    <t>段位挑战回</t>
-  </si>
-  <si>
-    <t>游戏力加成结局</t>
-  </si>
-  <si>
-    <t>4,7,4</t>
-  </si>
-  <si>
-    <t>清楚聊天室</t>
-  </si>
-  <si>
-    <t>杂谈力加成结局</t>
-  </si>
-  <si>
-    <t>人头麦回</t>
-  </si>
-  <si>
-    <t>营收加成结局</t>
-  </si>
-  <si>
-    <t>6,4,5</t>
-  </si>
-  <si>
-    <t>健身环耐久回</t>
-  </si>
-  <si>
-    <t>体力加成结局</t>
-  </si>
-  <si>
-    <t>4,6,5</t>
-  </si>
-  <si>
-    <t>百舰回</t>
-  </si>
-  <si>
-    <t>舰长加成结局</t>
-  </si>
-  <si>
-    <t>新衣回嘉宾</t>
-  </si>
-  <si>
-    <t>好感度加成结局</t>
-  </si>
-  <si>
-    <t>4,5,6</t>
+    <t>M卡</t>
+  </si>
+  <si>
+    <t>VCardTypeCondition</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>A卡</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>VCardRarityCondition</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>LiveType</t>
+  </si>
+  <si>
+    <t>VCardLiveTypeCondition</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t xml:space="preserve">Name </t>
@@ -1497,16 +1530,37 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -1515,27 +1569,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1865,7 +1898,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2427,6 +2460,76 @@
         <v>12</v>
       </c>
     </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2434,1156 +2537,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="10.425" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="2" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="2">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:11">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2">
-        <v>5</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1" spans="1:11">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="2">
-        <v>2</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="2">
-        <v>8</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="2">
-        <v>8</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:11">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:9">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
-      <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:9">
-      <c r="A28" s="2">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="2">
-        <v>27</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="2">
-        <v>28</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="2">
-        <v>29</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="2">
-        <v>30</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R30"/>
@@ -3621,46 +2574,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" t="s">
         <v>78</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>80</v>
       </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>81</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>82</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>83</v>
       </c>
-      <c r="K1" t="s">
-        <v>166</v>
-      </c>
-      <c r="L1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M1" t="s">
-        <v>168</v>
-      </c>
-      <c r="N1" t="s">
-        <v>169</v>
-      </c>
-      <c r="O1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P1" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>172</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>173</v>
+      <c r="R1" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -3668,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3686,9 +2639,9 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K2">
@@ -3704,9 +2657,9 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>176</v>
-      </c>
-      <c r="P2" s="2">
+        <v>89</v>
+      </c>
+      <c r="P2" s="1">
         <v>14</v>
       </c>
       <c r="Q2">
@@ -3718,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3736,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -3754,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -3768,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3786,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -3804,7 +2757,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -3818,13 +2771,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3836,9 +2789,9 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K5">
@@ -3854,28 +2807,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="P5">
         <v>6</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>7</v>
       </c>
-      <c r="R5" s="7"/>
+      <c r="R5" s="14"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3887,9 +2840,9 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K6">
@@ -3905,28 +2858,28 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>6</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>20</v>
       </c>
-      <c r="R6" s="7"/>
+      <c r="R6" s="14"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3938,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3956,28 +2909,28 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="P7">
         <v>6</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>20</v>
       </c>
-      <c r="R7" s="7"/>
+      <c r="R7" s="14"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3989,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>175</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -4007,28 +2960,28 @@
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="P8">
         <v>6</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>20</v>
       </c>
-      <c r="R8" s="7"/>
+      <c r="R8" s="14"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -4040,9 +2993,9 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K9">
@@ -4058,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -4066,20 +3019,20 @@
       <c r="Q9">
         <v>7</v>
       </c>
-      <c r="R9" s="7"/>
+      <c r="R9" s="14"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -4091,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>175</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -4109,7 +3062,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -4117,20 +3070,20 @@
       <c r="Q10">
         <v>7</v>
       </c>
-      <c r="R10" s="7"/>
+      <c r="R10" s="14"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -4142,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -4160,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -4174,13 +3127,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -4192,10 +3145,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -4210,7 +3163,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -4224,13 +3177,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -4242,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -4260,7 +3213,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -4274,13 +3227,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4292,9 +3245,9 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K14">
@@ -4310,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>208</v>
+        <v>123</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -4324,13 +3277,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4342,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -4360,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -4374,13 +3327,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -4392,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -4410,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -4424,13 +3377,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -4442,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -4460,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="O17" t="s">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -4474,13 +3427,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -4492,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -4510,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -4524,13 +3477,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -4542,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -4560,7 +3513,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -4574,13 +3527,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -4592,9 +3545,9 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
-      </c>
-      <c r="I20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K20">
@@ -4610,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -4624,13 +3577,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -4642,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -4660,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>228</v>
+        <v>143</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -4674,13 +3627,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>229</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -4692,9 +3645,9 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
-      </c>
-      <c r="I22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K22">
@@ -4710,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -4724,13 +3677,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -4742,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -4760,7 +3713,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -4770,29 +3723,1194 @@
       </c>
     </row>
     <row r="24" spans="9:17">
-      <c r="I24" s="5"/>
-      <c r="Q24" s="2"/>
+      <c r="I24" s="12"/>
+      <c r="Q24" s="1"/>
     </row>
     <row r="25" spans="9:17">
-      <c r="I25" s="5"/>
-      <c r="Q25" s="2"/>
+      <c r="I25" s="12"/>
+      <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="9:17">
-      <c r="I26" s="5"/>
-      <c r="Q26" s="2"/>
+      <c r="I26" s="12"/>
+      <c r="Q26" s="1"/>
     </row>
     <row r="27" spans="9:17">
-      <c r="I27" s="5"/>
-      <c r="Q27" s="2"/>
+      <c r="I27" s="12"/>
+      <c r="Q27" s="1"/>
     </row>
     <row r="28" spans="9:9">
-      <c r="I28" s="5"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" spans="9:9">
-      <c r="I29" s="5"/>
+      <c r="I29" s="12"/>
     </row>
     <row r="30" spans="9:9">
-      <c r="I30" s="5"/>
+      <c r="I30" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.425" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.8583333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="1">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="1">
+        <v>6</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:11">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:11">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="1">
+        <v>8</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="1">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:11">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" t="s">
+        <v>244</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4818,16 +4936,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -4864,10 +4982,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4881,7 +4999,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4901,7 +5019,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4921,13 +5039,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <t>CAPressure</t>
   </si>
   <si>
-    <t>金钱+X</t>
+    <t>沪币+X</t>
   </si>
   <si>
     <t>CAMoney</t>
@@ -589,9 +589,9 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>金钱+60，获得一张满足条件的卡体力-10
-金钱+60，获得一张满足条件卡，体力-10
-金钱+60，获得一张满足条件的卡</t>
+    <t>沪币+50，粉丝+100
+沪币+90
+金钱+50，获得一张卡</t>
   </si>
   <si>
     <t>Work</t>
@@ -4179,7 +4179,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>162</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="253">
   <si>
     <t>ID</t>
   </si>
@@ -214,7 +214,7 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
-    <t>0.5,0.3,0.1,0.1,0.5,0.1</t>
+    <t>0.5,0.3,0.1,0.1,0.05,0.01</t>
   </si>
   <si>
     <t>进入结局</t>
@@ -250,6 +250,9 @@
     <t>麻麻好感+X</t>
   </si>
   <si>
+    <t>选择一张卡获得</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -535,7 +538,7 @@
     <t>睡个大的</t>
   </si>
   <si>
-    <t>体力+35</t>
+    <t>体力+35，随机删除一张基础牌</t>
   </si>
   <si>
     <t>Sleep</t>
@@ -1898,7 +1901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2528,6 +2531,24 @@
       </c>
       <c r="F37">
         <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2574,46 +2595,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2621,28 +2642,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>87</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>86</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2657,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P2" s="1">
         <v>14</v>
@@ -2671,28 +2692,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>87</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>86</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2707,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -2721,28 +2742,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>87</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>86</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2757,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -2771,28 +2792,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
         <v>87</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>86</v>
-      </c>
       <c r="I5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2807,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -2822,28 +2843,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
         <v>87</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>86</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -2858,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -2873,28 +2894,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
         <v>87</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>86</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -2909,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -2924,28 +2945,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
         <v>87</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>86</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -2960,7 +2981,7 @@
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -2975,28 +2996,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>87</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>86</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3011,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3026,28 +3047,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>87</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>86</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3062,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3077,28 +3098,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
         <v>87</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>86</v>
-      </c>
       <c r="I11" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3113,7 +3134,7 @@
         <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3127,28 +3148,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>87</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>86</v>
-      </c>
       <c r="I12" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3163,7 +3184,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3177,28 +3198,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
         <v>87</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
       <c r="I13" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3213,7 +3234,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3227,28 +3248,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
         <v>87</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>86</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -3263,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -3277,28 +3298,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
         <v>87</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>86</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -3313,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -3327,28 +3348,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
         <v>87</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>86</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -3363,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -3377,28 +3398,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
         <v>87</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>86</v>
-      </c>
       <c r="I17" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -3413,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="O17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -3427,28 +3448,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
         <v>87</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>86</v>
-      </c>
       <c r="I18" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -3463,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -3477,28 +3498,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
         <v>87</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" t="s">
-        <v>86</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -3513,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -3527,28 +3548,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
         <v>87</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>86</v>
-      </c>
       <c r="I20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -3563,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -3577,28 +3598,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
         <v>87</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>86</v>
-      </c>
       <c r="I21" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -3613,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -3627,28 +3648,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
         <v>87</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>86</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -3663,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -3677,28 +3698,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
         <v>87</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>86</v>
-      </c>
       <c r="I23" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -3713,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -3786,25 +3807,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -3812,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3824,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3833,10 +3854,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -3844,10 +3865,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3856,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -3865,10 +3886,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -3876,10 +3897,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -3888,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -3897,10 +3918,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -3908,31 +3929,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -3940,31 +3961,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -3972,31 +3993,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4004,31 +4025,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4036,31 +4057,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4068,31 +4089,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4100,31 +4121,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4132,31 +4153,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4164,31 +4185,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4196,31 +4217,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -4228,28 +4249,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4257,31 +4278,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4289,31 +4310,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4321,31 +4342,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4353,10 +4374,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4365,7 +4386,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4374,7 +4395,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -4382,10 +4403,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4394,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4403,7 +4424,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -4411,10 +4432,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4423,7 +4444,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4432,7 +4453,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -4440,31 +4461,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4472,31 +4493,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4504,28 +4525,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4536,28 +4557,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4568,31 +4589,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4600,31 +4621,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4632,31 +4653,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -4664,31 +4685,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -4696,31 +4717,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -4728,28 +4749,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -4757,25 +4778,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -4819,13 +4840,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4833,13 +4854,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4847,13 +4868,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" t="s">
         <v>238</v>
-      </c>
-      <c r="E4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4861,13 +4882,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" t="s">
         <v>239</v>
       </c>
-      <c r="D5" t="s">
-        <v>238</v>
-      </c>
       <c r="E5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4875,13 +4896,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4889,13 +4910,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4903,13 +4924,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4936,16 +4957,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -4982,10 +5003,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4999,7 +5020,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5019,7 +5040,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5039,13 +5060,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="266">
   <si>
     <t>ID</t>
   </si>
@@ -251,6 +251,30 @@
   </si>
   <si>
     <t>选择一张卡获得</t>
+  </si>
+  <si>
+    <t>随机删除一张基础牌</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteCardEffect</t>
+  </si>
+  <si>
+    <t>随机获得一张A卡</t>
+  </si>
+  <si>
+    <t>VRaisingAddRandomCardEffect</t>
+  </si>
+  <si>
+    <t>0.5,0.3,0.1,0,0,0</t>
+  </si>
+  <si>
+    <t>随机获得一张M卡</t>
+  </si>
+  <si>
+    <t>随机获得一张红温卡</t>
+  </si>
+  <si>
+    <t>随机获得一张幽默卡</t>
   </si>
   <si>
     <t>Duration</t>
@@ -837,6 +861,21 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>红温</t>
+  </si>
+  <si>
+    <t>VCardTagCondition</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>幽默</t>
+  </si>
+  <si>
+    <t>fun</t>
   </si>
   <si>
     <t xml:space="preserve">Name </t>
@@ -1901,7 +1940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2549,6 +2588,79 @@
       <c r="E38"/>
       <c r="F38" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2595,46 +2707,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="M1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="P1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="Q1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2642,28 +2754,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2678,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="P2" s="1">
         <v>14</v>
@@ -2692,28 +2804,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2728,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -2742,28 +2854,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2778,7 +2890,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -2792,28 +2904,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2828,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -2843,28 +2955,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -2879,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -2894,28 +3006,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -2930,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -2945,28 +3057,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -2981,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -2996,28 +3108,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3032,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3047,28 +3159,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3083,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3098,28 +3210,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3134,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3148,28 +3260,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3184,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3198,28 +3310,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3234,7 +3346,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3248,28 +3360,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -3284,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -3298,28 +3410,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -3334,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -3348,28 +3460,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -3384,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -3398,28 +3510,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -3434,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="O17" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -3448,28 +3560,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -3484,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -3498,28 +3610,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -3534,7 +3646,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -3548,28 +3660,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -3584,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -3598,28 +3710,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -3634,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -3648,28 +3760,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -3684,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -3698,28 +3810,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -3734,7 +3846,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -3807,25 +3919,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -3833,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3845,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3854,10 +3966,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -3865,10 +3977,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3877,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -3886,10 +3998,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -3897,10 +4009,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -3909,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -3918,10 +4030,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -3929,31 +4041,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -3961,31 +4073,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -3993,31 +4105,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4025,31 +4137,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4057,31 +4169,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4089,31 +4201,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4121,31 +4233,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4153,31 +4265,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>174</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4185,31 +4297,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4217,31 +4329,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -4249,28 +4361,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4278,31 +4390,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4310,31 +4422,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4342,31 +4454,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4374,10 +4486,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4386,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4395,7 +4507,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -4403,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4415,7 +4527,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4424,7 +4536,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -4432,10 +4544,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4444,7 +4556,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4453,7 +4565,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -4461,31 +4573,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4493,31 +4605,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4525,28 +4637,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4557,28 +4669,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4589,31 +4701,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4621,31 +4733,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4653,31 +4765,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -4685,31 +4797,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -4717,31 +4829,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>221</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -4749,28 +4861,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -4778,25 +4890,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4808,8 +4920,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4840,13 +4952,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4854,13 +4966,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4868,13 +4980,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4882,13 +4994,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4896,13 +5008,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4910,13 +5022,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4924,13 +5036,41 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4957,16 +5097,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5003,10 +5143,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5020,7 +5160,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5040,7 +5180,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5060,13 +5200,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="22190" windowHeight="9040"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="269">
   <si>
     <t>ID</t>
   </si>
@@ -274,6 +274,9 @@
     <t>随机获得一张红温卡</t>
   </si>
   <si>
+    <t>5\</t>
+  </si>
+  <si>
     <t>随机获得一张幽默卡</t>
   </si>
   <si>
@@ -578,6 +581,9 @@
   </si>
   <si>
     <t>直播成功</t>
+  </si>
+  <si>
+    <t>粉丝+200，金钱+30，舰长+1，获得一张卡</t>
   </si>
   <si>
     <t>Other</t>
@@ -652,6 +658,71 @@
   </si>
   <si>
     <t>歌回成功事件</t>
+  </si>
+  <si>
+    <r>
+      <t>粉丝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，金钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，舰长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，获得一张卡</t>
+    </r>
+  </si>
+  <si>
+    <t>SingSuccess</t>
+  </si>
+  <si>
+    <t>游戏回成功事件</t>
   </si>
   <si>
     <r>
@@ -717,12 +788,6 @@
       </rPr>
       <t>，获得一张卡</t>
     </r>
-  </si>
-  <si>
-    <t>SingSuccess</t>
-  </si>
-  <si>
-    <t>游戏回成功事件</t>
   </si>
   <si>
     <t>gameSuccess</t>
@@ -2650,11 +2715,11 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43">
-        <v>41</v>
+      <c r="A43" t="s">
+        <v>79</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
         <v>75</v>
@@ -2707,46 +2772,46 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -2754,28 +2819,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>96</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>95</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2790,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P2" s="1">
         <v>14</v>
@@ -2804,28 +2869,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>96</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>95</v>
-      </c>
       <c r="I3" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2840,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -2854,28 +2919,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>96</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>95</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2890,7 +2955,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -2904,28 +2969,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
         <v>96</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>95</v>
-      </c>
       <c r="I5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2940,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -2955,28 +3020,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
         <v>96</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>95</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -2991,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3006,28 +3071,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
         <v>96</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>95</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3042,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3057,28 +3122,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
         <v>96</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>95</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3093,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3108,28 +3173,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>96</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>95</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K9">
         <v>12</v>
@@ -3144,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3159,28 +3224,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>96</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>95</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3195,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3210,28 +3275,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
         <v>96</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>95</v>
-      </c>
       <c r="I11" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3246,7 +3311,7 @@
         <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3260,28 +3325,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>96</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>95</v>
-      </c>
       <c r="I12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3296,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3310,28 +3375,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
         <v>96</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
-        <v>95</v>
-      </c>
       <c r="I13" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3346,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3360,28 +3425,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
         <v>96</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>95</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -3396,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -3410,28 +3475,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
         <v>96</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>95</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K15">
         <v>12</v>
@@ -3446,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -3460,28 +3525,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
         <v>96</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>95</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K16">
         <v>12</v>
@@ -3496,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P16">
         <v>6</v>
@@ -3510,28 +3575,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>95</v>
-      </c>
       <c r="I17" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K17">
         <v>15</v>
@@ -3546,7 +3611,7 @@
         <v>2</v>
       </c>
       <c r="O17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -3560,28 +3625,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
         <v>96</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>95</v>
-      </c>
       <c r="I18" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K18">
         <v>15</v>
@@ -3596,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -3610,28 +3675,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
         <v>96</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19" t="s">
-        <v>95</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K19">
         <v>15</v>
@@ -3646,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="O19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -3660,28 +3725,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
         <v>96</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>95</v>
-      </c>
       <c r="I20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K20">
         <v>15</v>
@@ -3696,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -3710,28 +3775,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
         <v>96</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="s">
-        <v>95</v>
-      </c>
       <c r="I21" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K21">
         <v>15</v>
@@ -3746,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -3760,28 +3825,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
         <v>96</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>95</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K22">
         <v>15</v>
@@ -3796,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -3810,28 +3875,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
         <v>96</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>95</v>
-      </c>
       <c r="I23" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K23">
         <v>15</v>
@@ -3846,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="O23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P23">
         <v>6</v>
@@ -3919,25 +3984,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -3945,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3957,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3966,10 +4031,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -3977,10 +4042,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3989,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -3998,10 +4063,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -4009,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -4021,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -4030,10 +4095,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -4041,31 +4106,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -4073,31 +4138,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -4105,31 +4170,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4137,31 +4202,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4169,31 +4234,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>182</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4201,31 +4266,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4233,31 +4298,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4265,31 +4330,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4297,31 +4362,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4329,31 +4394,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -4361,28 +4426,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4390,31 +4455,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4422,31 +4487,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4454,31 +4519,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4486,10 +4551,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4498,7 +4563,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4507,7 +4572,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -4515,10 +4580,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4527,7 +4592,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4536,7 +4601,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -4544,10 +4609,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4556,7 +4621,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4565,7 +4630,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -4573,31 +4638,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4605,31 +4670,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4637,28 +4702,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4669,28 +4734,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4701,31 +4766,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4733,31 +4798,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="I27" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4765,31 +4830,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -4797,31 +4862,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -4829,31 +4894,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -4861,28 +4926,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -4890,25 +4955,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -4952,13 +5017,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4966,13 +5031,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4980,13 +5045,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4994,13 +5059,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5008,13 +5073,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5022,13 +5087,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5036,13 +5101,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5050,13 +5115,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5064,13 +5129,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5097,16 +5162,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -5143,10 +5208,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5160,7 +5225,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5180,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5200,13 +5265,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB6A128-3580-4A80-AAC0-40FF0E23745F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="3"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,7 @@
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$R$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -898,22 +902,22 @@
   <si>
     <t>VPhaseEndingEventCondition</t>
   </si>
+  <si>
+    <t>enter store</t>
+  </si>
+  <si>
+    <t>VRaisingEnterStoreEffect</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -924,157 +928,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1107,7 +973,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1129,194 +995,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1324,253 +1004,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1605,7 +1043,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1613,70 +1050,26 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
-      <color rgb="00E3A7F7"/>
-      <color rgb="00F567ED"/>
-      <color rgb="00DEBA2C"/>
-      <color rgb="00FD460D"/>
+      <color rgb="FF0BF30B"/>
+      <color rgb="FFE3A7F7"/>
+      <color rgb="FFF567ED"/>
+      <color rgb="FFDEBA2C"/>
+      <color rgb="FFFD460D"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1934,22 +1327,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2083,7 +1476,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2097,7 +1490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2111,7 +1504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2295,7 +1688,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2360,7 +1753,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2394,7 +1787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2585,12 +1978,11 @@
       <c r="D38" t="s">
         <v>58</v>
       </c>
-      <c r="E38"/>
       <c r="F38" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2663,37 +2055,46 @@
         <v>76</v>
       </c>
     </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="8.15" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="3.26666666666667" customWidth="1"/>
-    <col min="12" max="12" width="6.41666666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.75" customWidth="1"/>
-    <col min="14" max="14" width="10.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="10.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="11.9166666666667" customWidth="1"/>
-    <col min="17" max="17" width="8.25" customWidth="1"/>
-    <col min="18" max="18" width="10.0833333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2725,31 +2126,34 @@
         <v>85</v>
       </c>
       <c r="K1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L1" t="s">
         <v>86</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>87</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>88</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>89</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>90</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>91</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2777,29 +2181,32 @@
       <c r="I2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>100</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>10</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
         <v>98</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>14</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2827,29 +2234,32 @@
       <c r="I3" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L3">
         <v>8</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>100</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>101</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2877,29 +2287,32 @@
       <c r="I4" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>189</v>
+      </c>
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>100</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>104</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>6</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2927,30 +2340,33 @@
       <c r="I5" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>189</v>
+      </c>
+      <c r="L5">
         <v>10</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>200</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>25</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>106</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>6</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>7</v>
       </c>
-      <c r="R5" s="14"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="13"/>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2978,30 +2394,33 @@
       <c r="I6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>50</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
         <v>109</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>20</v>
       </c>
-      <c r="R6" s="14"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" s="13"/>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3029,30 +2448,33 @@
       <c r="I7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>189</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>5000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>50</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>112</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>6</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>20</v>
       </c>
-      <c r="R7" s="14"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" s="13"/>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3080,30 +2502,33 @@
       <c r="I8" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>189</v>
+      </c>
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>5000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>50</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>2</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>115</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>6</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>20</v>
       </c>
-      <c r="R8" s="14"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" s="13"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3131,30 +2556,33 @@
       <c r="I9" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L9">
         <v>12</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>12000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>80</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
         <v>118</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>6</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>7</v>
       </c>
-      <c r="R9" s="14"/>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9" s="13"/>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3182,30 +2610,33 @@
       <c r="I10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>189</v>
+      </c>
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>12000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>80</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>1</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>121</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>6</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>7</v>
       </c>
-      <c r="R10" s="14"/>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="S10" s="13"/>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3233,29 +2664,32 @@
       <c r="I11" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="s">
+        <v>189</v>
+      </c>
+      <c r="L11">
         <v>12</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>12000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>80</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>2</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>124</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>6</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3283,29 +2717,32 @@
       <c r="I12" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>189</v>
+      </c>
+      <c r="L12">
         <v>12</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>12000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>80</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>2</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>127</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>6</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3333,29 +2770,32 @@
       <c r="I13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>189</v>
+      </c>
+      <c r="L13">
         <v>12</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>20000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>100</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>124</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:19">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3383,29 +2823,32 @@
       <c r="I14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>189</v>
+      </c>
+      <c r="L14">
         <v>12</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>20000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>100</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
         <v>132</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>6</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:19">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3433,29 +2876,32 @@
       <c r="I15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>189</v>
+      </c>
+      <c r="L15">
         <v>12</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>20000</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>100</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>1</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>135</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>6</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3483,29 +2929,32 @@
       <c r="I16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="s">
+        <v>189</v>
+      </c>
+      <c r="L16">
         <v>12</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>20000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>100</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>1</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>138</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>6</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3533,29 +2982,32 @@
       <c r="I17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="s">
+        <v>189</v>
+      </c>
+      <c r="L17">
         <v>15</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>40000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>130</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>2</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>141</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>6</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3583,29 +3035,32 @@
       <c r="I18" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>189</v>
+      </c>
+      <c r="L18">
         <v>15</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>40000</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>130</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>1</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>144</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>6</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3633,29 +3088,32 @@
       <c r="I19" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19">
         <v>15</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>40000</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>130</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>2</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>141</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>6</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3683,29 +3141,32 @@
       <c r="I20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20">
         <v>15</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>40000</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>130</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
         <v>149</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>6</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3733,29 +3194,32 @@
       <c r="I21" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="s">
+        <v>189</v>
+      </c>
+      <c r="L21">
         <v>15</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>40000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>130</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>1</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>152</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>6</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3783,29 +3247,32 @@
       <c r="I22" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22">
         <v>15</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>40000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>130</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
         <v>149</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>6</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3833,79 +3300,68 @@
       <c r="I23" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="s">
+        <v>189</v>
+      </c>
+      <c r="L23">
         <v>15</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>40000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>130</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>2</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>157</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>6</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="9:17">
-      <c r="I24" s="12"/>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="9:17">
-      <c r="I25" s="12"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="9:17">
-      <c r="I26" s="12"/>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="9:17">
-      <c r="I27" s="12"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="9:9">
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="9:9">
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="9:9">
-      <c r="I30" s="12"/>
+    <row r="24" spans="1:18">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="R27" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3940,7 +3396,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
+    <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3972,7 +3428,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
+    <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4004,7 +3460,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4036,7 +3492,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
+    <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4068,7 +3524,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="1:11">
+    <row r="6" spans="1:11" ht="33" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4100,7 +3556,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4132,7 +3588,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:11">
+    <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4164,7 +3620,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:11">
+    <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4196,7 +3652,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:11">
+    <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4228,7 +3684,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:11">
+    <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4260,7 +3716,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
+    <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4292,7 +3748,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:11">
+    <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4324,7 +3780,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4356,7 +3812,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4385,7 +3841,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1" spans="1:11">
+    <row r="16" spans="1:11" ht="42" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4417,7 +3873,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:11">
+    <row r="17" spans="1:11" ht="30" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4449,7 +3905,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:11">
+    <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4481,7 +3937,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:9">
+    <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4510,7 +3966,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:9">
+    <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4539,7 +3995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:9">
+    <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4568,7 +4024,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:11">
+    <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4600,7 +4056,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:11">
+    <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4632,7 +4088,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:11">
+    <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4664,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:11">
+    <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4696,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:11">
+    <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4728,7 +4184,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:11">
+    <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -4760,7 +4216,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:11">
+    <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4792,7 +4248,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:11">
+    <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -4824,7 +4280,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:11">
+    <row r="30" spans="1:11" ht="30" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4856,7 +4312,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:9">
+    <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4885,7 +4341,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:9">
+    <row r="32" spans="1:11" ht="30" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4913,21 +4369,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5075,21 +4529,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5111,22 +4563,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5211,6 +4661,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="268">
   <si>
     <t>ID</t>
   </si>
@@ -259,7 +259,7 @@
     <t>VRaisingDeleteCardEffect</t>
   </si>
   <si>
-    <t>随机获得一张A卡</t>
+    <t>随机获得一张A类型卡</t>
   </si>
   <si>
     <t>VRaisingAddRandomCardEffect</t>
@@ -268,16 +268,16 @@
     <t>0.5,0.3,0.1,0,0,0</t>
   </si>
   <si>
-    <t>随机获得一张M卡</t>
-  </si>
-  <si>
-    <t>随机获得一张红温卡</t>
+    <t>随机获得一张M类型卡</t>
+  </si>
+  <si>
+    <t>随机获得一张红温相关卡</t>
   </si>
   <si>
     <t>5\</t>
   </si>
   <si>
-    <t>随机获得一张幽默卡</t>
+    <t>随机获得一张幽默相关卡</t>
   </si>
   <si>
     <t>Duration</t>
@@ -658,71 +658,6 @@
   </si>
   <si>
     <t>歌回成功事件</t>
-  </si>
-  <si>
-    <r>
-      <t>粉丝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，金钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，舰长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，获得一张卡</t>
-    </r>
-  </si>
-  <si>
-    <t>SingSuccess</t>
-  </si>
-  <si>
-    <t>游戏回成功事件</t>
   </si>
   <si>
     <r>
@@ -788,6 +723,12 @@
       </rPr>
       <t>，获得一张卡</t>
     </r>
+  </si>
+  <si>
+    <t>SingSuccess</t>
+  </si>
+  <si>
+    <t>游戏回成功事件</t>
   </si>
   <si>
     <t>gameSuccess</t>
@@ -2650,7 +2591,6 @@
       <c r="D38" t="s">
         <v>58</v>
       </c>
-      <c r="E38"/>
       <c r="F38" t="s">
         <v>59</v>
       </c>
@@ -4490,7 +4430,7 @@
         <v>209</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>183</v>
@@ -4511,7 +4451,7 @@
         <v>184</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4519,10 +4459,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>183</v>
@@ -4551,10 +4491,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4580,10 +4520,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4609,10 +4549,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4638,10 +4578,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>183</v>
@@ -4662,7 +4602,7 @@
         <v>184</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4670,10 +4610,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>183</v>
@@ -4694,7 +4634,7 @@
         <v>184</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4702,10 +4642,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>183</v>
@@ -4723,7 +4663,7 @@
         <v>172</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4734,10 +4674,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>183</v>
@@ -4755,7 +4695,7 @@
         <v>172</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4766,13 +4706,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -4784,13 +4724,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="K26" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4798,13 +4738,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -4816,13 +4756,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4830,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -4848,13 +4788,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I28" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -4862,13 +4802,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -4880,13 +4820,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -4894,13 +4834,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -4912,13 +4852,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="I30" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -4926,13 +4866,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -4944,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -4955,7 +4895,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>204</v>
@@ -5017,13 +4957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" t="s">
         <v>244</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>245</v>
-      </c>
-      <c r="E2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5031,13 +4971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" t="s">
         <v>247</v>
-      </c>
-      <c r="D3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5045,13 +4985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
         <v>249</v>
       </c>
-      <c r="D4" t="s">
-        <v>250</v>
-      </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5059,13 +4999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" t="s">
         <v>250</v>
-      </c>
-      <c r="E5" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5073,13 +5013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5087,13 +5027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" t="s">
         <v>253</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>254</v>
-      </c>
-      <c r="E7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5101,13 +5041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D8" t="s">
         <v>253</v>
       </c>
-      <c r="D8" t="s">
-        <v>254</v>
-      </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5115,13 +5055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" t="s">
         <v>257</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>258</v>
-      </c>
-      <c r="E9" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5129,13 +5069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" t="s">
         <v>260</v>
-      </c>
-      <c r="D10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E10" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5162,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" t="s">
         <v>263</v>
-      </c>
-      <c r="E1" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -5208,10 +5148,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" t="s">
         <v>265</v>
-      </c>
-      <c r="F1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5225,7 +5165,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5245,7 +5185,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5265,7 +5205,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E4">
         <v>5</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -15,7 +15,7 @@
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$R$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$S$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -274,9 +274,6 @@
     <t>随机获得一张红温相关卡</t>
   </si>
   <si>
-    <t>5\</t>
-  </si>
-  <si>
     <t>随机获得一张幽默相关卡</t>
   </si>
   <si>
@@ -296,6 +293,9 @@
   </si>
   <si>
     <t>PlacingCondition</t>
+  </si>
+  <si>
+    <t>直播前对话</t>
   </si>
   <si>
     <t>TurnCount</t>
@@ -642,7 +642,7 @@
     <t>粉丝+100，金钱+15，从卡组中删除一张牌</t>
   </si>
   <si>
-    <t>Edit</t>
+    <t>Work2</t>
   </si>
   <si>
     <t>购物</t>
@@ -2655,11 +2655,11 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
         <v>79</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
       </c>
       <c r="D43" t="s">
         <v>75</v>
@@ -2677,7 +2677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
@@ -2688,17 +2688,18 @@
     <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
     <col min="9" max="9" width="8.15" customWidth="1"/>
     <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="3.26666666666667" customWidth="1"/>
-    <col min="12" max="12" width="6.41666666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.75" customWidth="1"/>
-    <col min="14" max="14" width="10.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="10.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="11.9166666666667" customWidth="1"/>
-    <col min="17" max="17" width="8.25" customWidth="1"/>
-    <col min="18" max="18" width="10.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="3.26666666666667" customWidth="1"/>
+    <col min="13" max="13" width="6.41666666666667" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="10.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="10.6666666666667" customWidth="1"/>
+    <col min="17" max="17" width="11.9166666666667" customWidth="1"/>
+    <col min="18" max="18" width="8.25" customWidth="1"/>
+    <col min="19" max="19" width="10.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2712,49 +2713,52 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>84</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>85</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>86</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>87</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>88</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>89</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>90</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>91</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>93</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2782,29 +2786,29 @@
       <c r="I2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>100</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>10</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
         <v>99</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>14</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2832,29 +2836,29 @@
       <c r="I3" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>8</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>100</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>102</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2882,29 +2886,29 @@
       <c r="I4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>100</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>105</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>6</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2932,30 +2936,30 @@
       <c r="I5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>10</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>200</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>25</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>107</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>6</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>7</v>
       </c>
-      <c r="R5" s="14"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="14"/>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2983,30 +2987,30 @@
       <c r="I6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>50</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
         <v>110</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>20</v>
       </c>
-      <c r="R6" s="14"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" s="14"/>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3034,30 +3038,30 @@
       <c r="I7" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>5000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>50</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>113</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>6</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>20</v>
       </c>
-      <c r="R7" s="14"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" s="14"/>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3085,30 +3089,30 @@
       <c r="I8" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>5000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>50</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>2</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>116</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>6</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>20</v>
       </c>
-      <c r="R8" s="14"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" s="14"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3136,30 +3140,30 @@
       <c r="I9" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>12</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>12000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>80</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
         <v>119</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>6</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>7</v>
       </c>
-      <c r="R9" s="14"/>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9" s="14"/>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3187,30 +3191,30 @@
       <c r="I10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>12000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>80</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>1</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>122</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>6</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>7</v>
       </c>
-      <c r="R10" s="14"/>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="S10" s="14"/>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3238,29 +3242,29 @@
       <c r="I11" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>12</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>12000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>80</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>2</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>125</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>6</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3288,29 +3292,29 @@
       <c r="I12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>12</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>12000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>80</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>2</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>128</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>6</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3338,29 +3342,29 @@
       <c r="I13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>12</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>20000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>100</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>125</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3388,29 +3392,29 @@
       <c r="I14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>12</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>20000</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>100</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
         <v>133</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>6</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3438,29 +3442,29 @@
       <c r="I15" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>12</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>20000</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>100</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>1</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>136</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>6</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3488,29 +3492,29 @@
       <c r="I16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>12</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>20000</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>100</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>1</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>139</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>6</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3538,29 +3542,29 @@
       <c r="I17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>15</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>40000</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>130</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>2</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>142</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>6</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3588,29 +3592,29 @@
       <c r="I18" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>15</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>40000</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>130</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>1</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>145</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>6</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3638,29 +3642,29 @@
       <c r="I19" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>15</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>40000</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>130</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>2</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>142</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>6</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3688,29 +3692,29 @@
       <c r="I20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>15</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>40000</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>130</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
         <v>150</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>6</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3738,29 +3742,29 @@
       <c r="I21" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>15</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>40000</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>130</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>1</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>153</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>6</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3788,29 +3792,29 @@
       <c r="I22" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>15</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>40000</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>130</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
         <v>150</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>6</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3838,43 +3842,43 @@
       <c r="I23" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>15</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>40000</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>130</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>2</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>158</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>6</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="9:17">
+    <row r="24" spans="9:18">
       <c r="I24" s="12"/>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="9:17">
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="9:18">
       <c r="I25" s="12"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="9:17">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="9:18">
       <c r="I26" s="12"/>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="9:17">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="9:18">
       <c r="I27" s="12"/>
-      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
     </row>
     <row r="28" spans="9:9">
       <c r="I28" s="12"/>
@@ -3924,22 +3928,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" t="s">
         <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>86</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>159</v>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB6A128-3580-4A80-AAC0-40FF0E23745F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AECD525-ADBA-4DAE-A7D1-79794551CCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$S$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$V$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="270">
   <si>
     <t>ID</t>
   </si>
@@ -318,9 +318,6 @@
   </si>
   <si>
     <t>FailEvent</t>
-  </si>
-  <si>
-    <t>Conditions</t>
   </si>
   <si>
     <t>歌回</t>
@@ -907,6 +904,15 @@
   </si>
   <si>
     <t>VRaisingEnterStoreEffect</t>
+  </si>
+  <si>
+    <t>ExtraTarget</t>
+  </si>
+  <si>
+    <t>AttributeBonus</t>
+  </si>
+  <si>
+    <t>7,4,4</t>
   </si>
 </sst>
 </file>
@@ -2060,10 +2066,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" t="s">
         <v>266</v>
-      </c>
-      <c r="D44" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2086,15 +2092,17 @@
     <col min="10" max="11" width="15.42578125" customWidth="1"/>
     <col min="12" max="12" width="3.28515625" customWidth="1"/>
     <col min="13" max="13" width="6.42578125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" customWidth="1"/>
-    <col min="18" max="18" width="8.28515625" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" customWidth="1"/>
+    <col min="20" max="21" width="14.5703125" customWidth="1"/>
+    <col min="22" max="22" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2126,7 +2134,7 @@
         <v>85</v>
       </c>
       <c r="K1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L1" t="s">
         <v>86</v>
@@ -2135,54 +2143,58 @@
         <v>87</v>
       </c>
       <c r="N1" t="s">
+        <v>267</v>
+      </c>
+      <c r="O1" t="s">
         <v>88</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>89</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>90</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>91</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>92</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" t="s">
+        <v>268</v>
+      </c>
+      <c r="V1" s="12"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2191,51 +2203,57 @@
         <v>100</v>
       </c>
       <c r="N2">
+        <v>200</v>
+      </c>
+      <c r="O2">
         <v>10</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="1">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" s="1">
         <v>14</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2244,51 +2262,57 @@
         <v>100</v>
       </c>
       <c r="N3">
+        <v>200</v>
+      </c>
+      <c r="O3">
         <v>10</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q3">
+      <c r="Q3" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2297,51 +2321,57 @@
         <v>100</v>
       </c>
       <c r="N4">
+        <v>200</v>
+      </c>
+      <c r="O4">
         <v>10</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="P4" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q4">
+      <c r="Q4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R4">
         <v>6</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -2350,52 +2380,59 @@
         <v>200</v>
       </c>
       <c r="N5">
+        <v>300</v>
+      </c>
+      <c r="O5">
         <v>25</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q5">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5">
         <v>6</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>7</v>
       </c>
-      <c r="S5" s="13"/>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="13"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
         <v>107</v>
       </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -2404,52 +2441,59 @@
         <v>5000</v>
       </c>
       <c r="N6">
+        <v>6000</v>
+      </c>
+      <c r="O6">
         <v>50</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q6">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6">
         <v>6</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>20</v>
       </c>
-      <c r="S6" s="13"/>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="V6" s="13"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
         <v>110</v>
       </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -2458,52 +2502,59 @@
         <v>5000</v>
       </c>
       <c r="N7">
+        <v>6000</v>
+      </c>
+      <c r="O7">
         <v>50</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q7">
+      <c r="Q7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7">
         <v>6</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>20</v>
       </c>
-      <c r="S7" s="13"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7" s="1"/>
+      <c r="V7" s="13"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" t="s">
         <v>113</v>
       </c>
-      <c r="C8" t="s">
-        <v>114</v>
-      </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -2512,52 +2563,59 @@
         <v>5000</v>
       </c>
       <c r="N8">
+        <v>6000</v>
+      </c>
+      <c r="O8">
         <v>50</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2</v>
       </c>
-      <c r="P8" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q8">
+      <c r="Q8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R8">
         <v>6</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>20</v>
       </c>
-      <c r="S8" s="13"/>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="V8" s="13"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
         <v>116</v>
       </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -2566,52 +2624,58 @@
         <v>12000</v>
       </c>
       <c r="N9">
+        <v>22000</v>
+      </c>
+      <c r="O9">
         <v>80</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q9">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>117</v>
+      </c>
+      <c r="R9">
         <v>6</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>7</v>
       </c>
-      <c r="S9" s="13"/>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="V9" s="13"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
         <v>119</v>
       </c>
-      <c r="C10" t="s">
-        <v>120</v>
-      </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -2620,52 +2684,58 @@
         <v>12000</v>
       </c>
       <c r="N10">
+        <v>22000</v>
+      </c>
+      <c r="O10">
         <v>80</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>1</v>
       </c>
-      <c r="P10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q10">
+      <c r="Q10" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10">
         <v>6</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>7</v>
       </c>
-      <c r="S10" s="13"/>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="V10" s="13"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" t="s">
         <v>122</v>
       </c>
-      <c r="C11" t="s">
-        <v>123</v>
-      </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -2674,51 +2744,57 @@
         <v>12000</v>
       </c>
       <c r="N11">
+        <v>22000</v>
+      </c>
+      <c r="O11">
         <v>80</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>2</v>
       </c>
-      <c r="P11" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q11">
+      <c r="Q11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11">
         <v>6</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" t="s">
         <v>125</v>
       </c>
-      <c r="C12" t="s">
-        <v>126</v>
-      </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -2727,51 +2803,57 @@
         <v>12000</v>
       </c>
       <c r="N12">
+        <v>22000</v>
+      </c>
+      <c r="O12">
         <v>80</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>2</v>
       </c>
-      <c r="P12" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q12">
+      <c r="Q12" t="s">
+        <v>126</v>
+      </c>
+      <c r="R12">
         <v>6</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" t="s">
         <v>128</v>
       </c>
-      <c r="C13" t="s">
-        <v>129</v>
-      </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -2780,51 +2862,57 @@
         <v>20000</v>
       </c>
       <c r="N13">
+        <v>30000</v>
+      </c>
+      <c r="O13">
         <v>100</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>2</v>
       </c>
-      <c r="P13" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q13">
+      <c r="Q13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13">
         <v>6</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
         <v>130</v>
       </c>
-      <c r="C14" t="s">
-        <v>131</v>
-      </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -2833,51 +2921,57 @@
         <v>20000</v>
       </c>
       <c r="N14">
+        <v>30000</v>
+      </c>
+      <c r="O14">
         <v>100</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q14">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>131</v>
+      </c>
+      <c r="R14">
         <v>6</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s">
         <v>133</v>
       </c>
-      <c r="C15" t="s">
-        <v>134</v>
-      </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -2886,51 +2980,57 @@
         <v>20000</v>
       </c>
       <c r="N15">
+        <v>30000</v>
+      </c>
+      <c r="O15">
         <v>100</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>1</v>
       </c>
-      <c r="P15" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q15">
+      <c r="Q15" t="s">
+        <v>134</v>
+      </c>
+      <c r="R15">
         <v>6</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
         <v>136</v>
       </c>
-      <c r="C16" t="s">
-        <v>137</v>
-      </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -2939,51 +3039,57 @@
         <v>20000</v>
       </c>
       <c r="N16">
+        <v>30000</v>
+      </c>
+      <c r="O16">
         <v>100</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>1</v>
       </c>
-      <c r="P16" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q16">
+      <c r="Q16" t="s">
+        <v>137</v>
+      </c>
+      <c r="R16">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="T16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" t="s">
         <v>139</v>
       </c>
-      <c r="C17" t="s">
-        <v>140</v>
-      </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="K17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L17">
         <v>15</v>
@@ -2992,51 +3098,57 @@
         <v>40000</v>
       </c>
       <c r="N17">
+        <v>50000</v>
+      </c>
+      <c r="O17">
         <v>130</v>
       </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-      <c r="P17" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q17">
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>269</v>
+      </c>
+      <c r="R17">
         <v>6</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="T17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" t="s">
         <v>142</v>
       </c>
-      <c r="C18" t="s">
-        <v>143</v>
-      </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -3045,51 +3157,57 @@
         <v>40000</v>
       </c>
       <c r="N18">
+        <v>50000</v>
+      </c>
+      <c r="O18">
         <v>130</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>1</v>
       </c>
-      <c r="P18" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18">
+      <c r="Q18" t="s">
+        <v>143</v>
+      </c>
+      <c r="R18">
         <v>6</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="T18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" t="s">
         <v>145</v>
       </c>
-      <c r="C19" t="s">
-        <v>146</v>
-      </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L19">
         <v>15</v>
@@ -3098,51 +3216,57 @@
         <v>40000</v>
       </c>
       <c r="N19">
+        <v>50000</v>
+      </c>
+      <c r="O19">
         <v>130</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2</v>
       </c>
-      <c r="P19" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q19">
+      <c r="Q19" t="s">
+        <v>140</v>
+      </c>
+      <c r="R19">
         <v>6</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="T19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="C20" t="s">
-        <v>148</v>
-      </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L20">
         <v>15</v>
@@ -3151,51 +3275,57 @@
         <v>40000</v>
       </c>
       <c r="N20">
+        <v>50000</v>
+      </c>
+      <c r="O20">
         <v>130</v>
       </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q20">
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>148</v>
+      </c>
+      <c r="R20">
         <v>6</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="T20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" t="s">
         <v>150</v>
       </c>
-      <c r="C21" t="s">
-        <v>151</v>
-      </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21">
         <v>15</v>
@@ -3204,51 +3334,57 @@
         <v>40000</v>
       </c>
       <c r="N21">
+        <v>50000</v>
+      </c>
+      <c r="O21">
         <v>130</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>1</v>
       </c>
-      <c r="P21" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q21">
+      <c r="Q21" t="s">
+        <v>151</v>
+      </c>
+      <c r="R21">
         <v>6</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="T21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" t="s">
         <v>153</v>
       </c>
-      <c r="C22" t="s">
-        <v>154</v>
-      </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L22">
         <v>15</v>
@@ -3257,51 +3393,57 @@
         <v>40000</v>
       </c>
       <c r="N22">
+        <v>50000</v>
+      </c>
+      <c r="O22">
         <v>130</v>
       </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q22">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>148</v>
+      </c>
+      <c r="R22">
         <v>6</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="T22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
         <v>155</v>
       </c>
-      <c r="C23" t="s">
-        <v>156</v>
-      </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L23">
         <v>15</v>
@@ -3310,36 +3452,51 @@
         <v>40000</v>
       </c>
       <c r="N23">
+        <v>50000</v>
+      </c>
+      <c r="O23">
         <v>130</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>2</v>
       </c>
-      <c r="P23" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q23">
+      <c r="Q23" t="s">
+        <v>156</v>
+      </c>
+      <c r="R23">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="R24" s="1"/>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="R27" s="1"/>
+      <c r="T23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3393,7 +3550,7 @@
         <v>85</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
@@ -3401,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3413,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3422,10 +3579,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -3433,10 +3590,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3445,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -3454,10 +3611,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -3465,10 +3622,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -3477,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -3486,10 +3643,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
@@ -3497,31 +3654,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="K5" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="33" customHeight="1">
@@ -3529,31 +3686,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -3561,31 +3718,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -3593,31 +3750,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="K8" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
@@ -3625,31 +3782,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
@@ -3657,31 +3814,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -3689,31 +3846,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -3721,31 +3878,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -3753,31 +3910,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I13" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -3785,31 +3942,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -3817,28 +3974,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="42" customHeight="1">
@@ -3846,31 +4003,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -3878,31 +4035,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -3910,31 +4067,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -3942,10 +4099,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -3954,7 +4111,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -3963,7 +4120,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
@@ -3971,10 +4128,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -3983,7 +4140,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -3992,7 +4149,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
@@ -4000,10 +4157,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4012,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4021,7 +4178,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
@@ -4029,31 +4186,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -4061,31 +4218,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
@@ -4093,28 +4250,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>223</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4125,28 +4282,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4157,31 +4314,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="K26" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
@@ -4189,31 +4346,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
@@ -4221,31 +4378,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
@@ -4253,31 +4410,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1">
@@ -4285,31 +4442,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1">
@@ -4317,28 +4474,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1">
@@ -4346,25 +4503,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I32" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4406,13 +4563,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" t="s">
         <v>241</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>242</v>
-      </c>
-      <c r="E2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4420,13 +4577,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" t="s">
         <v>244</v>
-      </c>
-      <c r="D3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4434,13 +4591,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" t="s">
         <v>246</v>
       </c>
-      <c r="D4" t="s">
-        <v>247</v>
-      </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4448,13 +4605,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" t="s">
         <v>247</v>
-      </c>
-      <c r="E5" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4462,13 +4619,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4476,13 +4633,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" t="s">
         <v>250</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>251</v>
-      </c>
-      <c r="E7" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4490,13 +4647,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8" t="s">
         <v>250</v>
       </c>
-      <c r="D8" t="s">
-        <v>251</v>
-      </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4504,13 +4661,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
         <v>254</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>255</v>
-      </c>
-      <c r="E9" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4518,13 +4675,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" t="s">
         <v>257</v>
-      </c>
-      <c r="D10" t="s">
-        <v>255</v>
-      </c>
-      <c r="E10" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4549,16 +4706,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" t="s">
         <v>260</v>
-      </c>
-      <c r="E1" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4593,10 +4750,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" t="s">
         <v>262</v>
-      </c>
-      <c r="F1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4610,7 +4767,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4630,7 +4787,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4650,13 +4807,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102F328D-F77B-48E1-BB06-9E2C18F7419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -26,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -295,9 +299,6 @@
     <t>PlacingCondition</t>
   </si>
   <si>
-    <t>直播前对话</t>
-  </si>
-  <si>
     <t>TurnCount</t>
   </si>
   <si>
@@ -319,9 +320,6 @@
     <t>FailEvent</t>
   </si>
   <si>
-    <t>Conditions</t>
-  </si>
-  <si>
     <t>歌回</t>
   </si>
   <si>
@@ -575,9 +573,6 @@
   </si>
   <si>
     <t>体力+70,从卡组中选择一张卡牌删除</t>
-  </si>
-  <si>
-    <t>DayOff</t>
   </si>
   <si>
     <t>直播成功</t>
@@ -904,22 +899,49 @@
   <si>
     <t>VPhaseEndingEventCondition</t>
   </si>
+  <si>
+    <t>ExtraTarget</t>
+  </si>
+  <si>
+    <t>AttributeBonus</t>
+  </si>
+  <si>
+    <t>7,4,4</t>
+  </si>
+  <si>
+    <t>KPI1</t>
+  </si>
+  <si>
+    <t>KPI2</t>
+  </si>
+  <si>
+    <t>KPI3</t>
+  </si>
+  <si>
+    <t>Stream,3</t>
+  </si>
+  <si>
+    <t>Coop,5</t>
+  </si>
+  <si>
+    <t>Work,4</t>
+  </si>
+  <si>
+    <t>Outside,6</t>
+  </si>
+  <si>
+    <t>Dayoff</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -930,157 +952,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1113,7 +991,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1135,194 +1013,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1330,253 +1022,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1611,7 +1061,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1619,70 +1068,26 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
-      <color rgb="00E3A7F7"/>
-      <color rgb="00F567ED"/>
-      <color rgb="00DEBA2C"/>
-      <color rgb="00FD460D"/>
+      <color rgb="FF0BF30B"/>
+      <color rgb="FFE3A7F7"/>
+      <color rgb="FFF567ED"/>
+      <color rgb="FFDEBA2C"/>
+      <color rgb="FFFD460D"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1940,22 +1345,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2089,7 +1494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2103,7 +1508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2117,7 +1522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2301,7 +1706,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2366,7 +1771,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2400,7 +1805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2595,7 +2000,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2670,36 +2075,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:W27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.41666666666667" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="8.15" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="10.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="3.26666666666667" customWidth="1"/>
-    <col min="13" max="13" width="6.41666666666667" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="10.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="10.6666666666667" customWidth="1"/>
-    <col min="17" max="17" width="11.9166666666667" customWidth="1"/>
-    <col min="18" max="18" width="8.25" customWidth="1"/>
-    <col min="19" max="19" width="10.0833333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2731,60 +2135,75 @@
         <v>85</v>
       </c>
       <c r="K1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L1" t="s">
         <v>86</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>87</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>265</v>
+      </c>
+      <c r="O1" t="s">
         <v>88</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>89</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>90</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>91</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
+        <v>266</v>
+      </c>
+      <c r="U1" t="s">
+        <v>268</v>
+      </c>
+      <c r="V1" t="s">
+        <v>269</v>
+      </c>
+      <c r="W1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>93</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>96</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>98</v>
+      <c r="K2" t="s">
+        <v>188</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2793,48 +2212,57 @@
         <v>100</v>
       </c>
       <c r="N2">
+        <v>200</v>
+      </c>
+      <c r="O2">
         <v>10</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q2" s="1">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2">
         <v>14</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="T2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>188</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2843,48 +2271,57 @@
         <v>100</v>
       </c>
       <c r="N3">
+        <v>200</v>
+      </c>
+      <c r="O3">
         <v>10</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3">
+      <c r="Q3" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="T3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K4" t="s">
+        <v>188</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2893,48 +2330,57 @@
         <v>100</v>
       </c>
       <c r="N4">
+        <v>200</v>
+      </c>
+      <c r="O4">
         <v>10</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="P4" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q4">
+      <c r="Q4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R4">
         <v>6</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>98</v>
+      <c r="K5" t="s">
+        <v>188</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -2943,49 +2389,57 @@
         <v>200</v>
       </c>
       <c r="N5">
+        <v>300</v>
+      </c>
+      <c r="O5">
         <v>25</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q5">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" s="1">
         <v>6</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="13">
         <v>7</v>
       </c>
-      <c r="S5" s="14"/>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>98</v>
+      <c r="K6" t="s">
+        <v>188</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -2994,49 +2448,63 @@
         <v>5000</v>
       </c>
       <c r="N6">
+        <v>6000</v>
+      </c>
+      <c r="O6">
         <v>50</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q6">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6" s="1">
         <v>6</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="13">
         <v>20</v>
       </c>
-      <c r="S6" s="14"/>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6" t="s">
+        <v>271</v>
+      </c>
+      <c r="V6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K7" t="s">
+        <v>188</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -3045,49 +2513,63 @@
         <v>5000</v>
       </c>
       <c r="N7">
+        <v>6000</v>
+      </c>
+      <c r="O7">
         <v>50</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7">
+      <c r="Q7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="1">
         <v>6</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="13">
         <v>20</v>
       </c>
-      <c r="S7" s="14"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7" t="s">
+        <v>273</v>
+      </c>
+      <c r="V7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K8" t="s">
+        <v>188</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -3096,49 +2578,57 @@
         <v>5000</v>
       </c>
       <c r="N8">
+        <v>6000</v>
+      </c>
+      <c r="O8">
         <v>50</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2</v>
       </c>
-      <c r="P8" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q8">
+      <c r="Q8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R8" s="1">
         <v>6</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="13">
         <v>20</v>
       </c>
-      <c r="S8" s="14"/>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>98</v>
+      <c r="K9" t="s">
+        <v>188</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -3147,49 +2637,57 @@
         <v>12000</v>
       </c>
       <c r="N9">
+        <v>22000</v>
+      </c>
+      <c r="O9">
         <v>80</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q9">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>117</v>
+      </c>
+      <c r="R9">
         <v>6</v>
       </c>
-      <c r="R9">
+      <c r="S9" s="13">
         <v>7</v>
       </c>
-      <c r="S9" s="14"/>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K10" t="s">
+        <v>188</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -3198,49 +2696,57 @@
         <v>12000</v>
       </c>
       <c r="N10">
+        <v>22000</v>
+      </c>
+      <c r="O10">
         <v>80</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>1</v>
       </c>
-      <c r="P10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q10">
+      <c r="Q10" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10">
         <v>6</v>
       </c>
-      <c r="R10">
+      <c r="S10" s="13">
         <v>7</v>
       </c>
-      <c r="S10" s="14"/>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="T10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K11" t="s">
+        <v>188</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -3249,48 +2755,57 @@
         <v>12000</v>
       </c>
       <c r="N11">
+        <v>22000</v>
+      </c>
+      <c r="O11">
         <v>80</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>2</v>
       </c>
-      <c r="P11" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q11">
+      <c r="Q11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11">
         <v>6</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="T11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K12" t="s">
+        <v>188</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -3299,48 +2814,57 @@
         <v>12000</v>
       </c>
       <c r="N12">
+        <v>22000</v>
+      </c>
+      <c r="O12">
         <v>80</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>2</v>
       </c>
-      <c r="P12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q12">
+      <c r="Q12" t="s">
+        <v>126</v>
+      </c>
+      <c r="R12">
         <v>6</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="T12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K13" t="s">
+        <v>188</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -3349,48 +2873,57 @@
         <v>20000</v>
       </c>
       <c r="N13">
+        <v>30000</v>
+      </c>
+      <c r="O13">
         <v>100</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>2</v>
       </c>
-      <c r="P13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q13">
+      <c r="Q13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13">
         <v>6</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="T13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>98</v>
+      <c r="K14" t="s">
+        <v>188</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -3399,48 +2932,57 @@
         <v>20000</v>
       </c>
       <c r="N14">
+        <v>30000</v>
+      </c>
+      <c r="O14">
         <v>100</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q14">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>131</v>
+      </c>
+      <c r="R14">
         <v>6</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="T14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K15" t="s">
+        <v>188</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -3449,48 +2991,57 @@
         <v>20000</v>
       </c>
       <c r="N15">
+        <v>30000</v>
+      </c>
+      <c r="O15">
         <v>100</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>1</v>
       </c>
-      <c r="P15" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q15">
+      <c r="Q15" t="s">
+        <v>134</v>
+      </c>
+      <c r="R15">
         <v>6</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="T15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K16" t="s">
+        <v>188</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -3499,48 +3050,57 @@
         <v>20000</v>
       </c>
       <c r="N16">
+        <v>30000</v>
+      </c>
+      <c r="O16">
         <v>100</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>1</v>
       </c>
-      <c r="P16" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q16">
+      <c r="Q16" t="s">
+        <v>137</v>
+      </c>
+      <c r="R16">
         <v>6</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="T16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>104</v>
+      <c r="K17" t="s">
+        <v>188</v>
       </c>
       <c r="L17">
         <v>15</v>
@@ -3549,48 +3109,57 @@
         <v>40000</v>
       </c>
       <c r="N17">
+        <v>50000</v>
+      </c>
+      <c r="O17">
         <v>130</v>
       </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-      <c r="P17" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q17">
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>267</v>
+      </c>
+      <c r="R17">
         <v>6</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="T17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K18" t="s">
+        <v>188</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -3599,48 +3168,57 @@
         <v>40000</v>
       </c>
       <c r="N18">
+        <v>50000</v>
+      </c>
+      <c r="O18">
         <v>130</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>1</v>
       </c>
-      <c r="P18" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q18">
+      <c r="Q18" t="s">
+        <v>143</v>
+      </c>
+      <c r="R18">
         <v>6</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="T18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K19" t="s">
+        <v>188</v>
       </c>
       <c r="L19">
         <v>15</v>
@@ -3649,48 +3227,57 @@
         <v>40000</v>
       </c>
       <c r="N19">
+        <v>50000</v>
+      </c>
+      <c r="O19">
         <v>130</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2</v>
       </c>
-      <c r="P19" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q19">
+      <c r="Q19" t="s">
+        <v>140</v>
+      </c>
+      <c r="R19">
         <v>6</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="T19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>98</v>
+      <c r="K20" t="s">
+        <v>188</v>
       </c>
       <c r="L20">
         <v>15</v>
@@ -3699,48 +3286,57 @@
         <v>40000</v>
       </c>
       <c r="N20">
+        <v>50000</v>
+      </c>
+      <c r="O20">
         <v>130</v>
       </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q20">
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>148</v>
+      </c>
+      <c r="R20">
         <v>6</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="T20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="K21" t="s">
+        <v>188</v>
       </c>
       <c r="L21">
         <v>15</v>
@@ -3749,48 +3345,57 @@
         <v>40000</v>
       </c>
       <c r="N21">
+        <v>50000</v>
+      </c>
+      <c r="O21">
         <v>130</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>1</v>
       </c>
-      <c r="P21" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q21">
+      <c r="Q21" t="s">
+        <v>151</v>
+      </c>
+      <c r="R21">
         <v>6</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="T21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>98</v>
+      <c r="K22" t="s">
+        <v>188</v>
       </c>
       <c r="L22">
         <v>15</v>
@@ -3799,48 +3404,57 @@
         <v>40000</v>
       </c>
       <c r="N22">
+        <v>50000</v>
+      </c>
+      <c r="O22">
         <v>130</v>
       </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q22">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>148</v>
+      </c>
+      <c r="R22">
         <v>6</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="T22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="K23" t="s">
+        <v>188</v>
       </c>
       <c r="L23">
         <v>15</v>
@@ -3849,72 +3463,63 @@
         <v>40000</v>
       </c>
       <c r="N23">
+        <v>50000</v>
+      </c>
+      <c r="O23">
         <v>130</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>2</v>
       </c>
-      <c r="P23" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q23">
+      <c r="Q23" t="s">
+        <v>156</v>
+      </c>
+      <c r="R23">
         <v>6</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="9:18">
-      <c r="I24" s="12"/>
+      <c r="T23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="9:18">
-      <c r="I25" s="12"/>
+    <row r="25" spans="1:20">
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="9:18">
-      <c r="I26" s="12"/>
+    <row r="26" spans="1:20">
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="9:18">
-      <c r="I27" s="12"/>
+    <row r="27" spans="1:20">
       <c r="R27" s="1"/>
-    </row>
-    <row r="28" spans="9:9">
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="9:9">
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="9:9">
-      <c r="I30" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3946,18 +3551,18 @@
         <v>85</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3966,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3975,21 +3580,21 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:11">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3998,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -4007,21 +3612,21 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:11">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -4030,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -4039,466 +3644,466 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:11">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1" spans="1:11">
+    </row>
+    <row r="6" spans="1:11" ht="33" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I9" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1" spans="1:11">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="42" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4507,7 +4112,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4516,18 +4121,18 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4536,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4545,18 +4150,18 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4565,7 +4170,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4574,369 +4179,367 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:11">
+    <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:11">
+    <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:11">
+    </row>
+    <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I27" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:11">
+    </row>
+    <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:11">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4961,13 +4564,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4975,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" t="s">
         <v>244</v>
-      </c>
-      <c r="E3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4989,13 +4592,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5003,13 +4606,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5017,13 +4620,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5031,13 +4634,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5045,13 +4648,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" t="s">
         <v>252</v>
-      </c>
-      <c r="D8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E8" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5059,13 +4662,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5073,32 +4676,30 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" t="s">
         <v>257</v>
-      </c>
-      <c r="E10" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.08333333333333" customWidth="1"/>
-    <col min="2" max="2" width="6.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
-    <col min="4" max="4" width="5.66666666666667" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5106,36 +4707,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.425" customWidth="1"/>
-    <col min="3" max="3" width="22.8583333333333" customWidth="1"/>
-    <col min="4" max="4" width="31.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="23.425" customWidth="1"/>
-    <col min="6" max="6" width="9.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5152,10 +4751,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5169,7 +4768,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5189,7 +4788,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5209,17 +4808,16 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="289">
   <si>
     <t>ID</t>
   </si>
@@ -277,6 +277,48 @@
     <t>随机获得一张幽默相关卡</t>
   </si>
   <si>
+    <t>选择一张高稀有度卡牌获得</t>
+  </si>
+  <si>
+    <t>0,0.7,0.3,0,0,0</t>
+  </si>
+  <si>
+    <t>选择一张卡变成随机卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingReplaceCardEffect</t>
+  </si>
+  <si>
+    <t>0.2,0.6,0.2,0,0,0</t>
+  </si>
+  <si>
+    <t>获得一张强化过的卡牌</t>
+  </si>
+  <si>
+    <t>0.5,0.4,0.1,1,1,1</t>
+  </si>
+  <si>
+    <t>商店商品价格-25%</t>
+  </si>
+  <si>
+    <t>VRaisingStoreGlobalDiscountEffect</t>
+  </si>
+  <si>
+    <t>进入商店</t>
+  </si>
+  <si>
+    <t>VRaisingEnterStoreEffect</t>
+  </si>
+  <si>
+    <t>随机升级一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeRandomCardEffect</t>
+  </si>
+  <si>
+    <t>0.33,0.33,0.33</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -332,6 +374,9 @@
   </si>
   <si>
     <t>#FF2160</t>
+  </si>
+  <si>
+    <t>Livestart</t>
   </si>
   <si>
     <t>4,2,2</t>
@@ -655,6 +700,9 @@
   </si>
   <si>
     <t>#0BF30B</t>
+  </si>
+  <si>
+    <t>Store</t>
   </si>
   <si>
     <t>歌回成功事件</t>
@@ -725,15 +773,9 @@
     </r>
   </si>
   <si>
-    <t>SingSuccess</t>
-  </si>
-  <si>
     <t>游戏回成功事件</t>
   </si>
   <si>
-    <t>gameSuccess</t>
-  </si>
-  <si>
     <t>杂谈回成功事件</t>
   </si>
   <si>
@@ -761,7 +803,7 @@
     <t>第一阶段失败</t>
   </si>
   <si>
-    <t>Graduation_1</t>
+    <t>Graduation</t>
   </si>
   <si>
     <t>毕业2</t>
@@ -779,12 +821,18 @@
     <t>#D1CECE</t>
   </si>
   <si>
+    <t>phase3</t>
+  </si>
+  <si>
     <t>结局阶段开始</t>
   </si>
   <si>
     <t>#D2CECE</t>
   </si>
   <si>
+    <t>phase4</t>
+  </si>
+  <si>
     <t>雪王好感度增加事件</t>
   </si>
   <si>
@@ -828,6 +876,21 @@
   </si>
   <si>
     <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>Money</t>
+  </si>
+  <si>
+    <t>Lamian</t>
+  </si>
+  <si>
+    <t>段位挑战结局</t>
+  </si>
+  <si>
+    <t>游戏力结局</t>
+  </si>
+  <si>
+    <t>end1</t>
   </si>
   <si>
     <t>M卡</t>
@@ -1946,7 +2009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2650,6 +2713,9 @@
       <c r="D42" t="s">
         <v>75</v>
       </c>
+      <c r="E42">
+        <v>7</v>
+      </c>
       <c r="F42" t="s">
         <v>76</v>
       </c>
@@ -2664,8 +2730,89 @@
       <c r="D43" t="s">
         <v>75</v>
       </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
       <c r="F43" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2713,49 +2860,49 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="N1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="O1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="P1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="Q1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="R1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2763,28 +2910,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K2" t="s">
+        <v>113</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2799,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R2">
         <v>7</v>
@@ -2813,28 +2963,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K3" t="s">
+        <v>113</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2849,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="Q3">
         <v>6</v>
@@ -2863,28 +3016,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K4" t="s">
+        <v>113</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2899,7 +3055,7 @@
         <v>2</v>
       </c>
       <c r="P4" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -2913,28 +3069,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K5" t="s">
+        <v>113</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -2949,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -2964,28 +3123,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K6" t="s">
+        <v>113</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -3000,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <v>6</v>
@@ -3015,28 +3177,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K7" t="s">
+        <v>113</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -3051,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -3066,28 +3231,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K8" t="s">
+        <v>113</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -3102,7 +3270,7 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="Q8">
         <v>6</v>
@@ -3117,28 +3285,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K9" t="s">
+        <v>113</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -3153,13 +3324,13 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="Q9">
         <v>6</v>
       </c>
-      <c r="R9">
-        <v>7</v>
+      <c r="R9" s="1">
+        <v>20</v>
       </c>
       <c r="S9" s="14"/>
     </row>
@@ -3168,28 +3339,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K10" t="s">
+        <v>113</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -3204,13 +3378,13 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="Q10">
         <v>6</v>
       </c>
-      <c r="R10">
-        <v>7</v>
+      <c r="R10" s="1">
+        <v>20</v>
       </c>
       <c r="S10" s="14"/>
     </row>
@@ -3219,28 +3393,31 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>113</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -3255,13 +3432,13 @@
         <v>2</v>
       </c>
       <c r="P11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="Q11">
         <v>6</v>
       </c>
-      <c r="R11">
-        <v>7</v>
+      <c r="R11" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3269,28 +3446,31 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K12" t="s">
+        <v>113</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -3305,13 +3485,13 @@
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="Q12">
         <v>6</v>
       </c>
-      <c r="R12">
-        <v>7</v>
+      <c r="R12" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3319,28 +3499,31 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K13" t="s">
+        <v>113</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -3355,13 +3538,13 @@
         <v>2</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="Q13">
         <v>6</v>
       </c>
-      <c r="R13">
-        <v>7</v>
+      <c r="R13" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3369,28 +3552,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K14" t="s">
+        <v>113</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -3405,13 +3591,13 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="Q14">
         <v>6</v>
       </c>
-      <c r="R14">
-        <v>7</v>
+      <c r="R14" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3419,28 +3605,31 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K15" t="s">
+        <v>113</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -3455,13 +3644,13 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="Q15">
         <v>6</v>
       </c>
-      <c r="R15">
-        <v>7</v>
+      <c r="R15" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3469,28 +3658,31 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K16" t="s">
+        <v>113</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -3505,13 +3697,13 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="Q16">
         <v>6</v>
       </c>
-      <c r="R16">
-        <v>7</v>
+      <c r="R16" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3519,28 +3711,31 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K17" t="s">
+        <v>113</v>
       </c>
       <c r="L17">
         <v>15</v>
@@ -3555,13 +3750,13 @@
         <v>2</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="Q17">
         <v>6</v>
       </c>
-      <c r="R17">
-        <v>7</v>
+      <c r="R17" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3569,28 +3764,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K18" t="s">
+        <v>113</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -3605,13 +3803,13 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="Q18">
-        <v>6</v>
-      </c>
-      <c r="R18">
-        <v>7</v>
+        <v>31</v>
+      </c>
+      <c r="R18" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3619,28 +3817,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K19" t="s">
+        <v>113</v>
       </c>
       <c r="L19">
         <v>15</v>
@@ -3655,13 +3856,13 @@
         <v>2</v>
       </c>
       <c r="P19" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="Q19">
         <v>6</v>
       </c>
-      <c r="R19">
-        <v>7</v>
+      <c r="R19" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3669,28 +3870,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K20" t="s">
+        <v>113</v>
       </c>
       <c r="L20">
         <v>15</v>
@@ -3705,13 +3909,13 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="Q20">
         <v>6</v>
       </c>
-      <c r="R20">
-        <v>7</v>
+      <c r="R20" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3719,28 +3923,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
+      </c>
+      <c r="K21" t="s">
+        <v>113</v>
       </c>
       <c r="L21">
         <v>15</v>
@@ -3755,13 +3962,13 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q21">
         <v>6</v>
       </c>
-      <c r="R21">
-        <v>7</v>
+      <c r="R21" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3769,28 +3976,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="K22" t="s">
+        <v>113</v>
       </c>
       <c r="L22">
         <v>15</v>
@@ -3805,13 +4015,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="Q22">
         <v>6</v>
       </c>
-      <c r="R22">
-        <v>7</v>
+      <c r="R22" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3819,28 +4029,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
+      </c>
+      <c r="K23" t="s">
+        <v>113</v>
       </c>
       <c r="L23">
         <v>15</v>
@@ -3855,13 +4068,13 @@
         <v>2</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>6</v>
       </c>
-      <c r="R23">
-        <v>7</v>
+      <c r="R23" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="9:18">
@@ -3898,7 +4111,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
@@ -3928,25 +4141,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -3954,10 +4167,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3966,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3975,10 +4188,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -3986,10 +4199,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3998,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -4007,10 +4220,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -4018,10 +4231,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -4030,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -4039,10 +4252,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -4050,31 +4263,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -4082,31 +4295,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -4114,31 +4327,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4146,31 +4359,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4178,31 +4391,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4210,31 +4423,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4242,31 +4455,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4274,31 +4487,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4306,31 +4519,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4338,60 +4551,63 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:11">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>205</v>
+        <v>220</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4399,31 +4615,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4431,31 +4647,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4463,31 +4679,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4495,10 +4711,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4507,7 +4723,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4516,7 +4732,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -4524,10 +4740,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4536,7 +4752,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4545,7 +4761,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -4553,10 +4769,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4565,7 +4781,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4574,7 +4790,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
@@ -4582,31 +4798,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4614,31 +4830,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4646,31 +4862,31 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:11">
@@ -4678,31 +4894,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
+        <v>242</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:11">
@@ -4710,31 +4926,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4742,31 +4958,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4774,31 +4990,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -4806,31 +5022,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -4838,31 +5054,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -4870,54 +5086,89 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G32" s="1">
+        <v>50</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:11">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>205</v>
+      <c r="K33" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4961,13 +5212,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4975,13 +5226,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4989,13 +5240,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5003,13 +5254,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5017,13 +5268,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5031,13 +5282,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5045,13 +5296,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5059,13 +5310,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5073,13 +5324,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="E10" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -5106,16 +5357,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -5152,10 +5403,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="F1" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5169,7 +5420,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5189,7 +5440,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5209,13 +5460,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102F328D-F77B-48E1-BB06-9E2C18F7419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5F8CC1-ABB2-4F14-95B6-0690D9287E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5F8CC1-ABB2-4F14-95B6-0690D9287E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7194B4-54AB-4B92-8669-7F743DF207E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId4"/>
     <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
-    <sheet name="PhaseEndingConditions" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$S$30</definedName>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="272">
   <si>
     <t>ID</t>
   </si>
@@ -888,18 +887,6 @@
     <t xml:space="preserve"> TargetValue</t>
   </si>
   <si>
-    <t>NameOrID</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>VPhaseEndingAttributeCondition</t>
-  </si>
-  <si>
-    <t>VPhaseEndingEventCondition</t>
-  </si>
-  <si>
     <t>ExtraTarget</t>
   </si>
   <si>
@@ -918,12 +905,6 @@
     <t>KPI3</t>
   </si>
   <si>
-    <t>Stream,3</t>
-  </si>
-  <si>
-    <t>Coop,5</t>
-  </si>
-  <si>
     <t>Work,4</t>
   </si>
   <si>
@@ -931,6 +912,12 @@
   </si>
   <si>
     <t>Dayoff</t>
+  </si>
+  <si>
+    <t>Stream,0,3</t>
+  </si>
+  <si>
+    <t>Practice,5</t>
   </si>
 </sst>
 </file>
@@ -2101,6 +2088,7 @@
     <col min="18" max="18" width="8.28515625" customWidth="1"/>
     <col min="19" max="19" width="10.140625" customWidth="1"/>
     <col min="20" max="20" width="14.140625" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -2144,7 +2132,7 @@
         <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O1" t="s">
         <v>88</v>
@@ -2162,16 +2150,16 @@
         <v>92</v>
       </c>
       <c r="T1" t="s">
+        <v>262</v>
+      </c>
+      <c r="U1" t="s">
+        <v>264</v>
+      </c>
+      <c r="V1" t="s">
+        <v>265</v>
+      </c>
+      <c r="W1" t="s">
         <v>266</v>
-      </c>
-      <c r="U1" t="s">
-        <v>268</v>
-      </c>
-      <c r="V1" t="s">
-        <v>269</v>
-      </c>
-      <c r="W1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -2469,10 +2457,10 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
+        <v>270</v>
+      </c>
+      <c r="V6" t="s">
         <v>271</v>
-      </c>
-      <c r="V6" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2534,10 +2522,10 @@
         <v>100</v>
       </c>
       <c r="U7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="V7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3118,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -3743,7 +3731,7 @@
         <v>171</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -4722,102 +4710,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7194B4-54AB-4B92-8669-7F743DF207E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -31,6 +25,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="273">
   <si>
     <t>ID</t>
   </si>
@@ -298,12 +294,18 @@
     <t>PlacingCondition</t>
   </si>
   <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
     <t>TurnCount</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
+    <t>ExtraTarget</t>
+  </si>
+  <si>
     <t>InitialViewers</t>
   </si>
   <si>
@@ -319,6 +321,18 @@
     <t>FailEvent</t>
   </si>
   <si>
+    <t>AttributeBonus</t>
+  </si>
+  <si>
+    <t>KPI1</t>
+  </si>
+  <si>
+    <t>KPI2</t>
+  </si>
+  <si>
+    <t>KPI3</t>
+  </si>
+  <si>
     <t>歌回</t>
   </si>
   <si>
@@ -331,6 +345,9 @@
     <t>#FF2160</t>
   </si>
   <si>
+    <t>Livestart</t>
+  </si>
+  <si>
     <t>4,2,2</t>
   </si>
   <si>
@@ -367,6 +384,12 @@
     <t>5,2,3</t>
   </si>
   <si>
+    <t>Stream,0,3</t>
+  </si>
+  <si>
+    <t>Practice,5</t>
+  </si>
+  <si>
     <t>水友联动游戏回</t>
   </si>
   <si>
@@ -376,6 +399,12 @@
     <t>2,5,3</t>
   </si>
   <si>
+    <t>Work,4</t>
+  </si>
+  <si>
+    <t>Outside,6</t>
+  </si>
+  <si>
     <t>棉花糖回</t>
   </si>
   <si>
@@ -460,24 +489,27 @@
     <t>歌力加成结局</t>
   </si>
   <si>
+    <t>7,4,4</t>
+  </si>
+  <si>
+    <t>段位挑战回</t>
+  </si>
+  <si>
+    <t>游戏力加成结局</t>
+  </si>
+  <si>
+    <t>4,7,4</t>
+  </si>
+  <si>
+    <t>清楚聊天室</t>
+  </si>
+  <si>
+    <t>杂谈力加成结局</t>
+  </si>
+  <si>
     <t>4,4,7</t>
   </si>
   <si>
-    <t>段位挑战回</t>
-  </si>
-  <si>
-    <t>游戏力加成结局</t>
-  </si>
-  <si>
-    <t>4,7,4</t>
-  </si>
-  <si>
-    <t>清楚聊天室</t>
-  </si>
-  <si>
-    <t>杂谈力加成结局</t>
-  </si>
-  <si>
     <t>人头麦回</t>
   </si>
   <si>
@@ -511,9 +543,6 @@
     <t>4,5,6</t>
   </si>
   <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
     <t>声乐练习</t>
   </si>
   <si>
@@ -572,6 +601,9 @@
   </si>
   <si>
     <t>体力+70,从卡组中选择一张卡牌删除</t>
+  </si>
+  <si>
+    <t>Dayoff</t>
   </si>
   <si>
     <t>直播成功</t>
@@ -886,49 +918,22 @@
   <si>
     <t xml:space="preserve"> TargetValue</t>
   </si>
-  <si>
-    <t>ExtraTarget</t>
-  </si>
-  <si>
-    <t>AttributeBonus</t>
-  </si>
-  <si>
-    <t>7,4,4</t>
-  </si>
-  <si>
-    <t>KPI1</t>
-  </si>
-  <si>
-    <t>KPI2</t>
-  </si>
-  <si>
-    <t>KPI3</t>
-  </si>
-  <si>
-    <t>Work,4</t>
-  </si>
-  <si>
-    <t>Outside,6</t>
-  </si>
-  <si>
-    <t>Dayoff</t>
-  </si>
-  <si>
-    <t>Stream,0,3</t>
-  </si>
-  <si>
-    <t>Practice,5</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -939,13 +944,157 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -978,7 +1127,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.0999786370433668"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,8 +1149,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1009,9 +1344,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1055,26 +1632,70 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF0BF30B"/>
-      <color rgb="FFE3A7F7"/>
-      <color rgb="FFF567ED"/>
-      <color rgb="FFDEBA2C"/>
-      <color rgb="FFFD460D"/>
+      <color rgb="000BF30B"/>
+      <color rgb="00E3A7F7"/>
+      <color rgb="00F567ED"/>
+      <color rgb="00DEBA2C"/>
+      <color rgb="00FD460D"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1332,22 +1953,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="31.425" customWidth="1"/>
+    <col min="3" max="3" width="29.425" customWidth="1"/>
+    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1481,7 +2102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1495,7 +2116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1509,7 +2130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1693,7 +2314,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1758,7 +2379,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1792,7 +2413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1987,7 +2608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2062,33 +2683,35 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" customWidth="1"/>
-    <col min="18" max="18" width="8.28515625" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
-    <col min="20" max="20" width="14.140625" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3.425" customWidth="1"/>
+    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
+    <col min="5" max="6" width="11.425" customWidth="1"/>
+    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.14166666666667" customWidth="1"/>
+    <col min="10" max="10" width="15.425" customWidth="1"/>
+    <col min="11" max="11" width="10.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="3.28333333333333" customWidth="1"/>
+    <col min="13" max="13" width="6.425" customWidth="1"/>
+    <col min="14" max="14" width="11.7083333333333" customWidth="1"/>
+    <col min="15" max="15" width="10.2833333333333" customWidth="1"/>
+    <col min="16" max="16" width="10.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="11.8583333333333" customWidth="1"/>
+    <col min="18" max="18" width="8.28333333333333" customWidth="1"/>
+    <col min="19" max="19" width="10.1416666666667" customWidth="1"/>
+    <col min="20" max="20" width="14.1416666666667" customWidth="1"/>
+    <col min="21" max="21" width="10.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -2123,75 +2746,75 @@
         <v>85</v>
       </c>
       <c r="K1" t="s">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="L1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N1" t="s">
-        <v>261</v>
+        <v>89</v>
       </c>
       <c r="O1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="T1" t="s">
-        <v>262</v>
+        <v>95</v>
       </c>
       <c r="U1" t="s">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="V1" t="s">
-        <v>265</v>
+        <v>97</v>
       </c>
       <c r="W1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2209,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="R2">
         <v>14</v>
@@ -2221,36 +2844,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K3" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2268,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="R3">
         <v>6</v>
@@ -2280,36 +2903,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K4" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2327,7 +2950,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -2339,36 +2962,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -2386,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="R5" s="1">
         <v>6</v>
@@ -2398,36 +3021,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -2445,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="R6" s="1">
         <v>6</v>
@@ -2457,42 +3080,42 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>270</v>
+        <v>116</v>
       </c>
       <c r="V6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K7" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -2510,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="R7" s="1">
         <v>6</v>
@@ -2522,42 +3145,42 @@
         <v>100</v>
       </c>
       <c r="U7" t="s">
-        <v>267</v>
+        <v>121</v>
       </c>
       <c r="V7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K8" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -2575,7 +3198,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="R8" s="1">
         <v>6</v>
@@ -2587,36 +3210,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -2634,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -2646,36 +3269,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K10" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -2693,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -2705,36 +3328,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -2752,7 +3375,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -2764,36 +3387,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K12" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -2811,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -2823,36 +3446,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -2870,7 +3493,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -2882,36 +3505,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -2929,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -2941,36 +3564,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K15" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -2988,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -3000,36 +3623,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K16" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -3047,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -3064,31 +3687,31 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L17">
         <v>15</v>
@@ -3106,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>263</v>
+        <v>151</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -3123,31 +3746,31 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K18" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -3165,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -3182,31 +3805,31 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K19" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L19">
         <v>15</v>
@@ -3224,7 +3847,7 @@
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -3241,31 +3864,31 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K20" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L20">
         <v>15</v>
@@ -3283,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -3300,31 +3923,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K21" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L21">
         <v>15</v>
@@ -3342,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -3359,31 +3982,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L22">
         <v>15</v>
@@ -3401,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -3418,31 +4041,31 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="L23">
         <v>15</v>
@@ -3460,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -3472,42 +4095,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="18:18">
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="18:18">
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="18:18">
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="18:18">
       <c r="R27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.14166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.425" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.2833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5666666666667" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.8583333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
+    <row r="1" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3539,18 +4164,18 @@
         <v>85</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3559,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -3568,21 +4193,21 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3591,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -3600,21 +4225,21 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -3623,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -3632,466 +4257,466 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="33" customHeight="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1" spans="1:11">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="42" customHeight="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:11">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="30" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" customHeight="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4100,7 +4725,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G19" s="1">
         <v>8</v>
@@ -4109,18 +4734,18 @@
         <v>54</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" customHeight="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4129,7 +4754,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G20" s="1">
         <v>8</v>
@@ -4138,18 +4763,18 @@
         <v>54</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:9">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4158,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -4167,367 +4792,369 @@
         <v>54</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" customHeight="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" customHeight="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" customHeight="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="30" customHeight="1">
+    <row r="25" customHeight="1" spans="1:11">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="30" customHeight="1">
+    <row r="26" customHeight="1" spans="1:11">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="30" customHeight="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:11">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:11">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" customHeight="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:11">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="30" customHeight="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4552,13 +5179,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4566,13 +5193,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4580,13 +5207,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4594,13 +5221,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E5" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4608,13 +5235,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4622,13 +5249,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4636,13 +5263,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4650,13 +5277,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4664,30 +5291,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E10" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.70833333333333" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
+    <col min="2" max="2" width="6.70833333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.425" customWidth="1"/>
+    <col min="4" max="4" width="5.70833333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.425" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4695,19 +5324,20 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="E1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="271">
   <si>
     <t>ID</t>
   </si>
@@ -384,45 +384,42 @@
     <t>5,2,3</t>
   </si>
   <si>
+    <t>Stream,0,2</t>
+  </si>
+  <si>
+    <t>水友联动游戏回</t>
+  </si>
+  <si>
+    <t>第一阶段游戏力</t>
+  </si>
+  <si>
+    <t>2,5,3</t>
+  </si>
+  <si>
+    <t>Work,4</t>
+  </si>
+  <si>
+    <t>棉花糖回</t>
+  </si>
+  <si>
+    <t>第一阶段杂谈力</t>
+  </si>
+  <si>
+    <t>2,2,6</t>
+  </si>
+  <si>
+    <t>水友歌回</t>
+  </si>
+  <si>
+    <t>第二阶段歌力</t>
+  </si>
+  <si>
+    <t>6,3,3</t>
+  </si>
+  <si>
     <t>Stream,0,3</t>
   </si>
   <si>
-    <t>Practice,5</t>
-  </si>
-  <si>
-    <t>水友联动游戏回</t>
-  </si>
-  <si>
-    <t>第一阶段游戏力</t>
-  </si>
-  <si>
-    <t>2,5,3</t>
-  </si>
-  <si>
-    <t>Work,4</t>
-  </si>
-  <si>
-    <t>Outside,6</t>
-  </si>
-  <si>
-    <t>棉花糖回</t>
-  </si>
-  <si>
-    <t>第一阶段杂谈力</t>
-  </si>
-  <si>
-    <t>2,2,6</t>
-  </si>
-  <si>
-    <t>水友歌回</t>
-  </si>
-  <si>
-    <t>第二阶段歌力</t>
-  </si>
-  <si>
-    <t>6,3,3</t>
-  </si>
-  <si>
     <t>水友游戏回</t>
   </si>
   <si>
@@ -579,40 +576,40 @@
     <t>Rest</t>
   </si>
   <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>睡个大的</t>
+  </si>
+  <si>
+    <t>体力+35，随机删除一张基础牌</t>
+  </si>
+  <si>
+    <t>Sleep</t>
+  </si>
+  <si>
+    <t>放一天假</t>
+  </si>
+  <si>
+    <t>体力+70,从卡组中选择一张卡牌删除</t>
+  </si>
+  <si>
+    <t>Dayoff</t>
+  </si>
+  <si>
+    <t>直播成功</t>
+  </si>
+  <si>
+    <t>粉丝+200，金钱+30，舰长+1，获得一张卡</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>睡个大的</t>
-  </si>
-  <si>
-    <t>体力+35，随机删除一张基础牌</t>
-  </si>
-  <si>
-    <t>Sleep</t>
-  </si>
-  <si>
-    <t>放一天假</t>
-  </si>
-  <si>
-    <t>体力+70,从卡组中选择一张卡牌删除</t>
-  </si>
-  <si>
-    <t>Dayoff</t>
-  </si>
-  <si>
-    <t>直播成功</t>
-  </si>
-  <si>
-    <t>粉丝+200，金钱+30，舰长+1，获得一张卡</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>#D0CECE</t>
@@ -815,9 +812,6 @@
   </si>
   <si>
     <t>Coop</t>
-  </si>
-  <si>
-    <t>Contact</t>
   </si>
   <si>
     <t>#F567ED</t>
@@ -3021,7 +3015,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3056,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="N6">
         <v>6000</v>
@@ -3082,19 +3076,16 @@
       <c r="U6" t="s">
         <v>116</v>
       </c>
-      <c r="V6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
         <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>100</v>
@@ -3121,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="N7">
         <v>6000</v>
@@ -3133,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R7" s="1">
         <v>6</v>
@@ -3145,10 +3136,7 @@
         <v>100</v>
       </c>
       <c r="U7" t="s">
-        <v>121</v>
-      </c>
-      <c r="V7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -3156,10 +3144,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
         <v>100</v>
@@ -3186,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="N8">
         <v>6000</v>
@@ -3198,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R8" s="1">
         <v>6</v>
@@ -3210,15 +3198,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -3245,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="N9">
         <v>22000</v>
@@ -3257,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -3267,6 +3255,9 @@
       </c>
       <c r="T9">
         <v>100</v>
+      </c>
+      <c r="U9" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -3274,10 +3265,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" t="s">
         <v>129</v>
-      </c>
-      <c r="C10" t="s">
-        <v>130</v>
       </c>
       <c r="D10" t="s">
         <v>100</v>
@@ -3304,7 +3295,7 @@
         <v>12</v>
       </c>
       <c r="M10">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="N10">
         <v>22000</v>
@@ -3316,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -3333,10 +3324,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
         <v>132</v>
-      </c>
-      <c r="C11" t="s">
-        <v>133</v>
       </c>
       <c r="D11" t="s">
         <v>100</v>
@@ -3363,7 +3354,7 @@
         <v>12</v>
       </c>
       <c r="M11">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="N11">
         <v>22000</v>
@@ -3375,7 +3366,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -3392,10 +3383,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
         <v>135</v>
-      </c>
-      <c r="C12" t="s">
-        <v>136</v>
       </c>
       <c r="D12" t="s">
         <v>100</v>
@@ -3422,7 +3413,7 @@
         <v>12</v>
       </c>
       <c r="M12">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="N12">
         <v>22000</v>
@@ -3434,7 +3425,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -3451,10 +3442,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" t="s">
         <v>138</v>
-      </c>
-      <c r="C13" t="s">
-        <v>139</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -3481,7 +3472,7 @@
         <v>12</v>
       </c>
       <c r="M13">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="N13">
         <v>30000</v>
@@ -3493,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -3510,10 +3501,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
         <v>140</v>
-      </c>
-      <c r="C14" t="s">
-        <v>141</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -3540,7 +3531,7 @@
         <v>12</v>
       </c>
       <c r="M14">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="N14">
         <v>30000</v>
@@ -3552,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -3569,10 +3560,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" t="s">
         <v>143</v>
-      </c>
-      <c r="C15" t="s">
-        <v>144</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3599,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="M15">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="N15">
         <v>30000</v>
@@ -3611,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -3628,10 +3619,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
         <v>146</v>
-      </c>
-      <c r="C16" t="s">
-        <v>147</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3658,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="M16">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="N16">
         <v>30000</v>
@@ -3670,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -3687,10 +3678,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" t="s">
         <v>149</v>
-      </c>
-      <c r="C17" t="s">
-        <v>150</v>
       </c>
       <c r="D17" t="s">
         <v>100</v>
@@ -3707,7 +3698,7 @@
       <c r="H17" t="s">
         <v>100</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="4" t="s">
         <v>102</v>
       </c>
       <c r="K17" t="s">
@@ -3717,7 +3708,7 @@
         <v>15</v>
       </c>
       <c r="M17">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N17">
         <v>50000</v>
@@ -3729,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -3746,10 +3737,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" t="s">
         <v>152</v>
-      </c>
-      <c r="C18" t="s">
-        <v>153</v>
       </c>
       <c r="D18" t="s">
         <v>100</v>
@@ -3776,7 +3767,7 @@
         <v>15</v>
       </c>
       <c r="M18">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N18">
         <v>50000</v>
@@ -3788,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -3805,10 +3796,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" t="s">
         <v>155</v>
-      </c>
-      <c r="C19" t="s">
-        <v>156</v>
       </c>
       <c r="D19" t="s">
         <v>100</v>
@@ -3835,7 +3826,7 @@
         <v>15</v>
       </c>
       <c r="M19">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N19">
         <v>50000</v>
@@ -3847,7 +3838,7 @@
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -3864,10 +3855,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" t="s">
         <v>158</v>
-      </c>
-      <c r="C20" t="s">
-        <v>159</v>
       </c>
       <c r="D20" t="s">
         <v>100</v>
@@ -3894,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="M20">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N20">
         <v>50000</v>
@@ -3906,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -3923,10 +3914,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" t="s">
         <v>161</v>
-      </c>
-      <c r="C21" t="s">
-        <v>162</v>
       </c>
       <c r="D21" t="s">
         <v>100</v>
@@ -3953,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="M21">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N21">
         <v>50000</v>
@@ -3965,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -3982,10 +3973,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" t="s">
         <v>164</v>
-      </c>
-      <c r="C22" t="s">
-        <v>165</v>
       </c>
       <c r="D22" t="s">
         <v>100</v>
@@ -4012,7 +4003,7 @@
         <v>15</v>
       </c>
       <c r="M22">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N22">
         <v>50000</v>
@@ -4024,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -4041,10 +4032,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" t="s">
         <v>166</v>
-      </c>
-      <c r="C23" t="s">
-        <v>167</v>
       </c>
       <c r="D23" t="s">
         <v>100</v>
@@ -4071,7 +4062,7 @@
         <v>15</v>
       </c>
       <c r="M23">
-        <v>40000</v>
+        <v>140000</v>
       </c>
       <c r="N23">
         <v>50000</v>
@@ -4083,7 +4074,7 @@
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -4172,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -4196,7 +4187,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -4204,10 +4195,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -4228,7 +4219,7 @@
         <v>106</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -4236,10 +4227,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -4260,7 +4251,7 @@
         <v>109</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -4268,13 +4259,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -4286,13 +4277,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -4300,13 +4291,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4318,13 +4309,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -4332,13 +4323,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -4350,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4364,13 +4355,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -4382,13 +4373,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I8" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4396,13 +4387,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -4414,13 +4405,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4428,13 +4419,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -4446,13 +4437,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4460,13 +4451,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -4478,13 +4469,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4492,13 +4483,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -4510,13 +4501,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4524,13 +4515,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -4542,13 +4533,13 @@
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I13" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4556,13 +4547,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -4574,13 +4565,13 @@
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -4588,13 +4579,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -4606,10 +4597,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4617,13 +4608,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
@@ -4635,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4649,13 +4640,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -4667,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4681,13 +4672,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
@@ -4699,13 +4690,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4713,10 +4704,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4742,10 +4733,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4771,10 +4762,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4800,13 +4791,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
@@ -4818,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4832,13 +4823,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -4850,13 +4841,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4864,13 +4855,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -4882,10 +4873,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4896,13 +4887,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -4914,10 +4905,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4928,13 +4919,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -4946,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4960,13 +4951,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -4978,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4992,13 +4983,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -5010,13 +5001,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -5024,13 +5015,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -5042,13 +5033,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -5056,13 +5047,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -5074,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -5088,13 +5079,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -5106,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:9">
@@ -5117,10 +5108,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -5132,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -5179,13 +5170,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E2" t="s">
         <v>252</v>
-      </c>
-      <c r="D2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5193,13 +5184,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5207,13 +5198,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5221,13 +5212,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5235,13 +5226,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" t="s">
         <v>258</v>
-      </c>
-      <c r="E6" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5249,13 +5240,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" t="s">
         <v>261</v>
-      </c>
-      <c r="D7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5263,13 +5254,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" t="s">
         <v>262</v>
-      </c>
-      <c r="E8" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5277,13 +5268,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" t="s">
         <v>265</v>
-      </c>
-      <c r="D9" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5291,13 +5282,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -5324,16 +5315,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCF125-C83C-492F-9E96-93243EAE0330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9040" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -25,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -916,18 +920,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -938,157 +936,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1121,7 +975,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1143,194 +997,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1338,251 +1006,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1626,70 +1052,26 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="000BF30B"/>
-      <color rgb="00E3A7F7"/>
-      <color rgb="00F567ED"/>
-      <color rgb="00DEBA2C"/>
-      <color rgb="00FD460D"/>
+      <color rgb="FF0BF30B"/>
+      <color rgb="FFE3A7F7"/>
+      <color rgb="FFF567ED"/>
+      <color rgb="FFDEBA2C"/>
+      <color rgb="FFFD460D"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1947,22 +1329,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="31.7083333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="29.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2096,7 +1478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2110,7 +1492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2124,7 +1506,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2152,7 +1534,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2169,7 +1551,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2186,7 +1568,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2203,7 +1585,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2220,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2237,7 +1619,7 @@
         <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2308,7 +1690,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2373,7 +1755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2407,7 +1789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2602,7 +1984,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2677,35 +2059,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
-    <col min="9" max="9" width="8.14166666666667" customWidth="1"/>
-    <col min="10" max="10" width="15.425" customWidth="1"/>
-    <col min="11" max="11" width="10.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="3.28333333333333" customWidth="1"/>
-    <col min="13" max="13" width="6.425" customWidth="1"/>
-    <col min="14" max="14" width="11.7083333333333" customWidth="1"/>
-    <col min="15" max="15" width="10.2833333333333" customWidth="1"/>
-    <col min="16" max="16" width="10.7083333333333" customWidth="1"/>
-    <col min="17" max="17" width="11.8583333333333" customWidth="1"/>
-    <col min="18" max="18" width="8.28333333333333" customWidth="1"/>
-    <col min="19" max="19" width="10.1416666666667" customWidth="1"/>
-    <col min="20" max="20" width="14.1416666666667" customWidth="1"/>
-    <col min="21" max="21" width="10.2833333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="18" width="8.28515625" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -2779,7 +2159,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2838,7 +2218,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2897,7 +2277,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2956,7 +2336,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3015,7 +2395,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3050,10 +2430,10 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>15000</v>
+        <v>150</v>
       </c>
       <c r="N6">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="O6">
         <v>50</v>
@@ -3077,7 +2457,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3139,7 +2519,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3197,8 +2577,11 @@
       <c r="T8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="U8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3256,11 +2639,8 @@
       <c r="T9">
         <v>100</v>
       </c>
-      <c r="U9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3319,7 +2699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3378,7 +2758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3437,7 +2817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3496,7 +2876,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3555,7 +2935,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3614,7 +2994,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4086,44 +3466,42 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="18:18">
+    <row r="24" spans="1:20">
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="18:18">
+    <row r="25" spans="1:20">
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="18:18">
+    <row r="26" spans="1:20">
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="18:18">
+    <row r="27" spans="1:20">
       <c r="R27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7083333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.425" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.8583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
+    <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4158,7 +3536,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
+    <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4190,7 +3568,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
+    <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4222,7 +3600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4254,7 +3632,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
+    <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -4286,7 +3664,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="1:11">
+    <row r="6" spans="1:11" ht="33" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4318,7 +3696,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
+    <row r="7" spans="1:11" ht="30" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4350,7 +3728,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:11">
+    <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4382,7 +3760,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:11">
+    <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4414,7 +3792,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:11">
+    <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4446,7 +3824,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:11">
+    <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4478,7 +3856,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
+    <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4510,7 +3888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:11">
+    <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4533,7 +3911,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>205</v>
@@ -4542,7 +3920,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4565,7 +3943,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>205</v>
@@ -4574,7 +3952,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4603,7 +3981,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1" spans="1:11">
+    <row r="16" spans="1:11" ht="42" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -4635,7 +4013,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:11">
+    <row r="17" spans="1:11" ht="30" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -4667,7 +4045,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:11">
+    <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -4699,7 +4077,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:9">
+    <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -4728,7 +4106,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:9">
+    <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -4757,7 +4135,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:9">
+    <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -4786,7 +4164,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:11">
+    <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -4818,7 +4196,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:11">
+    <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -4850,7 +4228,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:11">
+    <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -4882,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:11">
+    <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -4914,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:11">
+    <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -4928,7 +4306,7 @@
         <v>237</v>
       </c>
       <c r="E26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>101</v>
@@ -4946,7 +4324,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:11">
+    <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -4960,7 +4338,7 @@
         <v>237</v>
       </c>
       <c r="E27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>101</v>
@@ -4978,7 +4356,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:11">
+    <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -4992,7 +4370,7 @@
         <v>237</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>101</v>
@@ -5010,7 +4388,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:11">
+    <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -5024,7 +4402,7 @@
         <v>237</v>
       </c>
       <c r="E29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>101</v>
@@ -5042,7 +4420,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:11">
+    <row r="30" spans="1:11" ht="30" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -5056,7 +4434,7 @@
         <v>237</v>
       </c>
       <c r="E30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>101</v>
@@ -5074,7 +4452,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:9">
+    <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -5088,7 +4466,7 @@
         <v>237</v>
       </c>
       <c r="E31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>101</v>
@@ -5103,7 +4481,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:9">
+    <row r="32" spans="1:11" ht="30" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -5131,21 +4509,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5293,21 +4669,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.70833333333333" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.14166666666667" customWidth="1"/>
-    <col min="2" max="2" width="6.70833333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.425" customWidth="1"/>
-    <col min="4" max="4" width="5.70833333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.425" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5329,6 +4703,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FCF125-C83C-492F-9E96-93243EAE0330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB17F89-48D2-45B9-9944-2DC22ED8AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="273">
   <si>
     <t>ID</t>
   </si>
@@ -386,9 +386,6 @@
   </si>
   <si>
     <t>5,2,3</t>
-  </si>
-  <si>
-    <t>Stream,0,2</t>
   </si>
   <si>
     <t>水友联动游戏回</t>
@@ -916,17 +913,33 @@
   <si>
     <t xml:space="preserve"> TargetValue</t>
   </si>
+  <si>
+    <t>Stream,0,1</t>
+  </si>
+  <si>
+    <t>upgrade</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeSelectEffect</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1010,7 +1023,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1018,7 +1031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1051,6 +1064,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1335,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2055,6 +2069,17 @@
       </c>
       <c r="F43" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>271</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2454,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>116</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2462,10 +2487,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
         <v>117</v>
-      </c>
-      <c r="C7" t="s">
-        <v>118</v>
       </c>
       <c r="D7" t="s">
         <v>100</v>
@@ -2504,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R7" s="1">
         <v>6</v>
@@ -2516,7 +2541,7 @@
         <v>100</v>
       </c>
       <c r="U7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2524,10 +2549,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
         <v>121</v>
-      </c>
-      <c r="C8" t="s">
-        <v>122</v>
       </c>
       <c r="D8" t="s">
         <v>100</v>
@@ -2566,7 +2591,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R8" s="1">
         <v>6</v>
@@ -2578,7 +2603,7 @@
         <v>100</v>
       </c>
       <c r="U8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2586,10 +2611,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -2628,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -2645,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
         <v>128</v>
-      </c>
-      <c r="C10" t="s">
-        <v>129</v>
       </c>
       <c r="D10" t="s">
         <v>100</v>
@@ -2687,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -2704,10 +2729,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
         <v>131</v>
-      </c>
-      <c r="C11" t="s">
-        <v>132</v>
       </c>
       <c r="D11" t="s">
         <v>100</v>
@@ -2746,7 +2771,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -2763,10 +2788,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
         <v>134</v>
-      </c>
-      <c r="C12" t="s">
-        <v>135</v>
       </c>
       <c r="D12" t="s">
         <v>100</v>
@@ -2805,7 +2830,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -2822,10 +2847,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" t="s">
         <v>137</v>
-      </c>
-      <c r="C13" t="s">
-        <v>138</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -2864,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -2881,10 +2906,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" t="s">
         <v>139</v>
-      </c>
-      <c r="C14" t="s">
-        <v>140</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -2923,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -2940,10 +2965,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" t="s">
         <v>142</v>
-      </c>
-      <c r="C15" t="s">
-        <v>143</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -2982,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -2999,10 +3024,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" t="s">
-        <v>146</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3041,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -3058,10 +3083,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" t="s">
         <v>148</v>
-      </c>
-      <c r="C17" t="s">
-        <v>149</v>
       </c>
       <c r="D17" t="s">
         <v>100</v>
@@ -3100,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -3117,10 +3142,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" t="s">
         <v>151</v>
-      </c>
-      <c r="C18" t="s">
-        <v>152</v>
       </c>
       <c r="D18" t="s">
         <v>100</v>
@@ -3159,7 +3184,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -3176,10 +3201,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" t="s">
         <v>154</v>
-      </c>
-      <c r="C19" t="s">
-        <v>155</v>
       </c>
       <c r="D19" t="s">
         <v>100</v>
@@ -3218,7 +3243,7 @@
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -3235,10 +3260,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" t="s">
         <v>157</v>
-      </c>
-      <c r="C20" t="s">
-        <v>158</v>
       </c>
       <c r="D20" t="s">
         <v>100</v>
@@ -3277,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -3294,10 +3319,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" t="s">
         <v>160</v>
-      </c>
-      <c r="C21" t="s">
-        <v>161</v>
       </c>
       <c r="D21" t="s">
         <v>100</v>
@@ -3336,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -3353,10 +3378,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" t="s">
         <v>163</v>
-      </c>
-      <c r="C22" t="s">
-        <v>164</v>
       </c>
       <c r="D22" t="s">
         <v>100</v>
@@ -3395,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -3412,10 +3437,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
         <v>165</v>
-      </c>
-      <c r="C23" t="s">
-        <v>166</v>
       </c>
       <c r="D23" t="s">
         <v>100</v>
@@ -3454,7 +3479,7 @@
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -3541,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -3565,7 +3590,7 @@
         <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -3573,10 +3598,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -3597,7 +3622,7 @@
         <v>106</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -3605,10 +3630,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -3629,7 +3654,7 @@
         <v>109</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
@@ -3637,13 +3662,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -3655,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="K5" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="33" customHeight="1">
@@ -3669,13 +3694,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -3687,13 +3712,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -3701,13 +3726,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -3719,13 +3744,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -3733,31 +3758,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="K8" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
@@ -3765,31 +3790,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
@@ -3797,31 +3822,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -3829,31 +3854,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -3861,31 +3886,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -3893,13 +3918,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3911,13 +3936,13 @@
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="K13" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -3925,13 +3950,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3943,13 +3968,13 @@
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>205</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -3957,13 +3982,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -3975,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I15" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="42" customHeight="1">
@@ -3986,31 +4011,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -4018,31 +4043,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -4050,31 +4075,31 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -4082,10 +4107,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4111,10 +4136,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4140,10 +4165,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4169,31 +4194,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -4201,31 +4226,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
@@ -4233,28 +4258,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4265,28 +4290,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>235</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4297,13 +4322,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -4315,13 +4340,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="K26" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
@@ -4329,13 +4354,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -4347,13 +4372,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>238</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
@@ -4361,13 +4386,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -4379,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I28" s="11" t="s">
-        <v>238</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
@@ -4393,13 +4418,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -4411,13 +4436,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>238</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1">
@@ -4425,13 +4450,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -4443,13 +4468,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="I30" s="11" t="s">
-        <v>238</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1">
@@ -4457,13 +4482,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -4475,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1">
@@ -4486,25 +4511,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I32" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4546,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
         <v>250</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>251</v>
-      </c>
-      <c r="E2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4560,13 +4585,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" t="s">
         <v>253</v>
-      </c>
-      <c r="D3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4574,13 +4599,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" t="s">
         <v>255</v>
       </c>
-      <c r="D4" t="s">
-        <v>256</v>
-      </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4588,13 +4613,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" t="s">
         <v>256</v>
-      </c>
-      <c r="E5" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4602,13 +4627,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4616,13 +4641,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" t="s">
         <v>259</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>260</v>
-      </c>
-      <c r="E7" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4630,13 +4655,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" t="s">
         <v>259</v>
       </c>
-      <c r="D8" t="s">
-        <v>260</v>
-      </c>
       <c r="E8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4644,13 +4669,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="s">
         <v>263</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>264</v>
-      </c>
-      <c r="E9" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4658,13 +4683,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" t="s">
+        <v>263</v>
+      </c>
+      <c r="E10" t="s">
         <v>266</v>
-      </c>
-      <c r="D10" t="s">
-        <v>264</v>
-      </c>
-      <c r="E10" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4689,16 +4714,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" t="s">
         <v>269</v>
-      </c>
-      <c r="E1" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10030" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="273">
   <si>
     <t>ID</t>
   </si>
@@ -668,7 +668,7 @@
     <t>Work2</t>
   </si>
   <si>
-    <t>购物</t>
+    <t>商店</t>
   </si>
   <si>
     <t>进入商店界面</t>
@@ -678,6 +678,9 @@
   </si>
   <si>
     <t>#0BF30B</t>
+  </si>
+  <si>
+    <t>Store</t>
   </si>
   <si>
     <t>歌回成功事件</t>
@@ -781,10 +784,10 @@
     <t>毕业1</t>
   </si>
   <si>
-    <t>第一阶段失败</t>
-  </si>
-  <si>
-    <t>Graduation_1</t>
+    <t>毕业结局</t>
+  </si>
+  <si>
+    <t>Graduation</t>
   </si>
   <si>
     <t>毕业2</t>
@@ -848,6 +851,9 @@
   </si>
   <si>
     <t>外出吃饭</t>
+  </si>
+  <si>
+    <t>Lamian</t>
   </si>
   <si>
     <t>M卡</t>
@@ -4533,7 +4539,7 @@
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>205</v>
@@ -4565,7 +4571,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>205</v>
@@ -4574,7 +4580,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" customHeight="1" spans="1:11">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4601,6 +4607,9 @@
       </c>
       <c r="I15" s="10" t="s">
         <v>213</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4608,10 +4617,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>190</v>
@@ -4632,7 +4641,7 @@
         <v>192</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4640,10 +4649,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>190</v>
@@ -4664,7 +4673,7 @@
         <v>192</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4672,10 +4681,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>190</v>
@@ -4696,7 +4705,7 @@
         <v>192</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -4704,10 +4713,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
@@ -4733,10 +4742,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>54</v>
@@ -4762,10 +4771,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>54</v>
@@ -4791,10 +4800,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>190</v>
@@ -4815,7 +4824,7 @@
         <v>192</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
@@ -4823,10 +4832,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>190</v>
@@ -4847,7 +4856,7 @@
         <v>192</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
@@ -4855,10 +4864,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>190</v>
@@ -4876,7 +4885,7 @@
         <v>191</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -4887,10 +4896,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>190</v>
@@ -4908,7 +4917,7 @@
         <v>191</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K25" s="1">
         <v>0</v>
@@ -4919,13 +4928,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -4937,13 +4946,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:11">
@@ -4951,13 +4960,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -4969,13 +4978,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
@@ -4983,13 +4992,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -5001,13 +5010,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:11">
@@ -5015,13 +5024,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -5033,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:11">
@@ -5047,13 +5056,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
@@ -5065,13 +5074,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:9">
@@ -5079,13 +5088,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -5097,18 +5106,18 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>212</v>
@@ -5127,6 +5136,9 @@
       </c>
       <c r="I32" s="10" t="s">
         <v>213</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5170,13 +5182,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5184,13 +5196,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" t="s">
         <v>253</v>
       </c>
-      <c r="D3" t="s">
-        <v>251</v>
-      </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5198,13 +5210,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5212,13 +5224,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5226,13 +5238,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" t="s">
         <v>258</v>
       </c>
-      <c r="D6" t="s">
-        <v>256</v>
-      </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5240,13 +5252,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5254,13 +5266,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5268,13 +5280,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5282,13 +5294,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" t="s">
         <v>266</v>
       </c>
-      <c r="D10" t="s">
-        <v>264</v>
-      </c>
       <c r="E10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5315,16 +5327,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/Raising.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10030" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="359">
   <si>
     <t>ID</t>
   </si>
@@ -276,6 +276,15 @@
     <t>随机获得一张幽默相关卡</t>
   </si>
   <si>
+    <t>随机强化一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeRandomCardEffect</t>
+  </si>
+  <si>
+    <t>选择一张营收牌获得</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -396,7 +405,7 @@
     <t>2,5,3</t>
   </si>
   <si>
-    <t>Work,4</t>
+    <t>Stream,1,2</t>
   </si>
   <si>
     <t>棉花糖回</t>
@@ -408,6 +417,9 @@
     <t>2,2,6</t>
   </si>
   <si>
+    <t>Stream,2,2</t>
+  </si>
+  <si>
     <t>水友歌回</t>
   </si>
   <si>
@@ -417,78 +429,93 @@
     <t>6,3,3</t>
   </si>
   <si>
+    <t>水友游戏回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>Work,2</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>Work,3</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>5,3,4</t>
+  </si>
+  <si>
+    <t>Stream,-1,3</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>Rest,4</t>
+  </si>
+  <si>
+    <t>Practice,3</t>
+  </si>
+  <si>
+    <t>光暗歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>7,4,4</t>
+  </si>
+  <si>
     <t>Stream,0,3</t>
   </si>
   <si>
-    <t>水友游戏回</t>
-  </si>
-  <si>
-    <t>第二阶段游戏</t>
-  </si>
-  <si>
-    <t>3,6,3</t>
-  </si>
-  <si>
-    <t>视频鉴赏回</t>
-  </si>
-  <si>
-    <t>第二阶段杂谈</t>
-  </si>
-  <si>
-    <t>3,3,6</t>
-  </si>
-  <si>
-    <t>代抽回</t>
-  </si>
-  <si>
-    <t>第二阶段营收</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>水友投稿回</t>
-  </si>
-  <si>
-    <t>第三阶段粉丝</t>
-  </si>
-  <si>
-    <t>生日回</t>
-  </si>
-  <si>
-    <t>第三阶段舰长</t>
-  </si>
-  <si>
-    <t>5,3,4</t>
-  </si>
-  <si>
-    <t>粉丝礼物回</t>
-  </si>
-  <si>
-    <t>第三阶段营收</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>健身环挑战回</t>
-  </si>
-  <si>
-    <t>第三阶段体力</t>
-  </si>
-  <si>
-    <t>3,5,4</t>
-  </si>
-  <si>
-    <t>光暗歌会</t>
-  </si>
-  <si>
-    <t>歌力加成结局</t>
-  </si>
-  <si>
-    <t>7,4,4</t>
-  </si>
-  <si>
     <t>段位挑战回</t>
   </si>
   <si>
@@ -498,6 +525,9 @@
     <t>4,7,4</t>
   </si>
   <si>
+    <t>Stream,1,3</t>
+  </si>
+  <si>
     <t>清楚聊天室</t>
   </si>
   <si>
@@ -507,6 +537,9 @@
     <t>4,4,7</t>
   </si>
   <si>
+    <t>Stream,2,3</t>
+  </si>
+  <si>
     <t>人头麦回</t>
   </si>
   <si>
@@ -516,6 +549,9 @@
     <t>6,4,5</t>
   </si>
   <si>
+    <t>Outside,1</t>
+  </si>
+  <si>
     <t>健身环耐久回</t>
   </si>
   <si>
@@ -525,6 +561,9 @@
     <t>4,6,5</t>
   </si>
   <si>
+    <t>Rest,2</t>
+  </si>
+  <si>
     <t>百舰回</t>
   </si>
   <si>
@@ -540,10 +579,13 @@
     <t>4,5,6</t>
   </si>
   <si>
+    <t>Coop,2</t>
+  </si>
+  <si>
     <t>声乐练习</t>
   </si>
   <si>
-    <t>歌力+20</t>
+    <t>歌力+18</t>
   </si>
   <si>
     <t>SingPractice</t>
@@ -552,7 +594,7 @@
     <t>游戏练习</t>
   </si>
   <si>
-    <t>游戏力+20</t>
+    <t>游戏力+18</t>
   </si>
   <si>
     <t>GamePractice</t>
@@ -561,7 +603,7 @@
     <t>对话练习</t>
   </si>
   <si>
-    <t>杂谈力+20</t>
+    <t>杂谈力+18</t>
   </si>
   <si>
     <t>ChatPractice</t>
@@ -656,6 +698,9 @@
     <t>#E5FD1F</t>
   </si>
   <si>
+    <t>1,2</t>
+  </si>
+  <si>
     <t>Work1</t>
   </si>
   <si>
@@ -668,10 +713,10 @@
     <t>Work2</t>
   </si>
   <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>进入商店界面</t>
+    <t>外出购物</t>
+  </si>
+  <si>
+    <t>进入商店</t>
   </si>
   <si>
     <t>Outside</t>
@@ -686,71 +731,6 @@
     <t>歌回成功事件</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>粉丝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，金钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，舰长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，获得一张卡</t>
-    </r>
-  </si>
-  <si>
     <t>SingSuccess</t>
   </si>
   <si>
@@ -766,19 +746,28 @@
     <t>进阶唱歌练习</t>
   </si>
   <si>
-    <t>歌力+30，获得一张卡</t>
+    <t>歌力+25</t>
+  </si>
+  <si>
+    <t>SingPractice2</t>
   </si>
   <si>
     <t>进阶游戏练习</t>
   </si>
   <si>
-    <t>游戏力+30，获得一张卡</t>
+    <t>游戏力+25</t>
+  </si>
+  <si>
+    <t>GamePractice2</t>
   </si>
   <si>
     <t>进阶杂谈练习</t>
   </si>
   <si>
-    <t>杂谈力+30，获得一张卡</t>
+    <t>杂谈力+25</t>
+  </si>
+  <si>
+    <t>ChatPractice2</t>
   </si>
   <si>
     <t>毕业1</t>
@@ -805,15 +794,24 @@
     <t>#D1CECE</t>
   </si>
   <si>
+    <t>phase3</t>
+  </si>
+  <si>
     <t>结局阶段开始</t>
   </si>
   <si>
     <t>#D2CECE</t>
   </si>
   <si>
+    <t>phase4</t>
+  </si>
+  <si>
     <t>雪王好感度增加事件</t>
   </si>
   <si>
+    <t>雪王好感度+5</t>
+  </si>
+  <si>
     <t>Coop</t>
   </si>
   <si>
@@ -826,36 +824,198 @@
     <t>小室好感度增加事件</t>
   </si>
   <si>
+    <t>小室好感度+5</t>
+  </si>
+  <si>
     <t>XiaoShiMeet1</t>
   </si>
   <si>
     <t>井井好感度增加事件</t>
   </si>
   <si>
+    <t>井井好感度+5</t>
+  </si>
+  <si>
     <t>##Meet1</t>
   </si>
   <si>
     <t>奶茶好感度增加事件</t>
   </si>
   <si>
+    <t>奶茶好感度+5</t>
+  </si>
+  <si>
     <t>YuzuMeet1</t>
   </si>
   <si>
     <t>画师好感度增加事件</t>
   </si>
   <si>
+    <t>画师好感度+5</t>
+  </si>
+  <si>
     <t>MamaMeet1</t>
   </si>
   <si>
     <t>大白猫好感度增加事件</t>
   </si>
   <si>
+    <t>大白猫好感度+5</t>
+  </si>
+  <si>
     <t>外出吃饭</t>
   </si>
   <si>
+    <t>Money</t>
+  </si>
+  <si>
     <t>Lamian</t>
   </si>
   <si>
+    <t>动态营业</t>
+  </si>
+  <si>
+    <t>粉丝+100</t>
+  </si>
+  <si>
+    <t>Work3</t>
+  </si>
+  <si>
+    <t>小室关系加深事件1</t>
+  </si>
+  <si>
+    <t>最大体力值+5，沪币+100</t>
+  </si>
+  <si>
+    <t>小室关系加深事件2</t>
+  </si>
+  <si>
+    <t>获得遗物小室的头绳，回复10点体力</t>
+  </si>
+  <si>
+    <t>小室关系加深事件3</t>
+  </si>
+  <si>
+    <t>最大体力值+5，选择一张高稀有度卡获得</t>
+  </si>
+  <si>
+    <t>小室关系加深事件4</t>
+  </si>
+  <si>
+    <t>获得遗物小室的玫瑰，回复15点体力</t>
+  </si>
+  <si>
+    <t>雪王关系加深事件1</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+3%，获得卡牌“赤石”</t>
+  </si>
+  <si>
+    <t>雪王关系加深事件2</t>
+  </si>
+  <si>
+    <t>获得遗物雪王的狗，随机强化一张卡</t>
+  </si>
+  <si>
+    <t>雪王关系加深事件3</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+3%，获得卡牌“窝里横”</t>
+  </si>
+  <si>
+    <t>雪王关系加深事件4</t>
+  </si>
+  <si>
+    <t>获得遗物雪王的心脏，压力-1</t>
+  </si>
+  <si>
+    <t>井井关系加深事件1</t>
+  </si>
+  <si>
+    <t>歌力提升率+3%，获得卡牌“养”</t>
+  </si>
+  <si>
+    <t>井井关系加深事件2</t>
+  </si>
+  <si>
+    <t>获得遗物井井的麦克风，粉丝+200</t>
+  </si>
+  <si>
+    <t>井井关系加深事件3</t>
+  </si>
+  <si>
+    <t>歌力提升率+3%，获得卡牌“gachi距离”</t>
+  </si>
+  <si>
+    <t>井井关系加深事件4</t>
+  </si>
+  <si>
+    <t>获得遗物井井的光环，粉丝+300</t>
+  </si>
+  <si>
+    <t>画师mama关系加深事件1</t>
+  </si>
+  <si>
+    <t>舰长+5，粉丝+200，获得卡牌“工作音”</t>
+  </si>
+  <si>
+    <t>画师mama关系加深事件2</t>
+  </si>
+  <si>
+    <t>获得遗物画师mama的画笔，沪币+50</t>
+  </si>
+  <si>
+    <t>画师mama关系加深事件3</t>
+  </si>
+  <si>
+    <t>舰长+10，粉丝+300，获得卡牌“摸鱼”</t>
+  </si>
+  <si>
+    <t>画师mama关系加深事件4</t>
+  </si>
+  <si>
+    <t>获得遗物画师mama的画板，沪币+100</t>
+  </si>
+  <si>
+    <t>柚茶关系加深事件1</t>
+  </si>
+  <si>
+    <t>游戏力提升率+3%获得卡牌“高僧预测”
+限定晚上</t>
+  </si>
+  <si>
+    <t>柚茶关系加深事件2</t>
+  </si>
+  <si>
+    <t>获得遗物柚子茶的手柄，体力+10
+限定晚上</t>
+  </si>
+  <si>
+    <t>柚茶关系加深事件3</t>
+  </si>
+  <si>
+    <t>游戏力提升率+3%获得卡牌“黏住”
+限定晚上</t>
+  </si>
+  <si>
+    <t>柚茶关系加深事件4</t>
+  </si>
+  <si>
+    <t>获得遗物柚子茶的枕头，体力+15
+限定晚上</t>
+  </si>
+  <si>
+    <t>朋友聚会</t>
+  </si>
+  <si>
+    <t>压力-1，体力+25，随机获得一张M卡
+压力-1，获得一张高稀有度卡牌，选择一张卡牌删除
+压力-1，选择两张卡强化</t>
+  </si>
+  <si>
+    <t>Patry</t>
+  </si>
+  <si>
     <t>M卡</t>
   </si>
   <si>
@@ -910,6 +1070,12 @@
     <t>fun</t>
   </si>
   <si>
+    <t>营收</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
@@ -917,6 +1083,42 @@
   </si>
   <si>
     <t xml:space="preserve"> TargetValue</t>
+  </si>
+  <si>
+    <t>限定晚上</t>
+  </si>
+  <si>
+    <t>VTimeOfDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>限定中午</t>
+  </si>
+  <si>
+    <t>限定早上</t>
+  </si>
+  <si>
+    <t>限定周1</t>
+  </si>
+  <si>
+    <t>VDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>限定周2</t>
+  </si>
+  <si>
+    <t>限定周3</t>
+  </si>
+  <si>
+    <t>限定周4</t>
+  </si>
+  <si>
+    <t>限定周5</t>
+  </si>
+  <si>
+    <t>限定周6</t>
+  </si>
+  <si>
+    <t>限定周7</t>
   </si>
 </sst>
 </file>
@@ -929,7 +1131,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1086,12 +1288,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="41">
@@ -1959,7 +2155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.425" customWidth="1"/>
@@ -2678,6 +2874,34 @@
         <v>75</v>
       </c>
       <c r="F43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2728,61 +2952,61 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="O1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="U1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="V1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="W1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -2790,31 +3014,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2832,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R2">
         <v>14</v>
@@ -2841,7 +3065,7 @@
         <v>7</v>
       </c>
       <c r="T2">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2849,31 +3073,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K3" t="s">
         <v>106</v>
-      </c>
-      <c r="K3" t="s">
-        <v>103</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2891,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R3">
         <v>6</v>
@@ -2900,7 +3124,7 @@
         <v>7</v>
       </c>
       <c r="T3">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -2908,31 +3132,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2950,7 +3174,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -2959,7 +3183,7 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -2967,31 +3191,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -3009,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R5" s="1">
         <v>6</v>
@@ -3026,31 +3250,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -3068,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R6" s="1">
         <v>6</v>
@@ -3080,7 +3304,7 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -3088,31 +3312,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" t="s">
         <v>106</v>
-      </c>
-      <c r="K7" t="s">
-        <v>103</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -3130,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="R7" s="1">
         <v>6</v>
@@ -3142,39 +3366,39 @@
         <v>100</v>
       </c>
       <c r="U7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -3192,7 +3416,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R8" s="1">
         <v>6</v>
@@ -3202,6 +3426,9 @@
       </c>
       <c r="T8">
         <v>100</v>
+      </c>
+      <c r="U8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -3209,31 +3436,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -3251,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -3263,39 +3490,39 @@
         <v>100</v>
       </c>
       <c r="U9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K10" t="s">
         <v>106</v>
-      </c>
-      <c r="K10" t="s">
-        <v>103</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -3313,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -3324,37 +3551,40 @@
       <c r="T10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -3372,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -3383,37 +3613,40 @@
       <c r="T11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -3431,7 +3664,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -3442,37 +3675,40 @@
       <c r="T12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -3490,7 +3726,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -3501,37 +3737,40 @@
       <c r="T13">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -3549,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -3560,37 +3799,40 @@
       <c r="T14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I15" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" t="s">
         <v>106</v>
-      </c>
-      <c r="K15" t="s">
-        <v>103</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -3608,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -3619,37 +3861,40 @@
       <c r="T15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" t="s">
         <v>106</v>
-      </c>
-      <c r="K16" t="s">
-        <v>103</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -3667,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="R16">
         <v>6</v>
@@ -3678,37 +3923,43 @@
       <c r="T16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16" t="s">
+        <v>154</v>
+      </c>
+      <c r="V16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L17">
         <v>15</v>
@@ -3726,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -3737,37 +3988,40 @@
       <c r="T17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" t="s">
         <v>106</v>
-      </c>
-      <c r="K18" t="s">
-        <v>103</v>
       </c>
       <c r="L18">
         <v>15</v>
@@ -3785,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="R18">
         <v>6</v>
@@ -3796,37 +4050,40 @@
       <c r="T18">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L19">
         <v>15</v>
@@ -3844,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -3855,37 +4112,40 @@
       <c r="T19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L20">
         <v>15</v>
@@ -3903,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -3914,37 +4174,43 @@
       <c r="T20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20" t="s">
+        <v>119</v>
+      </c>
+      <c r="V20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" t="s">
         <v>106</v>
-      </c>
-      <c r="K21" t="s">
-        <v>103</v>
       </c>
       <c r="L21">
         <v>15</v>
@@ -3962,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -3972,6 +4238,12 @@
       </c>
       <c r="T21">
         <v>100</v>
+      </c>
+      <c r="U21" t="s">
+        <v>123</v>
+      </c>
+      <c r="V21" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -3979,31 +4251,31 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L22">
         <v>15</v>
@@ -4021,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="R22">
         <v>6</v>
@@ -4033,36 +4305,36 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L23">
         <v>15</v>
@@ -4080,7 +4352,7 @@
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -4090,6 +4362,9 @@
       </c>
       <c r="T23">
         <v>100</v>
+      </c>
+      <c r="U23" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="18:18">
@@ -4113,7 +4388,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.425" style="1" customWidth="1"/>
@@ -4143,25 +4418,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
@@ -4169,10 +4444,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>54</v>
@@ -4181,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
@@ -4190,10 +4465,10 @@
         <v>54</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:11">
@@ -4201,10 +4476,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>54</v>
@@ -4213,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
@@ -4222,10 +4497,10 @@
         <v>54</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:11">
@@ -4233,10 +4508,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>54</v>
@@ -4245,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
@@ -4254,10 +4529,10 @@
         <v>54</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:11">
@@ -4265,31 +4540,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:11">
@@ -4297,31 +4572,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -4329,31 +4604,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:11">
@@ -4361,31 +4636,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:11">
@@ -4393,31 +4668,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -4425,31 +4700,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -4457,31 +4732,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -4489,31 +4764,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:11">
@@ -4521,31 +4796,34 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>205</v>
+        <v>219</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:11">
@@ -4553,31 +4831,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:11">
@@ -4585,31 +4863,34 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>213</v>
+        <v>228</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:11">
@@ -4617,31 +4898,29 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
@@ -4649,31 +4928,29 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -4681,118 +4958,125 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G19" s="1">
-        <v>8</v>
+ 